--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,8 +120,18 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -181,8 +191,23 @@
         <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B2A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F7F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -220,11 +245,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -296,6 +335,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -661,1746 +713,1479 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="B2:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Outcome Type Coding — PSAU Corpus (60 abstracts)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Coded from abstract results language. Categories: Binary (presence/absence, diagnostic pos/neg, yes/no); Continuous (means, yields, rates); Mixed; Null/NS (explicit non-significance); Other.</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Draft_004 — outcome type coding for the 60-abstract PSAU corpus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>Coded from abstract results language. Categories: Binary · Continuous · Mixed · Null/NS · Other. One row per abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Abstract ID</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Hedges</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Outcome Type</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>Coder Notes</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Acs1</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>Acs10</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F7" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Acs2</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F8" s="45" t="inlineStr">
+        <is>
+          <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>Acs3</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F9" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Acs4</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F10" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>Acs5</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>Acs6</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>Acs7</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F13" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Acs8</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>Acs9</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F15" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Aas1</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Aas10</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Aas2</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F18" s="45" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Aas3</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F19" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Aas4</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F20" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Aas5</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F21" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>Aas6</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F22" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Aas7</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D24" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F24" s="45" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Aas9</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F25" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>VM1</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F26" s="45" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>VM2</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>VM3</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F28" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>VM4</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F29" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>VM5</t>
+        </is>
+      </c>
+      <c r="C30" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F30" s="45" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>VM6</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F31" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>VM7</t>
+        </is>
+      </c>
+      <c r="C32" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D32" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F32" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>VM8</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F33" s="46" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>VM9</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D34" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F34" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>VM10</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F35" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="45" t="inlineStr">
+        <is>
+          <t>VM11</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F36" s="45" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>VM12</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F37" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>VM13</t>
+        </is>
+      </c>
+      <c r="C38" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D38" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F38" s="45" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>VM14</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F39" s="46" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>VM15</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F40" s="45" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>VM16</t>
+        </is>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F41" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>VM17</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D42" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F42" s="45" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>VM18</t>
+        </is>
+      </c>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F43" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="45" t="inlineStr">
+        <is>
+          <t>VM19</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D44" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F44" s="45" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>VM20</t>
+        </is>
+      </c>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F45" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="45" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="C46" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n">
+      <c r="D46" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="E46" s="45" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="F46" s="45" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="46" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="C47" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="D47" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="E47" s="46" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="F47" s="46" t="inlineStr">
         <is>
           <t>no zone of inhibition / did not possess</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="45" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="C48" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="D48" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="E48" s="45" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E7" s="40" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="F48" s="45" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="46" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="C49" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="D49" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="E49" s="46" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="F49" s="46" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="45" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="C50" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="D50" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="E50" s="45" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="F50" s="45" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="46" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="C51" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n">
+      <c r="D51" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="E51" s="46" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="F51" s="46" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="45" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="C52" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="D52" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="E52" s="45" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="E11" s="40" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="F52" s="45" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="46" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="C53" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C12" s="40" t="n">
+      <c r="D53" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="E53" s="46" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="F53" s="46" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="45" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="C54" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C13" s="40" t="n">
+      <c r="D54" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="E54" s="45" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="F54" s="45" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="46" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="C55" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C14" s="40" t="n">
+      <c r="D55" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="E55" s="46" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="F55" s="46" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="45" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="C56" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C15" s="40" t="n">
+      <c r="D56" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="E56" s="45" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="F56" s="45" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="40" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="46" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="C57" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C16" s="40" t="n">
+      <c r="D57" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="E57" s="46" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E16" s="40" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="F57" s="46" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="45" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="C58" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C17" s="40" t="n">
+      <c r="D58" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="E58" s="45" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="F58" s="45" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="46" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="C59" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n">
+      <c r="D59" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="E59" s="46" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="F59" s="46" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="45" t="inlineStr">
         <is>
           <t>B15</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="C60" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C19" s="40" t="n">
+      <c r="D60" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="E60" s="45" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="F60" s="45" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="46" t="inlineStr">
         <is>
           <t>B16</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="C61" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C20" s="40" t="n">
+      <c r="D61" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="40" t="inlineStr">
+      <c r="E61" s="46" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E20" s="40" t="inlineStr">
+      <c r="F61" s="46" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="45" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="C62" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C21" s="40" t="n">
+      <c r="D62" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="40" t="inlineStr">
+      <c r="E62" s="45" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E21" s="40" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="F62" s="45" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="46" t="inlineStr">
         <is>
           <t>B18</t>
         </is>
       </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="C63" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C22" s="40" t="n">
+      <c r="D63" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="40" t="inlineStr">
+      <c r="E63" s="46" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E22" s="40" t="inlineStr">
+      <c r="F63" s="46" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="45" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="C64" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C23" s="40" t="n">
+      <c r="D64" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="40" t="inlineStr">
+      <c r="E64" s="45" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="E23" s="40" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="F64" s="45" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="46" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="C65" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C24" s="40" t="n">
+      <c r="D65" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="40" t="inlineStr">
+      <c r="E65" s="46" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="E24" s="40" t="inlineStr">
+      <c r="F65" s="46" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>VM1</t>
-        </is>
-      </c>
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E25" s="40" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <t>VM2</t>
-        </is>
-      </c>
-      <c r="B26" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E26" s="40" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="40" t="inlineStr">
-        <is>
-          <t>VM3</t>
-        </is>
-      </c>
-      <c r="B27" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E27" s="40" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>VM4</t>
-        </is>
-      </c>
-      <c r="B28" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="40" t="inlineStr">
-        <is>
-          <t>VM5</t>
-        </is>
-      </c>
-      <c r="B29" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="40" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="E29" s="40" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="40" t="inlineStr">
-        <is>
-          <t>VM6</t>
-        </is>
-      </c>
-      <c r="B30" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="40" t="inlineStr">
-        <is>
-          <t>VM7</t>
-        </is>
-      </c>
-      <c r="B31" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E31" s="40" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>VM8</t>
-        </is>
-      </c>
-      <c r="B32" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C32" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="40" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="40" t="inlineStr">
-        <is>
-          <t>VM9</t>
-        </is>
-      </c>
-      <c r="B33" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E33" s="40" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>VM10</t>
-        </is>
-      </c>
-      <c r="B34" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="40" t="inlineStr">
-        <is>
-          <t>VM11</t>
-        </is>
-      </c>
-      <c r="B35" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E35" s="40" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="40" t="inlineStr">
-        <is>
-          <t>VM12</t>
-        </is>
-      </c>
-      <c r="B36" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="40" t="inlineStr">
-        <is>
-          <t>VM13</t>
-        </is>
-      </c>
-      <c r="B37" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E37" s="40" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>VM14</t>
-        </is>
-      </c>
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="40" t="inlineStr">
-        <is>
-          <t>VM15</t>
-        </is>
-      </c>
-      <c r="B39" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C39" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="40" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="E39" s="40" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="40" t="inlineStr">
-        <is>
-          <t>VM16</t>
-        </is>
-      </c>
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E40" s="40" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="40" t="inlineStr">
-        <is>
-          <t>VM17</t>
-        </is>
-      </c>
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C41" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E41" s="40" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="40" t="inlineStr">
-        <is>
-          <t>VM18</t>
-        </is>
-      </c>
-      <c r="B42" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C42" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E42" s="40" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="40" t="inlineStr">
-        <is>
-          <t>VM19</t>
-        </is>
-      </c>
-      <c r="B43" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C43" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E43" s="40" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="40" t="inlineStr">
-        <is>
-          <t>VM20</t>
-        </is>
-      </c>
-      <c r="B44" s="40" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C44" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="40" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="E44" s="40" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="40" t="inlineStr">
-        <is>
-          <t>Acs1</t>
-        </is>
-      </c>
-      <c r="B45" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C45" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E45" s="40" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="40" t="inlineStr">
-        <is>
-          <t>Acs2</t>
-        </is>
-      </c>
-      <c r="B46" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C46" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="D46" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E46" s="40" t="inlineStr">
-        <is>
-          <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="40" t="inlineStr">
-        <is>
-          <t>Acs3</t>
-        </is>
-      </c>
-      <c r="B47" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C47" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E47" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="40" t="inlineStr">
-        <is>
-          <t>Acs4</t>
-        </is>
-      </c>
-      <c r="B48" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C48" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="40" t="inlineStr">
-        <is>
-          <t>Acs5</t>
-        </is>
-      </c>
-      <c r="B49" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C49" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E49" s="40" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="40" t="inlineStr">
-        <is>
-          <t>Acs6</t>
-        </is>
-      </c>
-      <c r="B50" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C50" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="E50" s="40" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="40" t="inlineStr">
-        <is>
-          <t>Acs7</t>
-        </is>
-      </c>
-      <c r="B51" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C51" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E51" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="40" t="inlineStr">
-        <is>
-          <t>Acs8</t>
-        </is>
-      </c>
-      <c r="B52" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C52" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E52" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="40" t="inlineStr">
-        <is>
-          <t>Acs9</t>
-        </is>
-      </c>
-      <c r="B53" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C53" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E53" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="40" t="inlineStr">
-        <is>
-          <t>Acs10</t>
-        </is>
-      </c>
-      <c r="B54" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C54" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="40" t="inlineStr">
-        <is>
-          <t>Aas1</t>
-        </is>
-      </c>
-      <c r="B55" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C55" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E55" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="40" t="inlineStr">
-        <is>
-          <t>Aas2</t>
-        </is>
-      </c>
-      <c r="B56" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C56" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E56" s="40" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="40" t="inlineStr">
-        <is>
-          <t>Aas3</t>
-        </is>
-      </c>
-      <c r="B57" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C57" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D57" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E57" s="40" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="40" t="inlineStr">
-        <is>
-          <t>Aas4</t>
-        </is>
-      </c>
-      <c r="B58" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C58" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E58" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="40" t="inlineStr">
-        <is>
-          <t>Aas5</t>
-        </is>
-      </c>
-      <c r="B59" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C59" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" s="40" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="E59" s="40" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="40" t="inlineStr">
-        <is>
-          <t>Aas6</t>
-        </is>
-      </c>
-      <c r="B60" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C60" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E60" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="40" t="inlineStr">
-        <is>
-          <t>Aas7</t>
-        </is>
-      </c>
-      <c r="B61" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C61" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D61" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E61" s="40" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="40" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="B62" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C62" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="40" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="E62" s="40" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="40" t="inlineStr">
-        <is>
-          <t>Aas9</t>
-        </is>
-      </c>
-      <c r="B63" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C63" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E63" s="40" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="40" t="inlineStr">
-        <is>
-          <t>Aas10</t>
-        </is>
-      </c>
-      <c r="B64" s="40" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C64" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" s="40" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="E64" s="40" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="37" t="inlineStr">
-        <is>
-          <t>Cross-tab: Outcome Type × Discipline (abstract counts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="41" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="B69" s="41" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="E69" s="41" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" t="n">
-        <v>8</v>
-      </c>
-      <c r="D70" t="n">
-        <v>7</v>
-      </c>
-      <c r="E70" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>4</v>
-      </c>
-      <c r="C71" t="n">
-        <v>4</v>
-      </c>
-      <c r="D71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>2</v>
-      </c>
-      <c r="C72" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" t="n">
-        <v>4</v>
-      </c>
-      <c r="E72" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>14</v>
-      </c>
-      <c r="C73" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" t="n">
-        <v>5</v>
-      </c>
-      <c r="E73" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" t="n">
-        <v>3</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>20</v>
-      </c>
-      <c r="C75" t="n">
-        <v>20</v>
-      </c>
-      <c r="D75" t="n">
-        <v>20</v>
-      </c>
-      <c r="E75" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="37" t="inlineStr">
-        <is>
-          <t>Mean hedges per abstract by Outcome Type × Discipline</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="41" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="B79" s="41" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="42" t="inlineStr">
-        <is>
-          <t>Binary-outcome account of VM density is NOT supported: VM Binary mean 0.38 (n=8) vs Biology Binary mean 1.57 (n=7). VM low rate is a VM pattern, not a binary pattern. Clearer lead: Agriculture Null/NS 14/20 vs VM 2/20; Agri Null/NS mean ~1.5 hedges; Acs2 = null-rescue hedging.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Agri Null/NS n is high; Acs2 (Null/NS, 8 hedges) is the rescue-hedging outlier, not removed from outcome coding.</t>
-        </is>
-      </c>
+    <row r="66" ht="32" customHeight="1">
+      <c r="B66" s="46" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
+      <c r="E66" s="46" t="n"/>
+      <c r="F66" s="46" t="n"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="B67" s="46" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
+      <c r="E67" s="46" t="n"/>
+      <c r="F67" s="46" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2413,7 +2198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H101"/>
+  <dimension ref="B2:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2677,7 +2462,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -2777,8 +2561,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -11331,928 +11113,953 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="B2:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>P and DO Functions — Scan Log (Non-Hedge Inventory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>Discourse-organization connectors and politeness scan across 60 abstracts. Hedge? = N for all. Not counted in Layer 1/2 totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Abstract ID</t>
         </is>
       </c>
-      <c r="B1" s="37" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="C1" s="37" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Phrase / Token</t>
         </is>
       </c>
-      <c r="D1" s="37" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Context (short)</t>
         </is>
       </c>
-      <c r="E1" s="37" t="inlineStr">
-        <is>
-          <t>Function (EC/P/DO)</t>
-        </is>
-      </c>
-      <c r="F1" s="37" t="inlineStr">
-        <is>
-          <t>Hedge? (Y/N)</t>
-        </is>
-      </c>
-      <c r="G1" s="37" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="G5" s="44" t="inlineStr">
+        <is>
+          <t>Hedge?</t>
+        </is>
+      </c>
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>Ambiguous</t>
         </is>
       </c>
-      <c r="H1" s="37" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>Thus / Therefore</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>Thus, in the optimization process...; Therefore, further research will...</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F6" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G6" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H6" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I6" s="45" t="inlineStr">
         <is>
           <t>Move connectors (problem→method; limit→future work). Not epistemic hedges.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>Hence / thus</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E7" s="46" t="inlineStr">
         <is>
           <t>Hence, the biosynthesis is feasible; thus making a remarkable choice; thus demonstrating...</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F7" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G7" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H7" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I7" s="46" t="inlineStr">
         <is>
           <t>Claim-sequence connectors. Hedge if any is separate (may).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Thus</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
         <is>
           <t>Thus, the researcher provided a policy proposal...</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F8" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G8" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H8" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I8" s="45" t="inlineStr">
         <is>
           <t>Results→recommendation connector.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>Hence</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E9" s="46" t="inlineStr">
         <is>
           <t>Hence, this study aimed to investigate...</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F9" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G9" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H9" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I9" s="46" t="inlineStr">
         <is>
           <t>Background→aim connector.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>Hence</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>Hence, LAB have emerged as a focal point...</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F10" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G10" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H10" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I10" s="45" t="inlineStr">
         <is>
           <t>Problem→focus connector.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>B16</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>Thus / therefore</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E11" s="46" t="inlineStr">
         <is>
           <t>Thus, this study detected...; This study, therefore, underscores...</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F11" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G11" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H11" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I11" s="46" t="inlineStr">
         <is>
           <t>Rationale→aim / findings→implication connectors.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D12" s="45" t="inlineStr">
         <is>
           <t>Hence / Thus</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E12" s="45" t="inlineStr">
         <is>
           <t>Hence, sustainable planning should...; Thus, local government should...</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F12" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G12" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H12" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I12" s="45" t="inlineStr">
         <is>
           <t>Problem/findings→recommendation connectors.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>Therefore / Hence</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E13" s="46" t="inlineStr">
         <is>
           <t>Therefore, this study aims...; Hence, the study aimed...</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F13" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G13" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H13" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I13" s="46" t="inlineStr">
         <is>
           <t>Background→aim connectors.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="45" t="inlineStr">
         <is>
           <t>VM7</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D14" s="45" t="inlineStr">
         <is>
           <t>Thus</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E14" s="45" t="inlineStr">
         <is>
           <t>Thus, no significant association could be established</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F14" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G14" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H14" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I14" s="45" t="inlineStr">
         <is>
           <t>Results→conclusion connector.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>VM9</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>hence</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E15" s="46" t="inlineStr">
         <is>
           <t>hence, all individual shrimps counted as one sample</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F15" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G15" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H15" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I15" s="46" t="inlineStr">
         <is>
           <t>Methods sequencing only.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="45" t="inlineStr">
         <is>
           <t>VM12</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>Hence</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E16" s="45" t="inlineStr">
         <is>
           <t>Hence, this study aimed to detect ASF virus...</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F16" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G16" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H16" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I16" s="45" t="inlineStr">
         <is>
           <t>Background→aim connector.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Acs5</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>Therefore</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E17" s="46" t="inlineStr">
         <is>
           <t>Therefore, the... (yield inference connector)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F17" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G17" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H17" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I17" s="46" t="inlineStr">
         <is>
           <t>Results→inference connector.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="45" t="inlineStr">
         <is>
           <t>Aas9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D18" s="45" t="inlineStr">
         <is>
           <t>Therefore</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E18" s="45" t="inlineStr">
         <is>
           <t>Therefore, it is recommended for future researchers...</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F18" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G18" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H18" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I18" s="45" t="inlineStr">
         <is>
           <t>Results→recommendation connector.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Acs3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E19" s="46" t="inlineStr">
         <is>
           <t>In conclusion, the number of rooted...</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F19" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H19" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I19" s="46" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>Acs7</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C20" s="45" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E20" s="45" t="inlineStr">
         <is>
           <t>In conclusion, the use of rice hull...</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F20" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G20" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H20" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I20" s="45" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>Acs10</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E21" s="46" t="inlineStr">
         <is>
           <t>In conclusion, T3:...</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F21" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G21" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H21" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I21" s="46" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="B22" s="45" t="inlineStr">
         <is>
           <t>Aas3</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C22" s="45" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D22" s="45" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E22" s="45" t="inlineStr">
         <is>
           <t>In conclusion, proved the treatment 1...</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F22" s="45" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G22" s="45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H22" s="45" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I22" s="45" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Aas10</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E23" s="46" t="inlineStr">
         <is>
           <t>In conclusion, based on the results, it can be stated...</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F23" s="46" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G23" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H23" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I23" s="46" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="24" ht="40" customHeight="1">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>All disciplines</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D24" s="47" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E24" s="47" t="inlineStr">
         <is>
           <t>No "as X suggested", "in our view", "please", "kindly", "with due respect", "one might argue"</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F24" s="47" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G24" s="47" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H24" s="47" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I24" s="47" t="inlineStr">
         <is>
           <t>No politeness/deference devices in the 60 abstracts.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="25" ht="40" customHeight="1">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D25" s="47" t="inlineStr">
         <is>
           <t>regarding / with regard to / overall / first-second</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E25" s="47" t="inlineStr">
         <is>
           <t>Common in VM KAP and ranking sentences</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F25" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G25" s="47" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H25" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I25" s="47" t="inlineStr">
         <is>
           <t>Topic prepositions and ordinal ranking of results are NOT discourse-organization function. Left untagged.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="26" ht="40" customHeight="1">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D26" s="47" t="inlineStr">
         <is>
           <t>should / recommended (FP-Rec)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E26" s="47" t="inlineStr">
         <is>
           <t>See Rejected Candidates</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F26" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G26" s="47" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H26" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I26" s="47" t="inlineStr">
         <is>
           <t>Deontic prescriptions. Reject reason FP-Rec, not Layer 2 P or DO.</t>
         </is>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcome Type" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hedges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hedges" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected Candidates" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unhedged Sites" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected Candidates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P and DO Functions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcome Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P and DO Functions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,1491 +713,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F67"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Outcome Type Coding — PSAU Corpus (60 abstracts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="43" t="inlineStr">
-        <is>
-          <t>Coded from abstract results language. Categories: Binary · Continuous · Mixed · Null/NS · Other. One row per abstract.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="44" t="inlineStr">
-        <is>
-          <t>Abstract ID</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="inlineStr">
-        <is>
-          <t>Discipline</t>
-        </is>
-      </c>
-      <c r="D5" s="44" t="inlineStr">
-        <is>
-          <t>Hedges</t>
-        </is>
-      </c>
-      <c r="E5" s="44" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="F5" s="44" t="inlineStr">
-        <is>
-          <t>Coder Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t>Acs1</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D6" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="45" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F6" s="45" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="46" t="inlineStr">
-        <is>
-          <t>Acs10</t>
-        </is>
-      </c>
-      <c r="C7" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F7" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="45" t="inlineStr">
-        <is>
-          <t>Acs2</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D8" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F8" s="45" t="inlineStr">
-        <is>
-          <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="46" t="inlineStr">
-        <is>
-          <t>Acs3</t>
-        </is>
-      </c>
-      <c r="C9" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F9" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>Acs4</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F10" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="46" t="inlineStr">
-        <is>
-          <t>Acs5</t>
-        </is>
-      </c>
-      <c r="C11" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="46" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F11" s="46" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="45" t="inlineStr">
-        <is>
-          <t>Acs6</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="45" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F12" s="45" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="46" t="inlineStr">
-        <is>
-          <t>Acs7</t>
-        </is>
-      </c>
-      <c r="C13" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F13" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>Acs8</t>
-        </is>
-      </c>
-      <c r="C14" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F14" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="46" t="inlineStr">
-        <is>
-          <t>Acs9</t>
-        </is>
-      </c>
-      <c r="C15" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F15" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>Aas1</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="46" t="inlineStr">
-        <is>
-          <t>Aas10</t>
-        </is>
-      </c>
-      <c r="C17" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D17" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F17" s="46" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="45" t="inlineStr">
-        <is>
-          <t>Aas2</t>
-        </is>
-      </c>
-      <c r="C18" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D18" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="45" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F18" s="45" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="46" t="inlineStr">
-        <is>
-          <t>Aas3</t>
-        </is>
-      </c>
-      <c r="C19" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F19" s="46" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>Aas4</t>
-        </is>
-      </c>
-      <c r="C20" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D20" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F20" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="46" t="inlineStr">
-        <is>
-          <t>Aas5</t>
-        </is>
-      </c>
-      <c r="C21" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D21" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="46" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F21" s="46" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="45" t="inlineStr">
-        <is>
-          <t>Aas6</t>
-        </is>
-      </c>
-      <c r="C22" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D22" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F22" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="46" t="inlineStr">
-        <is>
-          <t>Aas7</t>
-        </is>
-      </c>
-      <c r="C23" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D23" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F23" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="45" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="C24" s="45" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D24" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="45" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F24" s="45" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="46" t="inlineStr">
-        <is>
-          <t>Aas9</t>
-        </is>
-      </c>
-      <c r="C25" s="46" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D25" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F25" s="46" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="45" t="inlineStr">
-        <is>
-          <t>VM1</t>
-        </is>
-      </c>
-      <c r="C26" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D26" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F26" s="45" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="46" t="inlineStr">
-        <is>
-          <t>VM2</t>
-        </is>
-      </c>
-      <c r="C27" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D27" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="46" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F27" s="46" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="45" t="inlineStr">
-        <is>
-          <t>VM3</t>
-        </is>
-      </c>
-      <c r="C28" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D28" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F28" s="45" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="46" t="inlineStr">
-        <is>
-          <t>VM4</t>
-        </is>
-      </c>
-      <c r="C29" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D29" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F29" s="46" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="45" t="inlineStr">
-        <is>
-          <t>VM5</t>
-        </is>
-      </c>
-      <c r="C30" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D30" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="45" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F30" s="45" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="46" t="inlineStr">
-        <is>
-          <t>VM6</t>
-        </is>
-      </c>
-      <c r="C31" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D31" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F31" s="46" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="45" t="inlineStr">
-        <is>
-          <t>VM7</t>
-        </is>
-      </c>
-      <c r="C32" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D32" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F32" s="45" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="46" t="inlineStr">
-        <is>
-          <t>VM8</t>
-        </is>
-      </c>
-      <c r="C33" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D33" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="46" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F33" s="46" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="45" t="inlineStr">
-        <is>
-          <t>VM9</t>
-        </is>
-      </c>
-      <c r="C34" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D34" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F34" s="45" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="46" t="inlineStr">
-        <is>
-          <t>VM10</t>
-        </is>
-      </c>
-      <c r="C35" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D35" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F35" s="46" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="45" t="inlineStr">
-        <is>
-          <t>VM11</t>
-        </is>
-      </c>
-      <c r="C36" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="45" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F36" s="45" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="46" t="inlineStr">
-        <is>
-          <t>VM12</t>
-        </is>
-      </c>
-      <c r="C37" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D37" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F37" s="46" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="45" t="inlineStr">
-        <is>
-          <t>VM13</t>
-        </is>
-      </c>
-      <c r="C38" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D38" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="45" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F38" s="45" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="46" t="inlineStr">
-        <is>
-          <t>VM14</t>
-        </is>
-      </c>
-      <c r="C39" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D39" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="46" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F39" s="46" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="45" t="inlineStr">
-        <is>
-          <t>VM15</t>
-        </is>
-      </c>
-      <c r="C40" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D40" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="45" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F40" s="45" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="46" t="inlineStr">
-        <is>
-          <t>VM16</t>
-        </is>
-      </c>
-      <c r="C41" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D41" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F41" s="46" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>VM17</t>
-        </is>
-      </c>
-      <c r="C42" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D42" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="45" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F42" s="45" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="46" t="inlineStr">
-        <is>
-          <t>VM18</t>
-        </is>
-      </c>
-      <c r="C43" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D43" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="46" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F43" s="46" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="45" t="inlineStr">
-        <is>
-          <t>VM19</t>
-        </is>
-      </c>
-      <c r="C44" s="45" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D44" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F44" s="45" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="46" t="inlineStr">
-        <is>
-          <t>VM20</t>
-        </is>
-      </c>
-      <c r="C45" s="46" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D45" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F45" s="46" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="45" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C46" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D46" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F46" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="46" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C47" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D47" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F47" s="46" t="inlineStr">
-        <is>
-          <t>no zone of inhibition / did not possess</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="45" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="C48" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D48" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F48" s="45" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="46" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C49" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D49" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="46" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F49" s="46" t="n"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="45" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="C50" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D50" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F50" s="45" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="46" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C51" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D51" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="46" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F51" s="46" t="n"/>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="45" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="C52" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D52" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="45" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F52" s="45" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="46" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="C53" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D53" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F53" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="B54" s="45" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="C54" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D54" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="45" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F54" s="45" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="46" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C55" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D55" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="46" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F55" s="46" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="B56" s="45" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="C56" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D56" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F56" s="45" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="B57" s="46" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
-      </c>
-      <c r="C57" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D57" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="46" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F57" s="46" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="B58" s="45" t="inlineStr">
-        <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="C58" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D58" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="45" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F58" s="45" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="B59" s="46" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="C59" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D59" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E59" s="46" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F59" s="46" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="45" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
-      </c>
-      <c r="C60" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D60" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F60" s="45" t="n"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="46" t="inlineStr">
-        <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="C61" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D61" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="E61" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F61" s="46" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="B62" s="45" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C62" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D62" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F62" s="45" t="n"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="B63" s="46" t="inlineStr">
-        <is>
-          <t>B18</t>
-        </is>
-      </c>
-      <c r="C63" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D63" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="46" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F63" s="46" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="B64" s="45" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="C64" s="45" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D64" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="45" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F64" s="45" t="n"/>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="B65" s="46" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C65" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D65" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F65" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="B66" s="46" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
-      <c r="E66" s="46" t="n"/>
-      <c r="F66" s="46" t="n"/>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="B67" s="46" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
-      <c r="E67" s="46" t="n"/>
-      <c r="F67" s="46" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B2:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4241,7 +2756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7111,6 +5626,2109 @@
         </is>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Rejected Hedge Candidates — False Positives</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Abstract ID</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Sentence #</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Clause</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Token</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Reason Code</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Coder Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>In this study, the growth promoting potential of Bacillus subtilis BIOTECH 1679 was assessed under greenhouse conditions.</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'the growth promoting potential of Bacillus subtilis BIOTECH 1679 was assessed' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Results indicated that Bacillus subtilis formulation (9.0 x 10⁸ CFU/mL) of 10 g/L (T1), 30 g/L (T2), and 50 g/L (T3) concentrations exhibited a notable increase in plant growth parameters.</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>indicated</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>[AMB] Factive reporting: 'Results indicated that... exhibited a notable increase' — synonym for 'showed', reports results as settled fact. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>In the antibacterial testing, the paper disc diffusion method is used in order to indicate the zone of inhibition in the evaluation of Antibacterial potential of Balitbitan on Mueller Hinton Agar.</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>indicate</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>FP-Proc</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>Procedural: 'the paper disc diffusion method is used in order to indicate the zone of inhibition' describes what the method does procedurally, not pointing to a location in a table/figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>In the antibacterial testing, the paper disc diffusion method is used in order to indicate the zone of inhibition in the evaluation of Antibacterial potential of Balitbitan on Mueller Hinton Agar.</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming: 'evaluation of Antibacterial potential of Balitbitan' names the research topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>This study evaluated the acute toxicity and antitussive activity of Mimosa pudica (Makahiya) ethanolic extract in ICR mice to assess its safety and potential as a natural antitussive agent or cough suppressant.</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'to assess its safety and potential as a natural antitussive agent' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>No mortality, distress, or significant weight changes were observed, indicating that Mimosa pudica extract is non-toxic up to 2000 mg/kg.</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>Operational restatement: 'no mortality... indicating non-toxic' — non-toxicity is the operational definition of no adverse effects in an acute toxicity design, not an inference beyond the measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Further studies are recommended to confirm its long-term safety, refine dosing, and better understand its mechanisms of action.</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'Further studies are recommended to confirm' prescribes action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>In the current study, the antibacterial and antioxidant potential of Copper oxide nanoparticles (CuO NPs) were evaluated.</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'the antibacterial and antioxidant potential of Copper oxide nanoparticles (CuO NPs) were evaluated' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Moreover, using growth-kinetic assay, antibacterial activities of the different concentrations of CuO NPs were determined and found to be statistically significantly different (p &lt;0.05) from each other for the Staphylococcus aureus, Salmonella enterica serovar Typhimurium, Shigella sp., and Bacillus cereus, indicating a dose-dependent response.</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>Factive (operational definition): 'statistically significantly different... indicating a dose-dependent response' — dose-dependency is the operational interpretation of significant differences between concentrations, not a hedged inference. Per indicating rule: restates operational meaning = factive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>The study would be on developing and optimizing eco-bricks using a mixture of SUPs and UCO developed through trial and error.</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>would</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>General (grammatical scaffolding): 'The study would be on developing...' required by sentence structure, not epistemic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Therefore, further research will aid in underlining the importance of optimizing the ingredient ratios to acquire desirable quality eco-bricks for sustainable construction applications.</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>will</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>General (future procedure): 'further research will aid in underlining' — future procedure, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>The study generally aimed to evaluate the embryo toxicity, lethality, and teratogenicity of Ziziphus talanai-infused nanozeolite pellets on Danio rerio was performed at the Biology and Chemistry Laboratory of Pampanga State Agricultural University from October 2023 to January 2024.</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>generally</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>FP-Proc</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>Procedural norm: 'The study generally aimed to evaluate' describes the framing of the aim, not a claim's scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>The antibacterial potential of fungus-mediated AgNPs was distinguished by performing the agar well diffusion method and determining minimum bactericidal concentration (MBC) and minimum inhibitory concentration (MIC) via resazurin and MTT assays.</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (methods): 'The antibacterial potential of fungus-mediated AgNPs was distinguished by performing the agar well diffusion method' names the research object being measured, parallel to aim-sentence topic-naming. Codebook rule applied consistently across aim and methods sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>This study aimed to identify the histoprotective potential of Balakat extract (Ziziphus talanai) against monosodium glutamate effect to the specific vital organs of Mus musculus through observing the lesions / aberrations to the heart, liver and kidney.</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'This study aimed to identify the histoprotective potential of Balakat extract' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>In terms of practices, proper waste management should be established to avoid the high danger of heavy metal contamination.</t>
+        </is>
+      </c>
+      <c r="F19" s="29" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="G19" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'proper waste management should be established' — deontic prescription, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>As a result, some community or local government-adopted measures are proposed.</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>General (describes an output, not a claim): 'some community or local government-adopted measures are proposed' names the study's output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Overall, the combination of Ziehl-Neelsen staining, biochemical testing like the catalase test, and evaluating growth in the presence of the Salt Tolerance Test provides a comprehensive approach for diagnosing and studying mycobacteriosis in cultivated milkfish, offering insights that can guide effective management strategies to control the spread of this disease in aquaculture system.</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>Capability: 'insights that can guide effective management strategies' describes inherent ability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Results also showed that the antibacterial property of Bangkok Kalachuchi (Adenium obesum) against Staphylococcus aureus (ATCC 25923) are significantly different at various concentration indicating that its antibacterial property is dose dependent.</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="G22" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>Factive (operational definition): 'significantly different at various concentration indicating that its antibacterial property is dose dependent' — dose-dependency is the operational interpretation of significant differences between concentrations. Per indicating rule: restates operational meaning = factive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>The present study conducted an experiment to determine the antifungal potential of paragis leaf extracts against Colletotrichum species.</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G23" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'antifungal potential of paragis leaf extracts' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Paper disc diffusion assay was done using crude ethanolic leaf extract in different concentrations and extraction techniques, Kupchan Partitioning Method (Polar, Semi-polar, Non-polar fractions), and ethanolic crude in boiled, and not boiled treatments in determining its antifungal potential.</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (methods): 'in determining its antifungal potential' names the research object being measured, parallel to the aim-sentence topic-naming rule. Same code applied regardless of sentence type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>The findings of this study showed and suggests that the extraction efficiency favors the highly polar solvents than the non-polar solvents in determining the antifungal potential of E. indica against Colletotrichum spp..</t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (methods): 'determining the antifungal potential of E. indica against Colletotrichum spp.' names the research object being measured, parallel to the aim-sentence topic-naming rule. Same code applied regardless of sentence type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>The biodegradable plate developed exhibited the following properties: Bamboo fiber plates (T1) and bamboo fiber plates coated with aloe vera (T2) degrade faster than styrofoam and silver foil plates; Bamboo fiber plates coated with aloe vera (T2) showcased the highest tensile strength compared to other treatments Bamboo fiber plates (T1) and bamboo fiber plates coated with aloe vera (T2) uptake more water than styrofoam and silver foil paper plates; The significant differences in melting temperature indicate variations in thermal stability among the different plate materials.</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>indicate</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>[AMB] Factive reporting: 'significant differences in melting temperature indicate variations in thermal stability' — direct logical entailment from statistical significance, not a hedged inference. Per Decision Rules: synonym for showed/demonstrated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>MRSA bacteria can survive long on surfaces and objects, including second-hand clothing (SHC).</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G27" s="30" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>Capability: 'MRSA bacteria can survive long on surfaces' describes inherent ability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>This study aimed to assess the phytochemical composition, antioxidant potential, and antibacterial activity of P. propinquum fruit ethanolic extract using Thin Layer Chromatography (TLC)-based techniques.</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'assess the phytochemical composition, antioxidant potential, and antibacterial activity of P. propinquum' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>The TLC-DPPH assay demonstrated notable antioxidant activity, as indicated by the reduction of DPPH radicals.</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>indicated</t>
+        </is>
+      </c>
+      <c r="G29" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>Evidential pointer: 'notable antioxidant activity, as indicated by the reduction of DPPH radicals' — points to evidence for a claim already asserted, not uncertainty about the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>Further studies should focus on the isolation and characterization of its active compounds, their mechanisms of action, and their potential pharmaceutical applications.</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'Further studies should focus on the isolation and characterization' — deontic prescription, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>Further studies should focus on the isolation and characterization of its active compounds, their mechanisms of action, and their potential pharmaceutical applications.</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (recommendation-embedded): 'their potential pharmaceutical applications' is the object of a future-research recommendation, not a hedged claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>Hence, sustainable planning and management approaches should be considered.</t>
+        </is>
+      </c>
+      <c r="F32" s="29" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'sustainable planning and management approaches should be considered' — deontic prescription, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>Thus, local government should address the possible negative impacts of tourism activities and manage the carrying capacity for sustainable tourism.</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="G33" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'local government should address the possible negative impacts of tourism activities' — deontic prescription, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>Therefore, this study aims to examine the potential of Trichoderma harzianum, an endophytic fungus, as a biocontrol agent for Cercospora leaf spot-on eggplants in the Philippines.</t>
+        </is>
+      </c>
+      <c r="F34" s="29" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'this study aims to examine the potential of Trichoderma harzianum' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>Hence, the study aimed to investigate the antagonistic potential of Trichoderma harzianum among the four isolates.</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G35" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'the study aimed to investigate the antagonistic potential of Trichoderma harzianum' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>The results indicate that the mean effect of Trichoderma harzianum on the test variables varied across the three days of observation.</t>
+        </is>
+      </c>
+      <c r="F36" s="29" t="inlineStr">
+        <is>
+          <t>indicate</t>
+        </is>
+      </c>
+      <c r="G36" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>[AMB] Factive reporting: 'The results indicate that the mean effect... varied' — factive reporting of a statistical outcome, synonym for 'showed'. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>VM3</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>The findings suggests the need for assessment of knowledge, attitudes and practices of retail egg vendors about food safety and regular antimicrobial resistance monitoring on retail eggs.</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>suggests</t>
+        </is>
+      </c>
+      <c r="G37" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'The findings suggests the need for assessment of knowledge, attitudes and practices' prescribes action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>VM4</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>These findings suggest the need to improve training, regulation of milk storage, and the enforcement of labeling and sanitation standards to improve public health safety in the milk supply chain.</t>
+        </is>
+      </c>
+      <c r="F38" s="29" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'These findings suggest the need to improve training, regulation of milk storage...' prescribes action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>VM5</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>This study explores the potential antifungal properties of Muntingia calabura L. methanolic leaf extracts against Trichophyton mentagrophytes, a dermatophyte species.</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G39" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'potential antifungal properties of Muntingia calabura L.' names the research object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>VM7</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>These measures can collectively contribute to the effective management and prevention of heartworm disease in the local canine population.</t>
+        </is>
+      </c>
+      <c r="F40" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
+          <t>General (recommendation-embedded): 'These measures can collectively contribute to...' follows a list of recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>VM7</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>Further research with larger sample sizes and diverse populations is needed to validate these findings and enhance our understanding of heartworm infection in the study area.</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>needed</t>
+        </is>
+      </c>
+      <c r="G41" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'Further research... is needed to validate these findings' prescribes action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>VM9</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>To reduce microplastic pollution, the findings recommend removing the shrimp’s GIT during preparation to avoid ingestion, use fishing gear made from durable or natural materials, regularly maintain and replace worn equipment, and properly dispose of plastics instead of discarding them into water bodies.</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="inlineStr">
+        <is>
+          <t>recommend</t>
+        </is>
+      </c>
+      <c r="G42" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'the findings recommend removing the shrimp's GIT during preparation' prescribes action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>VM11</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>The stray cats’ hematological profiles were compared to normal parameters to assess their health status and whether they had the possibility of any underlying diseases based on the blood profiling.</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>possibility</t>
+        </is>
+      </c>
+      <c r="G43" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="inlineStr">
+        <is>
+          <t>Topic-naming (aim): 'whether they had the possibility of any underlying diseases' names the research object being investigated. Per extended rule: possibility + noun in aim/methods sentences = topic-naming, same as potential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>VM12</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>Nevertheless, it is recommended to consider monitoring and surveillance of ASF at the market level, and maintain and continue the strict implementation of collaborative efforts to effectively and efficiently prevent and control the further entry and spread of ASF from farm to farm.</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="G44" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'it is recommended to consider monitoring and surveillance of ASF at the market level'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>VM14</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Multiple regression analysis indicated that knowledge significantly predicted self-assessed awareness, while personal experience did not.</t>
+        </is>
+      </c>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>indicated</t>
+        </is>
+      </c>
+      <c r="G45" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H45" s="21" t="inlineStr">
+        <is>
+          <t>[AMB] Factive reporting: 'Multiple regression analysis indicated that knowledge significantly predicted self-assessed awareness' — factive reporting of regression output, synonym for 'showed'. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>VM15</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>The anti-cancer potential of the extract was determined using a brine shrimp lethality assay, and after three and six hours of exposure, the surviving brine shrimps were counted.</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>Topic-naming (methods): 'The anti-cancer potential of the extract was determined using a brine shrimp lethality assay' names the research object being measured, parallel to aim-sentence topic-naming. Codebook rule applied consistently across aim and methods sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>VM18</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>Zoonotic diseases are a significant public health concern, particularly those that can be transmitted from dogs to humans.</t>
+        </is>
+      </c>
+      <c r="F47" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G47" s="30" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H47" s="21" t="inlineStr">
+        <is>
+          <t>Capability: 'Zoonotic diseases... particularly those that can be transmitted from dogs to humans' describes inherent property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>VM20</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>Strengthening policies on pet vaccination programs and implementing stricter guidelines for pet care are recommended to mitigate rabies transmission risks.</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="G48" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'stricter guidelines for pet care are recommended to mitigate rabies transmission risks'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Acs1</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>These findings suggest that fermented banana peel, when applied at an optimal rate in combination with reduced synthetic fertilizer input, can significantly enhance the growth and yield performance of finger pepper, offering a sustainable alternative for crop production.</t>
+        </is>
+      </c>
+      <c r="F49" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G49" s="30" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H49" s="21" t="inlineStr">
+        <is>
+          <t>[AMB] Capability: 'can significantly enhance' — can + active content verb (enhance) describing a treatment effect. Per Decision Rules: can + enhance/promote/reduce/help = capability regardless of clause embedding. Working Test: remove 'can' alone, 'suggests that... significantly enhances' remains fully hedged by 'suggests.'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Acs2</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>Further research could unveil additional insights and applications for optimizing plant health.</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="inlineStr">
+        <is>
+          <t>could</t>
+        </is>
+      </c>
+      <c r="G50" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>Future research framing: 'Further research could unveil additional insights and applications' — the modal scopes over the feasibility of a future research activity, not over the truth value of a present claim. Same rule as Aas8 'Further research can explore'. Per codebook: epistemic hedges concern claim uncertainty, not research possibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Acs3</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>Most can survive the water treatment application but may not establish roots and die after several days.</t>
+        </is>
+      </c>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G51" s="30" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H51" s="21" t="inlineStr">
+        <is>
+          <t>Capability: 'Most can survive the water treatment application' describes inherent ability of cuttings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Acs4</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>However, the negative control can reduce production cost and provide the highest return on investment.</t>
+        </is>
+      </c>
+      <c r="F52" s="31" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G52" s="32" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>Capability: 'the negative control can reduce production cost' — describes the inherent ability of a specific treatment, not epistemic possibility. Swap with 'is able to' and meaning holds. Per codebook: capability 'can' = FP-Cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Acs6</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>Treatment 3 (Carbonized Rice Hull) showed moderate growth improvement, while Treatments 1 (Topsoil only) and 5 (Biochar) performed poorly in most parameters, indicating limited benefits.</t>
+        </is>
+      </c>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="G53" s="30" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="inlineStr">
+        <is>
+          <t>Operational restatement: 'performed poorly... indicating limited benefits' — limited benefit is near-tautological with poor performance, not an inference beyond the measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Acs8</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>The researcher recommends foliar and drenching application of kuhol amino acid. because, numerically, it consistently produced the highest yield performance.</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="inlineStr">
+        <is>
+          <t>recommends</t>
+        </is>
+      </c>
+      <c r="G54" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'The researcher recommends foliar and drenching application of kuhol amino acid'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Aas3</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>It can also be concluded that D1 rice bran mixed with water spinach and with golden apple snail used in the study can help minimize the cost of production, specifically the feed cost.</t>
+        </is>
+      </c>
+      <c r="F55" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G55" s="30" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H55" s="21" t="inlineStr">
+        <is>
+          <t>Capability: 'golden apple snail used in the study can help minimize the cost of production' describes inherent ability. Capability substitution test: 'is able to help' preserves meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Aas5</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>In order to meet the demand for highly nutritious animal food, the future will drive animal production systems to find new sources of high-quality and sustainable protein feed raw materials.</t>
+        </is>
+      </c>
+      <c r="F56" s="31" t="inlineStr">
+        <is>
+          <t>will</t>
+        </is>
+      </c>
+      <c r="G56" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>General (future procedure): 'the future will drive animal production systems to find new sources' — future procedure, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>However, T1 exhibited the lowest feed conversion ratio (FCR) and mortality rate, indicating superior feed efficiency and improved survivability to T2.</t>
+        </is>
+      </c>
+      <c r="F57" s="31" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="G57" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H57" s="23" t="inlineStr">
+        <is>
+          <t>Operational restatement: 'lowest FCR... indicating superior feed efficiency' — lower feed conversion ratio is the definitional measure of superior feed efficiency in animal nutrition, not an inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>Based on the results of the study, it is recommended to feed mallard ducks with 75% rice porridge and 25% fish entrails during brooding stage at day 1 to day 21 for enhancing weight gain and achieving higher final weights in mallard ducks.</t>
+        </is>
+      </c>
+      <c r="F58" s="29" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H58" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'it is recommended to feed mallard ducks with 75% rice porridge and 25% fish entrails'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>Further research can explore the long-term effects and cost-effectiveness of these treatments and their impact on meat quality and reproductive performance.</t>
+        </is>
+      </c>
+      <c r="F59" s="31" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G59" s="32" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="inlineStr">
+        <is>
+          <t>General (future research statement): 'Further research can explore the long-term effects and cost-effectiveness' — future research framing, not hedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Aas9</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>Therefore, it is recommended for future researchers to add Diatomaceous earth and neem tree extract and check the humidity.</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H60" s="21" t="inlineStr">
+        <is>
+          <t>Recommendation: 'it is recommended for future researchers to add Diatomaceous earth and neem tree extract'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Aas10</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>The researchers still recommended incorporating 50% Guinea grass + 20% Azolla + 30% concentrates for rabbit growth performance, considering the results show that this treatment performs well and doesn't differ from treatment 1, which is the farmer practice.</t>
+        </is>
+      </c>
+      <c r="F61" s="31" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="G61" s="32" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t>Recommendation: 'The researchers still recommended incorporating 50% Guinea grass + 20% Azolla + 30% concentrates for rabbit growth performance'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aas10</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>The researchers also saw that the treatment of 50% Guinea grass + 20% Azolla + 30% concentrates has potential as an alternative feed ration for rabbits without adverse effects, and considering that azolla can help breeders to lessen the feed cost in production.</t>
+        </is>
+      </c>
+      <c r="F62" s="29" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="H62" s="21" t="inlineStr">
+        <is>
+          <t>Capability: 'azolla can help breeders to lessen the feed cost' describes inherent ability. Capability substitution test: 'is able to help' preserves meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1"/>
+    <row r="64" ht="45" customHeight="1"/>
+    <row r="65" ht="45" customHeight="1"/>
+    <row r="66" ht="45" customHeight="1"/>
+    <row r="67" ht="45" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8485,2629 +9103,1486 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H62"/>
+  <dimension ref="B2:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>Rejected Hedge Candidates — False Positives</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+          <t>Outcome Type Coding — PSAU Corpus (60 abstracts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>Coded from abstract results language. Categories: Binary · Continuous · Mixed · Null/NS · Other. One row per abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Abstract ID</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Sentence #</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Clause</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Token</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Reason Code</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>Hedges</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>Coder Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="B5" s="5" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Acs1</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>Acs10</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F7" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Acs2</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F8" s="45" t="inlineStr">
+        <is>
+          <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>Acs3</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F9" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Acs4</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F10" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>Acs5</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D11" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>Acs6</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="46" t="inlineStr">
+        <is>
+          <t>Acs7</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F13" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Acs8</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="46" t="inlineStr">
+        <is>
+          <t>Acs9</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F15" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Aas1</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Aas10</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Aas2</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F18" s="45" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Aas3</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F19" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Aas4</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F20" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Aas5</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D21" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F21" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>Aas6</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F22" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Aas7</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D24" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F24" s="45" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Aas9</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F25" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>VM1</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F26" s="45" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>VM2</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>VM3</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F28" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>VM4</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F29" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>VM5</t>
+        </is>
+      </c>
+      <c r="C30" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D30" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F30" s="45" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>VM6</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F31" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>VM7</t>
+        </is>
+      </c>
+      <c r="C32" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D32" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F32" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>VM8</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F33" s="46" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>VM9</t>
+        </is>
+      </c>
+      <c r="C34" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D34" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F34" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>VM10</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F35" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="45" t="inlineStr">
+        <is>
+          <t>VM11</t>
+        </is>
+      </c>
+      <c r="C36" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F36" s="45" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>VM12</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F37" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>VM13</t>
+        </is>
+      </c>
+      <c r="C38" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D38" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F38" s="45" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>VM14</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F39" s="46" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>VM15</t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F40" s="45" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>VM16</t>
+        </is>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F41" s="46" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>VM17</t>
+        </is>
+      </c>
+      <c r="C42" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D42" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F42" s="45" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>VM18</t>
+        </is>
+      </c>
+      <c r="C43" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F43" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="45" t="inlineStr">
+        <is>
+          <t>VM19</t>
+        </is>
+      </c>
+      <c r="C44" s="45" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D44" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F44" s="45" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>VM20</t>
+        </is>
+      </c>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F45" s="46" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="45" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C46" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D46" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F46" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="46" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F47" s="46" t="inlineStr">
+        <is>
+          <t>no zone of inhibition / did not possess</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="45" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C48" s="45" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D48" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F48" s="45" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>In this study, the growth promoting potential of Bacillus subtilis BIOTECH 1679 was assessed under greenhouse conditions.</t>
-        </is>
-      </c>
-      <c r="F5" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G5" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'the growth promoting potential of Bacillus subtilis BIOTECH 1679 was assessed' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="E49" s="46" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F49" s="46" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C50" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>Results indicated that Bacillus subtilis formulation (9.0 x 10⁸ CFU/mL) of 10 g/L (T1), 30 g/L (T2), and 50 g/L (T3) concentrations exhibited a notable increase in plant growth parameters.</t>
-        </is>
-      </c>
-      <c r="F6" s="31" t="inlineStr">
-        <is>
-          <t>indicated</t>
-        </is>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>[AMB] Factive reporting: 'Results indicated that... exhibited a notable increase' — synonym for 'showed', reports results as settled fact. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D50" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F50" s="45" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C51" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>In the antibacterial testing, the paper disc diffusion method is used in order to indicate the zone of inhibition in the evaluation of Antibacterial potential of Balitbitan on Mueller Hinton Agar.</t>
-        </is>
-      </c>
-      <c r="F7" s="29" t="inlineStr">
-        <is>
-          <t>indicate</t>
-        </is>
-      </c>
-      <c r="G7" s="30" t="inlineStr">
-        <is>
-          <t>FP-Proc</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>Procedural: 'the paper disc diffusion method is used in order to indicate the zone of inhibition' describes what the method does procedurally, not pointing to a location in a table/figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="D51" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="46" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F51" s="46" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="45" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C52" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>In the antibacterial testing, the paper disc diffusion method is used in order to indicate the zone of inhibition in the evaluation of Antibacterial potential of Balitbitan on Mueller Hinton Agar.</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming: 'evaluation of Antibacterial potential of Balitbitan' names the research topic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D52" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="45" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F52" s="45" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C53" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D53" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F53" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="45" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D54" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="45" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F54" s="45" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="B55" s="46" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C55" s="46" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>This study evaluated the acute toxicity and antitussive activity of Mimosa pudica (Makahiya) ethanolic extract in ICR mice to assess its safety and potential as a natural antitussive agent or cough suppressant.</t>
-        </is>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'to assess its safety and potential as a natural antitussive agent' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F55" s="46" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="45" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="C56" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D56" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F56" s="45" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="C57" s="46" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F57" s="46" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="45" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="C58" s="45" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D58" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="45" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F58" s="45" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="C59" s="46" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D59" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>No mortality, distress, or significant weight changes were observed, indicating that Mimosa pudica extract is non-toxic up to 2000 mg/kg.</t>
-        </is>
-      </c>
-      <c r="F10" s="31" t="inlineStr">
-        <is>
-          <t>indicating</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>Operational restatement: 'no mortality... indicating non-toxic' — non-toxicity is the operational definition of no adverse effects in an acute toxicity design, not an inference beyond the measurement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F59" s="46" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="45" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="C60" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>Further studies are recommended to confirm its long-term safety, refine dosing, and better understand its mechanisms of action.</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="G11" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'Further studies are recommended to confirm' prescribes action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="D60" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F60" s="45" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="C61" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>In the current study, the antibacterial and antioxidant potential of Copper oxide nanoparticles (CuO NPs) were evaluated.</t>
-        </is>
-      </c>
-      <c r="F12" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G12" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'the antibacterial and antioxidant potential of Copper oxide nanoparticles (CuO NPs) were evaluated' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="D61" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F61" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="45" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C62" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>Moreover, using growth-kinetic assay, antibacterial activities of the different concentrations of CuO NPs were determined and found to be statistically significantly different (p &lt;0.05) from each other for the Staphylococcus aureus, Salmonella enterica serovar Typhimurium, Shigella sp., and Bacillus cereus, indicating a dose-dependent response.</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>indicating</t>
-        </is>
-      </c>
-      <c r="G13" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>Factive (operational definition): 'statistically significantly different... indicating a dose-dependent response' — dose-dependency is the operational interpretation of significant differences between concentrations, not a hedged inference. Per indicating rule: restates operational meaning = factive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="D62" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F62" s="45" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="C63" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D63" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>The study would be on developing and optimizing eco-bricks using a mixture of SUPs and UCO developed through trial and error.</t>
-        </is>
-      </c>
-      <c r="F14" s="31" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t>General (grammatical scaffolding): 'The study would be on developing...' required by sentence structure, not epistemic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F63" s="46" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="45" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>Therefore, further research will aid in underlining the importance of optimizing the ingredient ratios to acquire desirable quality eco-bricks for sustainable construction applications.</t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="G15" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>General (future procedure): 'further research will aid in underlining' — future procedure, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="D64" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="45" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F64" s="45" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C65" s="46" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D65" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>The study generally aimed to evaluate the embryo toxicity, lethality, and teratogenicity of Ziziphus talanai-infused nanozeolite pellets on Danio rerio was performed at the Biology and Chemistry Laboratory of Pampanga State Agricultural University from October 2023 to January 2024.</t>
-        </is>
-      </c>
-      <c r="F16" s="31" t="inlineStr">
-        <is>
-          <t>generally</t>
-        </is>
-      </c>
-      <c r="G16" s="32" t="inlineStr">
-        <is>
-          <t>FP-Proc</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>Procedural norm: 'The study generally aimed to evaluate' describes the framing of the aim, not a claim's scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>The antibacterial potential of fungus-mediated AgNPs was distinguished by performing the agar well diffusion method and determining minimum bactericidal concentration (MBC) and minimum inhibitory concentration (MIC) via resazurin and MTT assays.</t>
-        </is>
-      </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G17" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (methods): 'The antibacterial potential of fungus-mediated AgNPs was distinguished by performing the agar well diffusion method' names the research object being measured, parallel to aim-sentence topic-naming. Codebook rule applied consistently across aim and methods sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>This study aimed to identify the histoprotective potential of Balakat extract (Ziziphus talanai) against monosodium glutamate effect to the specific vital organs of Mus musculus through observing the lesions / aberrations to the heart, liver and kidney.</t>
-        </is>
-      </c>
-      <c r="F18" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G18" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'This study aimed to identify the histoprotective potential of Balakat extract' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>In terms of practices, proper waste management should be established to avoid the high danger of heavy metal contamination.</t>
-        </is>
-      </c>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="G19" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'proper waste management should be established' — deontic prescription, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>As a result, some community or local government-adopted measures are proposed.</t>
-        </is>
-      </c>
-      <c r="F20" s="31" t="inlineStr">
-        <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="G20" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>General (describes an output, not a claim): 'some community or local government-adopted measures are proposed' names the study's output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>Overall, the combination of Ziehl-Neelsen staining, biochemical testing like the catalase test, and evaluating growth in the presence of the Salt Tolerance Test provides a comprehensive approach for diagnosing and studying mycobacteriosis in cultivated milkfish, offering insights that can guide effective management strategies to control the spread of this disease in aquaculture system.</t>
-        </is>
-      </c>
-      <c r="F21" s="31" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G21" s="32" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H21" s="23" t="inlineStr">
-        <is>
-          <t>Capability: 'insights that can guide effective management strategies' describes inherent ability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Results also showed that the antibacterial property of Bangkok Kalachuchi (Adenium obesum) against Staphylococcus aureus (ATCC 25923) are significantly different at various concentration indicating that its antibacterial property is dose dependent.</t>
-        </is>
-      </c>
-      <c r="F22" s="31" t="inlineStr">
-        <is>
-          <t>indicating</t>
-        </is>
-      </c>
-      <c r="G22" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H22" s="23" t="inlineStr">
-        <is>
-          <t>Factive (operational definition): 'significantly different at various concentration indicating that its antibacterial property is dose dependent' — dose-dependency is the operational interpretation of significant differences between concentrations. Per indicating rule: restates operational meaning = factive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>The present study conducted an experiment to determine the antifungal potential of paragis leaf extracts against Colletotrichum species.</t>
-        </is>
-      </c>
-      <c r="F23" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G23" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'antifungal potential of paragis leaf extracts' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Paper disc diffusion assay was done using crude ethanolic leaf extract in different concentrations and extraction techniques, Kupchan Partitioning Method (Polar, Semi-polar, Non-polar fractions), and ethanolic crude in boiled, and not boiled treatments in determining its antifungal potential.</t>
-        </is>
-      </c>
-      <c r="F24" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G24" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (methods): 'in determining its antifungal potential' names the research object being measured, parallel to the aim-sentence topic-naming rule. Same code applied regardless of sentence type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>The findings of this study showed and suggests that the extraction efficiency favors the highly polar solvents than the non-polar solvents in determining the antifungal potential of E. indica against Colletotrichum spp..</t>
-        </is>
-      </c>
-      <c r="F25" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G25" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (methods): 'determining the antifungal potential of E. indica against Colletotrichum spp.' names the research object being measured, parallel to the aim-sentence topic-naming rule. Same code applied regardless of sentence type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>The biodegradable plate developed exhibited the following properties: Bamboo fiber plates (T1) and bamboo fiber plates coated with aloe vera (T2) degrade faster than styrofoam and silver foil plates; Bamboo fiber plates coated with aloe vera (T2) showcased the highest tensile strength compared to other treatments Bamboo fiber plates (T1) and bamboo fiber plates coated with aloe vera (T2) uptake more water than styrofoam and silver foil paper plates; The significant differences in melting temperature indicate variations in thermal stability among the different plate materials.</t>
-        </is>
-      </c>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>indicate</t>
-        </is>
-      </c>
-      <c r="G26" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H26" s="23" t="inlineStr">
-        <is>
-          <t>[AMB] Factive reporting: 'significant differences in melting temperature indicate variations in thermal stability' — direct logical entailment from statistical significance, not a hedged inference. Per Decision Rules: synonym for showed/demonstrated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>MRSA bacteria can survive long on surfaces and objects, including second-hand clothing (SHC).</t>
-        </is>
-      </c>
-      <c r="F27" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>Capability: 'MRSA bacteria can survive long on surfaces' describes inherent ability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>This study aimed to assess the phytochemical composition, antioxidant potential, and antibacterial activity of P. propinquum fruit ethanolic extract using Thin Layer Chromatography (TLC)-based techniques.</t>
-        </is>
-      </c>
-      <c r="F28" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G28" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'assess the phytochemical composition, antioxidant potential, and antibacterial activity of P. propinquum' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>The TLC-DPPH assay demonstrated notable antioxidant activity, as indicated by the reduction of DPPH radicals.</t>
-        </is>
-      </c>
-      <c r="F29" s="31" t="inlineStr">
-        <is>
-          <t>indicated</t>
-        </is>
-      </c>
-      <c r="G29" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>Evidential pointer: 'notable antioxidant activity, as indicated by the reduction of DPPH radicals' — points to evidence for a claim already asserted, not uncertainty about the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>Further studies should focus on the isolation and characterization of its active compounds, their mechanisms of action, and their potential pharmaceutical applications.</t>
-        </is>
-      </c>
-      <c r="F30" s="29" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="G30" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'Further studies should focus on the isolation and characterization' — deontic prescription, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>Further studies should focus on the isolation and characterization of its active compounds, their mechanisms of action, and their potential pharmaceutical applications.</t>
-        </is>
-      </c>
-      <c r="F31" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G31" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (recommendation-embedded): 'their potential pharmaceutical applications' is the object of a future-research recommendation, not a hedged claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>Hence, sustainable planning and management approaches should be considered.</t>
-        </is>
-      </c>
-      <c r="F32" s="29" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'sustainable planning and management approaches should be considered' — deontic prescription, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>Thus, local government should address the possible negative impacts of tourism activities and manage the carrying capacity for sustainable tourism.</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="G33" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'local government should address the possible negative impacts of tourism activities' — deontic prescription, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>Therefore, this study aims to examine the potential of Trichoderma harzianum, an endophytic fungus, as a biocontrol agent for Cercospora leaf spot-on eggplants in the Philippines.</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G34" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'this study aims to examine the potential of Trichoderma harzianum' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>Hence, the study aimed to investigate the antagonistic potential of Trichoderma harzianum among the four isolates.</t>
-        </is>
-      </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G35" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H35" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'the study aimed to investigate the antagonistic potential of Trichoderma harzianum' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>The results indicate that the mean effect of Trichoderma harzianum on the test variables varied across the three days of observation.</t>
-        </is>
-      </c>
-      <c r="F36" s="29" t="inlineStr">
-        <is>
-          <t>indicate</t>
-        </is>
-      </c>
-      <c r="G36" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>[AMB] Factive reporting: 'The results indicate that the mean effect... varied' — factive reporting of a statistical outcome, synonym for 'showed'. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>VM3</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>The findings suggests the need for assessment of knowledge, attitudes and practices of retail egg vendors about food safety and regular antimicrobial resistance monitoring on retail eggs.</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>suggests</t>
-        </is>
-      </c>
-      <c r="G37" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'The findings suggests the need for assessment of knowledge, attitudes and practices' prescribes action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>VM4</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>These findings suggest the need to improve training, regulation of milk storage, and the enforcement of labeling and sanitation standards to improve public health safety in the milk supply chain.</t>
-        </is>
-      </c>
-      <c r="F38" s="29" t="inlineStr">
-        <is>
-          <t>suggest</t>
-        </is>
-      </c>
-      <c r="G38" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'These findings suggest the need to improve training, regulation of milk storage...' prescribes action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>VM5</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>This study explores the potential antifungal properties of Muntingia calabura L. methanolic leaf extracts against Trichophyton mentagrophytes, a dermatophyte species.</t>
-        </is>
-      </c>
-      <c r="F39" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G39" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H39" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'potential antifungal properties of Muntingia calabura L.' names the research object.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>VM7</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>These measures can collectively contribute to the effective management and prevention of heartworm disease in the local canine population.</t>
-        </is>
-      </c>
-      <c r="F40" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G40" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H40" s="21" t="inlineStr">
-        <is>
-          <t>General (recommendation-embedded): 'These measures can collectively contribute to...' follows a list of recommendations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>VM7</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E41" s="22" t="inlineStr">
-        <is>
-          <t>Further research with larger sample sizes and diverse populations is needed to validate these findings and enhance our understanding of heartworm infection in the study area.</t>
-        </is>
-      </c>
-      <c r="F41" s="31" t="inlineStr">
-        <is>
-          <t>needed</t>
-        </is>
-      </c>
-      <c r="G41" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'Further research... is needed to validate these findings' prescribes action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>VM9</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="E42" s="22" t="inlineStr">
-        <is>
-          <t>To reduce microplastic pollution, the findings recommend removing the shrimp’s GIT during preparation to avoid ingestion, use fishing gear made from durable or natural materials, regularly maintain and replace worn equipment, and properly dispose of plastics instead of discarding them into water bodies.</t>
-        </is>
-      </c>
-      <c r="F42" s="31" t="inlineStr">
-        <is>
-          <t>recommend</t>
-        </is>
-      </c>
-      <c r="G42" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H42" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'the findings recommend removing the shrimp's GIT during preparation' prescribes action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>VM11</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>The stray cats’ hematological profiles were compared to normal parameters to assess their health status and whether they had the possibility of any underlying diseases based on the blood profiling.</t>
-        </is>
-      </c>
-      <c r="F43" s="29" t="inlineStr">
-        <is>
-          <t>possibility</t>
-        </is>
-      </c>
-      <c r="G43" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H43" s="21" t="inlineStr">
-        <is>
-          <t>Topic-naming (aim): 'whether they had the possibility of any underlying diseases' names the research object being investigated. Per extended rule: possibility + noun in aim/methods sentences = topic-naming, same as potential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>VM12</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E44" s="22" t="inlineStr">
-        <is>
-          <t>Nevertheless, it is recommended to consider monitoring and surveillance of ASF at the market level, and maintain and continue the strict implementation of collaborative efforts to effectively and efficiently prevent and control the further entry and spread of ASF from farm to farm.</t>
-        </is>
-      </c>
-      <c r="F44" s="31" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="G44" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H44" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'it is recommended to consider monitoring and surveillance of ASF at the market level'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>VM14</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>Multiple regression analysis indicated that knowledge significantly predicted self-assessed awareness, while personal experience did not.</t>
-        </is>
-      </c>
-      <c r="F45" s="29" t="inlineStr">
-        <is>
-          <t>indicated</t>
-        </is>
-      </c>
-      <c r="G45" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H45" s="21" t="inlineStr">
-        <is>
-          <t>[AMB] Factive reporting: 'Multiple regression analysis indicated that knowledge significantly predicted self-assessed awareness' — factive reporting of regression output, synonym for 'showed'. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>VM15</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E46" s="22" t="inlineStr">
-        <is>
-          <t>The anti-cancer potential of the extract was determined using a brine shrimp lethality assay, and after three and six hours of exposure, the surviving brine shrimps were counted.</t>
-        </is>
-      </c>
-      <c r="F46" s="31" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="G46" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H46" s="23" t="inlineStr">
-        <is>
-          <t>Topic-naming (methods): 'The anti-cancer potential of the extract was determined using a brine shrimp lethality assay' names the research object being measured, parallel to aim-sentence topic-naming. Codebook rule applied consistently across aim and methods sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>VM18</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>Zoonotic diseases are a significant public health concern, particularly those that can be transmitted from dogs to humans.</t>
-        </is>
-      </c>
-      <c r="F47" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G47" s="30" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H47" s="21" t="inlineStr">
-        <is>
-          <t>Capability: 'Zoonotic diseases... particularly those that can be transmitted from dogs to humans' describes inherent property.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>VM20</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E48" s="22" t="inlineStr">
-        <is>
-          <t>Strengthening policies on pet vaccination programs and implementing stricter guidelines for pet care are recommended to mitigate rabies transmission risks.</t>
-        </is>
-      </c>
-      <c r="F48" s="31" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="G48" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H48" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'stricter guidelines for pet care are recommended to mitigate rabies transmission risks'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Acs1</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>These findings suggest that fermented banana peel, when applied at an optimal rate in combination with reduced synthetic fertilizer input, can significantly enhance the growth and yield performance of finger pepper, offering a sustainable alternative for crop production.</t>
-        </is>
-      </c>
-      <c r="F49" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G49" s="30" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H49" s="21" t="inlineStr">
-        <is>
-          <t>[AMB] Capability: 'can significantly enhance' — can + active content verb (enhance) describing a treatment effect. Per Decision Rules: can + enhance/promote/reduce/help = capability regardless of clause embedding. Working Test: remove 'can' alone, 'suggests that... significantly enhances' remains fully hedged by 'suggests.'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Acs2</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="22" t="inlineStr">
-        <is>
-          <t>Further research could unveil additional insights and applications for optimizing plant health.</t>
-        </is>
-      </c>
-      <c r="F50" s="31" t="inlineStr">
-        <is>
-          <t>could</t>
-        </is>
-      </c>
-      <c r="G50" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H50" s="23" t="inlineStr">
-        <is>
-          <t>Future research framing: 'Further research could unveil additional insights and applications' — the modal scopes over the feasibility of a future research activity, not over the truth value of a present claim. Same rule as Aas8 'Further research can explore'. Per codebook: epistemic hedges concern claim uncertainty, not research possibility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Acs3</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>Most can survive the water treatment application but may not establish roots and die after several days.</t>
-        </is>
-      </c>
-      <c r="F51" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G51" s="30" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H51" s="21" t="inlineStr">
-        <is>
-          <t>Capability: 'Most can survive the water treatment application' describes inherent ability of cuttings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Acs4</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>However, the negative control can reduce production cost and provide the highest return on investment.</t>
-        </is>
-      </c>
-      <c r="F52" s="31" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G52" s="32" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H52" s="23" t="inlineStr">
-        <is>
-          <t>Capability: 'the negative control can reduce production cost' — describes the inherent ability of a specific treatment, not epistemic possibility. Swap with 'is able to' and meaning holds. Per codebook: capability 'can' = FP-Cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Acs6</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>Treatment 3 (Carbonized Rice Hull) showed moderate growth improvement, while Treatments 1 (Topsoil only) and 5 (Biochar) performed poorly in most parameters, indicating limited benefits.</t>
-        </is>
-      </c>
-      <c r="F53" s="29" t="inlineStr">
-        <is>
-          <t>indicating</t>
-        </is>
-      </c>
-      <c r="G53" s="30" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H53" s="21" t="inlineStr">
-        <is>
-          <t>Operational restatement: 'performed poorly... indicating limited benefits' — limited benefit is near-tautological with poor performance, not an inference beyond the measurement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Acs8</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" s="22" t="inlineStr">
-        <is>
-          <t>The researcher recommends foliar and drenching application of kuhol amino acid. because, numerically, it consistently produced the highest yield performance.</t>
-        </is>
-      </c>
-      <c r="F54" s="31" t="inlineStr">
-        <is>
-          <t>recommends</t>
-        </is>
-      </c>
-      <c r="G54" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H54" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'The researcher recommends foliar and drenching application of kuhol amino acid'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Aas3</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>It can also be concluded that D1 rice bran mixed with water spinach and with golden apple snail used in the study can help minimize the cost of production, specifically the feed cost.</t>
-        </is>
-      </c>
-      <c r="F55" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G55" s="30" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H55" s="21" t="inlineStr">
-        <is>
-          <t>Capability: 'golden apple snail used in the study can help minimize the cost of production' describes inherent ability. Capability substitution test: 'is able to help' preserves meaning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Aas5</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="22" t="inlineStr">
-        <is>
-          <t>In order to meet the demand for highly nutritious animal food, the future will drive animal production systems to find new sources of high-quality and sustainable protein feed raw materials.</t>
-        </is>
-      </c>
-      <c r="F56" s="31" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="G56" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H56" s="23" t="inlineStr">
-        <is>
-          <t>General (future procedure): 'the future will drive animal production systems to find new sources' — future procedure, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="22" t="inlineStr">
-        <is>
-          <t>However, T1 exhibited the lowest feed conversion ratio (FCR) and mortality rate, indicating superior feed efficiency and improved survivability to T2.</t>
-        </is>
-      </c>
-      <c r="F57" s="31" t="inlineStr">
-        <is>
-          <t>indicating</t>
-        </is>
-      </c>
-      <c r="G57" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t>Operational restatement: 'lowest FCR... indicating superior feed efficiency' — lower feed conversion ratio is the definitional measure of superior feed efficiency in animal nutrition, not an inference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E58" s="18" t="inlineStr">
-        <is>
-          <t>Based on the results of the study, it is recommended to feed mallard ducks with 75% rice porridge and 25% fish entrails during brooding stage at day 1 to day 21 for enhancing weight gain and achieving higher final weights in mallard ducks.</t>
-        </is>
-      </c>
-      <c r="F58" s="29" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="G58" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H58" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'it is recommended to feed mallard ducks with 75% rice porridge and 25% fish entrails'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E59" s="22" t="inlineStr">
-        <is>
-          <t>Further research can explore the long-term effects and cost-effectiveness of these treatments and their impact on meat quality and reproductive performance.</t>
-        </is>
-      </c>
-      <c r="F59" s="31" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G59" s="32" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="H59" s="23" t="inlineStr">
-        <is>
-          <t>General (future research statement): 'Further research can explore the long-term effects and cost-effectiveness' — future research framing, not hedge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>Aas9</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>Therefore, it is recommended for future researchers to add Diatomaceous earth and neem tree extract and check the humidity.</t>
-        </is>
-      </c>
-      <c r="F60" s="29" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="G60" s="30" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H60" s="21" t="inlineStr">
-        <is>
-          <t>Recommendation: 'it is recommended for future researchers to add Diatomaceous earth and neem tree extract'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Aas10</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E61" s="22" t="inlineStr">
-        <is>
-          <t>The researchers still recommended incorporating 50% Guinea grass + 20% Azolla + 30% concentrates for rabbit growth performance, considering the results show that this treatment performs well and doesn't differ from treatment 1, which is the farmer practice.</t>
-        </is>
-      </c>
-      <c r="F61" s="31" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="G61" s="32" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="H61" s="23" t="inlineStr">
-        <is>
-          <t>Recommendation: 'The researchers still recommended incorporating 50% Guinea grass + 20% Azolla + 30% concentrates for rabbit growth performance'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Aas10</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E62" s="18" t="inlineStr">
-        <is>
-          <t>The researchers also saw that the treatment of 50% Guinea grass + 20% Azolla + 30% concentrates has potential as an alternative feed ration for rabbits without adverse effects, and considering that azolla can help breeders to lessen the feed cost in production.</t>
-        </is>
-      </c>
-      <c r="F62" s="29" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="H62" s="21" t="inlineStr">
-        <is>
-          <t>Capability: 'azolla can help breeders to lessen the feed cost' describes inherent ability. Capability substitution test: 'is able to help' preserves meaning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1"/>
-    <row r="64" ht="45" customHeight="1"/>
-    <row r="65" ht="45" customHeight="1"/>
-    <row r="66" ht="45" customHeight="1"/>
-    <row r="67" ht="45" customHeight="1"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F65" s="46" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="B66" s="46" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
+      <c r="E66" s="46" t="n"/>
+      <c r="F66" s="46" t="n"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="B67" s="46" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
+      <c r="E67" s="46" t="n"/>
+      <c r="F67" s="46" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:H44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Final Coding Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Final coded output for the 60-abstract PSAU corpus, coded per the Hedging Codebook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Corpus-Level Totals</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Total abstracts</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Total words</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="36" t="n">
-        <v>13869</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Total hedges (Layer 1 + Layer 2)</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>Total false positives (rejected candidates)</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="36" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Total unhedged assertion sites (Layer 3)</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>Hedge density (per 100 words)</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Zero-hedge abstracts</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Breakdown by Discipline</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Discipline</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Abstracts</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Total Words</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Hedges</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>False Positives</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Unhedged Sites</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Hedges per 100 Words</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>4300</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>4509</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>5060</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>13869</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Hedge Type Breakdown (Layer 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Layer 1 Type</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Fill Color</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>% of Hedges</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Modal Verbs</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>32.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr"/>
-      <c r="D26" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>63.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Adverbial Hedges</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Clause-Level Hedges</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>False Positive Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>FP Code</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Capability: describes what something is able to do, not uncertainty</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Recommendation: prescribes what should be done, not uncertainty about a claim</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>FP-Proc</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Procedural norm: describes routine/standard procedure, not uncertainty</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>FP-Loc</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Location: 'appears in Table/Figure...'</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>General exclusion: topic-naming, evidential pointer, grammatical scaffolding, etc.</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Layer 3 — Unhedged Assertion Site Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Subtype</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>[R]</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Result Claim: finding stated as settled fact</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>[G]</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Generalization: broader inference beyond the data</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>[C]</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Causal Claim: cause-and-effect link stated as established</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12068,4 +11543,529 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Final Coding Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Final coded output for the 60-abstract PSAU corpus, coded per the Hedging Codebook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Corpus-Level Totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Total abstracts</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Total words</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="36" t="n">
+        <v>13869</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Total hedges (Layer 1 + Layer 2)</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Total false positives (rejected candidates)</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="36" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Total unhedged assertion sites (Layer 3)</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Hedge density (per 100 words)</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Zero-hedge abstracts</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Breakdown by Discipline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Abstracts</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Total Words</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Hedges</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>False Positives</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Unhedged Sites</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Hedges per 100 Words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4300</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4509</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5060</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>13869</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Hedge Type Breakdown (Layer 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Layer 1 Type</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Fill Color</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>% of Hedges</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
+      <c r="D25" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr"/>
+      <c r="D26" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>63.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Adverbial Hedges</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Clause-Level Hedges</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>False Positive Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>FP Code</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Capability: describes what something is able to do, not uncertainty</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Recommendation: prescribes what should be done, not uncertainty about a claim</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>FP-Proc</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Procedural norm: describes routine/standard procedure, not uncertainty</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>FP-Loc</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Location: 'appears in Table/Figure...'</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>General exclusion: topic-naming, evidential pointer, grammatical scaffolding, etc.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 3 — Unhedged Assertion Site Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Subtype</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>[R]</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Result Claim: finding stated as settled fact</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>[G]</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Generalization: broader inference beyond the data</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>[C]</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Causal Claim: cause-and-effect link stated as established</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +130,13 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font/>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="008C8A84"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -207,7 +214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -259,11 +266,12 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -346,6 +354,22 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2784,6 +2808,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="48" t="inlineStr">
+        <is>
+          <t>Confirmed Layer 1 type + Layer 2 function codes for all retained hedges (n=65 tokens).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -5654,6 +5685,13 @@
       <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Rejected Hedge Candidates — False Positives</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="48" t="inlineStr">
+        <is>
+          <t>False-positive hedge candidates rejected under the Working Test, with reason codes.</t>
         </is>
       </c>
     </row>
@@ -7760,6 +7798,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="48" t="inlineStr">
+        <is>
+          <t>Layer 3 optional unhedged assertion sites [R]/[G]/[C] (corpus-wide).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -9103,7 +9148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F67"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9114,1468 +9159,1959 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="n"/>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
+      <c r="L1" s="49" t="n"/>
+    </row>
     <row r="2">
-      <c r="B2" s="17" t="inlineStr">
+      <c r="A2" s="49" t="n"/>
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>Outcome Type Coding — PSAU Corpus (60 abstracts)</t>
         </is>
       </c>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="43" t="inlineStr">
+      <c r="A3" s="49" t="n"/>
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>Coded from abstract results language. Categories: Binary · Continuous · Mixed · Null/NS · Other. One row per abstract.</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="49" t="n"/>
+      <c r="K3" s="49" t="n"/>
+      <c r="L3" s="49" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="49" t="n"/>
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>Abstract ID</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D4" s="52" t="inlineStr">
         <is>
           <t>Hedges</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E4" s="52" t="inlineStr">
         <is>
           <t>Outcome Type</t>
         </is>
       </c>
-      <c r="F5" s="44" t="inlineStr">
+      <c r="F4" s="52" t="inlineStr">
         <is>
           <t>Coder Notes</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="45" t="inlineStr">
+      <c r="G4" s="49" t="n"/>
+      <c r="H4" s="49" t="n"/>
+      <c r="I4" s="49" t="n"/>
+      <c r="J4" s="49" t="n"/>
+      <c r="K4" s="49" t="n"/>
+      <c r="L4" s="49" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="49" t="n"/>
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>Acs1</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D5" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="45" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F6" s="45" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="46" t="inlineStr">
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="49" t="n"/>
+      <c r="I5" s="49" t="n"/>
+      <c r="J5" s="49" t="n"/>
+      <c r="K5" s="49" t="n"/>
+      <c r="L5" s="49" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="49" t="n"/>
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>Acs10</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
+      <c r="D6" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E6" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F7" s="46" t="inlineStr">
+      <c r="F6" s="54" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="45" t="inlineStr">
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="49" t="n"/>
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>Acs2</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D7" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="45" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F8" s="45" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="46" t="inlineStr">
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="49" t="n"/>
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>Acs3</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D9" s="46" t="n">
+      <c r="D8" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E8" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F9" s="46" t="inlineStr">
+      <c r="F8" s="54" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="49" t="n"/>
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>Acs4</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D9" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="45" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F10" s="45" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="46" t="inlineStr">
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="49" t="n"/>
+      <c r="I9" s="49" t="n"/>
+      <c r="J9" s="49" t="n"/>
+      <c r="K9" s="49" t="n"/>
+      <c r="L9" s="49" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>Acs5</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
+      <c r="D10" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E10" s="54" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F10" s="54" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="45" t="inlineStr">
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="n"/>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="49" t="n"/>
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>Acs6</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D11" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="45" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F12" s="45" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="46" t="inlineStr">
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="49" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="49" t="n"/>
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>Acs7</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C12" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D12" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E12" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F13" s="46" t="inlineStr">
+      <c r="F12" s="54" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="45" t="inlineStr">
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="49" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="49" t="n"/>
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>Acs8</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D13" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="45" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F14" s="45" t="inlineStr">
+      <c r="F13" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="46" t="inlineStr">
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="49" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="49" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>Acs9</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D15" s="46" t="n">
+      <c r="D14" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="46" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F15" s="46" t="inlineStr">
+      <c r="F14" s="54" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="45" t="inlineStr">
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="49" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="49" t="n"/>
+      <c r="B15" s="53" t="inlineStr">
         <is>
           <t>Aas1</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
+      <c r="C15" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="D15" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="45" t="inlineStr">
+      <c r="E15" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F16" s="45" t="inlineStr">
+      <c r="F15" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="46" t="inlineStr">
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="49" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="49" t="n"/>
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>Aas10</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C16" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D17" s="46" t="n">
+      <c r="D16" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="46" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F17" s="46" t="inlineStr">
+      <c r="F16" s="54" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="45" t="inlineStr">
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="49" t="n"/>
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>Aas2</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D18" s="45" t="n">
+      <c r="D17" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="45" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F18" s="45" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="46" t="inlineStr">
+      <c r="F17" s="53" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="49" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="49" t="n"/>
+      <c r="B18" s="54" t="inlineStr">
         <is>
           <t>Aas3</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C18" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D18" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="46" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F19" s="46" t="inlineStr">
+      <c r="F18" s="54" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="49" t="n"/>
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>Aas4</t>
         </is>
       </c>
-      <c r="C20" s="45" t="inlineStr">
+      <c r="C19" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D19" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="45" t="inlineStr">
+      <c r="E19" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F20" s="45" t="inlineStr">
+      <c r="F19" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="46" t="inlineStr">
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="49" t="n"/>
+      <c r="B20" s="54" t="inlineStr">
         <is>
           <t>Aas5</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C20" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
+      <c r="D20" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="46" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F21" s="46" t="inlineStr">
+      <c r="F20" s="54" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="45" t="inlineStr">
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="49" t="n"/>
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>Aas6</t>
         </is>
       </c>
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D22" s="45" t="n">
+      <c r="D21" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="45" t="inlineStr">
+      <c r="E21" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F22" s="45" t="inlineStr">
+      <c r="F21" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="46" t="inlineStr">
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="49" t="n"/>
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Aas7</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C22" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D22" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="46" t="inlineStr">
+      <c r="E22" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F23" s="46" t="inlineStr">
+      <c r="F22" s="54" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="45" t="inlineStr">
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="49" t="n"/>
+      <c r="B23" s="53" t="inlineStr">
         <is>
           <t>Aas8</t>
         </is>
       </c>
-      <c r="C24" s="45" t="inlineStr">
+      <c r="C23" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D24" s="45" t="n">
+      <c r="D23" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="45" t="inlineStr">
+      <c r="E23" s="53" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F24" s="45" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="46" t="inlineStr">
+      <c r="F23" s="53" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="49" t="n"/>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="49" t="n"/>
+      <c r="B24" s="54" t="inlineStr">
         <is>
           <t>Aas9</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C24" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D25" s="46" t="n">
+      <c r="D24" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="46" t="inlineStr">
+      <c r="E24" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F25" s="46" t="inlineStr">
+      <c r="F24" s="54" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="45" t="inlineStr">
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="49" t="n"/>
+      <c r="K24" s="49" t="n"/>
+      <c r="L24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="49" t="n"/>
+      <c r="B25" s="53" t="inlineStr">
         <is>
           <t>VM1</t>
         </is>
       </c>
-      <c r="C26" s="45" t="inlineStr">
+      <c r="C25" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D26" s="45" t="n">
+      <c r="D25" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="45" t="inlineStr">
+      <c r="E25" s="53" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F26" s="45" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="46" t="inlineStr">
+      <c r="F25" s="53" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="49" t="n"/>
+      <c r="K25" s="49" t="n"/>
+      <c r="L25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>VM2</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C26" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D26" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="46" t="inlineStr">
+      <c r="E26" s="54" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F27" s="46" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="45" t="inlineStr">
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49" t="n"/>
+      <c r="K26" s="49" t="n"/>
+      <c r="L26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="49" t="n"/>
+      <c r="B27" s="53" t="inlineStr">
         <is>
           <t>VM3</t>
         </is>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C27" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n">
+      <c r="D27" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="45" t="inlineStr">
+      <c r="E27" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F28" s="45" t="inlineStr">
+      <c r="F27" s="53" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="46" t="inlineStr">
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="49" t="n"/>
+      <c r="K27" s="49" t="n"/>
+      <c r="L27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="49" t="n"/>
+      <c r="B28" s="54" t="inlineStr">
         <is>
           <t>VM4</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C28" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D28" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="46" t="inlineStr">
+      <c r="E28" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F29" s="46" t="inlineStr">
+      <c r="F28" s="54" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="45" t="inlineStr">
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="49" t="n"/>
+      <c r="K28" s="49" t="n"/>
+      <c r="L28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="49" t="n"/>
+      <c r="B29" s="53" t="inlineStr">
         <is>
           <t>VM5</t>
         </is>
       </c>
-      <c r="C30" s="45" t="inlineStr">
+      <c r="C29" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D30" s="45" t="n">
+      <c r="D29" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="45" t="inlineStr">
+      <c r="E29" s="53" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F30" s="45" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="46" t="inlineStr">
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="49" t="n"/>
+      <c r="K29" s="49" t="n"/>
+      <c r="L29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="49" t="n"/>
+      <c r="B30" s="54" t="inlineStr">
         <is>
           <t>VM6</t>
         </is>
       </c>
-      <c r="C31" s="46" t="inlineStr">
+      <c r="C30" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D31" s="46" t="n">
+      <c r="D30" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="46" t="inlineStr">
+      <c r="E30" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F31" s="46" t="inlineStr">
+      <c r="F30" s="54" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="45" t="inlineStr">
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="49" t="n"/>
+      <c r="K30" s="49" t="n"/>
+      <c r="L30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="49" t="n"/>
+      <c r="B31" s="53" t="inlineStr">
         <is>
           <t>VM7</t>
         </is>
       </c>
-      <c r="C32" s="45" t="inlineStr">
+      <c r="C31" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D32" s="45" t="n">
+      <c r="D31" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="45" t="inlineStr">
+      <c r="E31" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F32" s="45" t="inlineStr">
+      <c r="F31" s="53" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="46" t="inlineStr">
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="49" t="n"/>
+      <c r="J31" s="49" t="n"/>
+      <c r="K31" s="49" t="n"/>
+      <c r="L31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="49" t="n"/>
+      <c r="B32" s="54" t="inlineStr">
         <is>
           <t>VM8</t>
         </is>
       </c>
-      <c r="C33" s="46" t="inlineStr">
+      <c r="C32" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D32" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="46" t="inlineStr">
+      <c r="E32" s="54" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F33" s="46" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="45" t="inlineStr">
+      <c r="F32" s="54" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="49" t="n"/>
+      <c r="J32" s="49" t="n"/>
+      <c r="K32" s="49" t="n"/>
+      <c r="L32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="49" t="n"/>
+      <c r="B33" s="53" t="inlineStr">
         <is>
           <t>VM9</t>
         </is>
       </c>
-      <c r="C34" s="45" t="inlineStr">
+      <c r="C33" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D34" s="45" t="n">
+      <c r="D33" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="45" t="inlineStr">
+      <c r="E33" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F34" s="45" t="inlineStr">
+      <c r="F33" s="53" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="46" t="inlineStr">
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="49" t="n"/>
+      <c r="J33" s="49" t="n"/>
+      <c r="K33" s="49" t="n"/>
+      <c r="L33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="49" t="n"/>
+      <c r="B34" s="54" t="inlineStr">
         <is>
           <t>VM10</t>
         </is>
       </c>
-      <c r="C35" s="46" t="inlineStr">
+      <c r="C34" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D34" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="46" t="inlineStr">
+      <c r="E34" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F35" s="46" t="inlineStr">
+      <c r="F34" s="54" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="45" t="inlineStr">
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="49" t="n"/>
+      <c r="J34" s="49" t="n"/>
+      <c r="K34" s="49" t="n"/>
+      <c r="L34" s="49" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="49" t="n"/>
+      <c r="B35" s="53" t="inlineStr">
         <is>
           <t>VM11</t>
         </is>
       </c>
-      <c r="C36" s="45" t="inlineStr">
+      <c r="C35" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D36" s="45" t="n">
+      <c r="D35" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="45" t="inlineStr">
+      <c r="E35" s="53" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F36" s="45" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="46" t="inlineStr">
+      <c r="F35" s="53" t="n"/>
+      <c r="G35" s="49" t="n"/>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="49" t="n"/>
+      <c r="J35" s="49" t="n"/>
+      <c r="K35" s="49" t="n"/>
+      <c r="L35" s="49" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="49" t="n"/>
+      <c r="B36" s="54" t="inlineStr">
         <is>
           <t>VM12</t>
         </is>
       </c>
-      <c r="C37" s="46" t="inlineStr">
+      <c r="C36" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D37" s="46" t="n">
+      <c r="D36" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="46" t="inlineStr">
+      <c r="E36" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F37" s="46" t="inlineStr">
+      <c r="F36" s="54" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="45" t="inlineStr">
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="49" t="n"/>
+      <c r="J36" s="49" t="n"/>
+      <c r="K36" s="49" t="n"/>
+      <c r="L36" s="49" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="49" t="n"/>
+      <c r="B37" s="53" t="inlineStr">
         <is>
           <t>VM13</t>
         </is>
       </c>
-      <c r="C38" s="45" t="inlineStr">
+      <c r="C37" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n">
+      <c r="D37" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="45" t="inlineStr">
+      <c r="E37" s="53" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F38" s="45" t="inlineStr">
+      <c r="F37" s="53" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="46" t="inlineStr">
+      <c r="G37" s="49" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="49" t="n"/>
+      <c r="J37" s="49" t="n"/>
+      <c r="K37" s="49" t="n"/>
+      <c r="L37" s="49" t="n"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="49" t="n"/>
+      <c r="B38" s="54" t="inlineStr">
         <is>
           <t>VM14</t>
         </is>
       </c>
-      <c r="C39" s="46" t="inlineStr">
+      <c r="C38" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D39" s="46" t="n">
+      <c r="D38" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="46" t="inlineStr">
+      <c r="E38" s="54" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F39" s="46" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="45" t="inlineStr">
+      <c r="F38" s="54" t="n"/>
+      <c r="G38" s="49" t="n"/>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="49" t="n"/>
+      <c r="J38" s="49" t="n"/>
+      <c r="K38" s="49" t="n"/>
+      <c r="L38" s="49" t="n"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="49" t="n"/>
+      <c r="B39" s="53" t="inlineStr">
         <is>
           <t>VM15</t>
         </is>
       </c>
-      <c r="C40" s="45" t="inlineStr">
+      <c r="C39" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D40" s="45" t="n">
+      <c r="D39" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="45" t="inlineStr">
+      <c r="E39" s="53" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F40" s="45" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="46" t="inlineStr">
+      <c r="F39" s="53" t="n"/>
+      <c r="G39" s="49" t="n"/>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="49" t="n"/>
+      <c r="J39" s="49" t="n"/>
+      <c r="K39" s="49" t="n"/>
+      <c r="L39" s="49" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="49" t="n"/>
+      <c r="B40" s="54" t="inlineStr">
         <is>
           <t>VM16</t>
         </is>
       </c>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="C40" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D41" s="46" t="n">
+      <c r="D40" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="46" t="inlineStr">
+      <c r="E40" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F41" s="46" t="inlineStr">
+      <c r="F40" s="54" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="45" t="inlineStr">
+      <c r="G40" s="49" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="49" t="n"/>
+      <c r="J40" s="49" t="n"/>
+      <c r="K40" s="49" t="n"/>
+      <c r="L40" s="49" t="n"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="49" t="n"/>
+      <c r="B41" s="53" t="inlineStr">
         <is>
           <t>VM17</t>
         </is>
       </c>
-      <c r="C42" s="45" t="inlineStr">
+      <c r="C41" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D42" s="45" t="n">
+      <c r="D41" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="45" t="inlineStr">
+      <c r="E41" s="53" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F42" s="45" t="inlineStr">
+      <c r="F41" s="53" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="46" t="inlineStr">
+      <c r="G41" s="49" t="n"/>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="49" t="n"/>
+      <c r="J41" s="49" t="n"/>
+      <c r="K41" s="49" t="n"/>
+      <c r="L41" s="49" t="n"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="49" t="n"/>
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>VM18</t>
         </is>
       </c>
-      <c r="C43" s="46" t="inlineStr">
+      <c r="C42" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D43" s="46" t="n">
+      <c r="D42" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="46" t="inlineStr">
+      <c r="E42" s="54" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F43" s="46" t="inlineStr">
+      <c r="F42" s="54" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="45" t="inlineStr">
+      <c r="G42" s="49" t="n"/>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="49" t="n"/>
+      <c r="J42" s="49" t="n"/>
+      <c r="K42" s="49" t="n"/>
+      <c r="L42" s="49" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="49" t="n"/>
+      <c r="B43" s="53" t="inlineStr">
         <is>
           <t>VM19</t>
         </is>
       </c>
-      <c r="C44" s="45" t="inlineStr">
+      <c r="C43" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D44" s="45" t="n">
+      <c r="D43" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="45" t="inlineStr">
+      <c r="E43" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F44" s="45" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="46" t="inlineStr">
+      <c r="F43" s="53" t="n"/>
+      <c r="G43" s="49" t="n"/>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="49" t="n"/>
+      <c r="J43" s="49" t="n"/>
+      <c r="K43" s="49" t="n"/>
+      <c r="L43" s="49" t="n"/>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="49" t="n"/>
+      <c r="B44" s="54" t="inlineStr">
         <is>
           <t>VM20</t>
         </is>
       </c>
-      <c r="C45" s="46" t="inlineStr">
+      <c r="C44" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D45" s="46" t="n">
+      <c r="D44" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="46" t="inlineStr">
+      <c r="E44" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F45" s="46" t="inlineStr">
+      <c r="F44" s="54" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="45" t="inlineStr">
+      <c r="G44" s="49" t="n"/>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="49" t="n"/>
+      <c r="J44" s="49" t="n"/>
+      <c r="K44" s="49" t="n"/>
+      <c r="L44" s="49" t="n"/>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="49" t="n"/>
+      <c r="B45" s="53" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="C46" s="45" t="inlineStr">
+      <c r="C45" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D46" s="45" t="n">
+      <c r="D45" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="45" t="inlineStr">
+      <c r="E45" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F46" s="45" t="inlineStr">
+      <c r="F45" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="46" t="inlineStr">
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="49" t="n"/>
+      <c r="B46" s="54" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="C47" s="46" t="inlineStr">
+      <c r="C46" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D47" s="46" t="n">
+      <c r="D46" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="46" t="inlineStr">
+      <c r="E46" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F47" s="46" t="inlineStr">
+      <c r="F46" s="54" t="inlineStr">
         <is>
           <t>no zone of inhibition / did not possess</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="45" t="inlineStr">
+      <c r="G46" s="49" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
+      <c r="J46" s="49" t="n"/>
+      <c r="K46" s="49" t="n"/>
+      <c r="L46" s="49" t="n"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="49" t="n"/>
+      <c r="B47" s="53" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="C48" s="45" t="inlineStr">
+      <c r="C47" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D48" s="45" t="n">
+      <c r="D47" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="45" t="inlineStr">
+      <c r="E47" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F48" s="45" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="46" t="inlineStr">
+      <c r="F47" s="53" t="n"/>
+      <c r="G47" s="49" t="n"/>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="49" t="n"/>
+      <c r="J47" s="49" t="n"/>
+      <c r="K47" s="49" t="n"/>
+      <c r="L47" s="49" t="n"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="49" t="n"/>
+      <c r="B48" s="54" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="C49" s="46" t="inlineStr">
+      <c r="C48" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D49" s="46" t="n">
+      <c r="D48" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="46" t="inlineStr">
+      <c r="E48" s="54" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F49" s="46" t="n"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="45" t="inlineStr">
+      <c r="F48" s="54" t="n"/>
+      <c r="G48" s="49" t="n"/>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="49" t="n"/>
+      <c r="J48" s="49" t="n"/>
+      <c r="K48" s="49" t="n"/>
+      <c r="L48" s="49" t="n"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="49" t="n"/>
+      <c r="B49" s="53" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="C50" s="45" t="inlineStr">
+      <c r="C49" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D50" s="45" t="n">
+      <c r="D49" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="45" t="inlineStr">
+      <c r="E49" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F50" s="45" t="inlineStr">
+      <c r="F49" s="53" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="46" t="inlineStr">
+      <c r="G49" s="49" t="n"/>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="49" t="n"/>
+      <c r="J49" s="49" t="n"/>
+      <c r="K49" s="49" t="n"/>
+      <c r="L49" s="49" t="n"/>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="49" t="n"/>
+      <c r="B50" s="54" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="C51" s="46" t="inlineStr">
+      <c r="C50" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D51" s="46" t="n">
+      <c r="D50" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="46" t="inlineStr">
+      <c r="E50" s="54" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F51" s="46" t="n"/>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="45" t="inlineStr">
+      <c r="F50" s="54" t="n"/>
+      <c r="G50" s="49" t="n"/>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="49" t="n"/>
+      <c r="J50" s="49" t="n"/>
+      <c r="K50" s="49" t="n"/>
+      <c r="L50" s="49" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="49" t="n"/>
+      <c r="B51" s="53" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="C52" s="45" t="inlineStr">
+      <c r="C51" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D52" s="45" t="n">
+      <c r="D51" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="E52" s="45" t="inlineStr">
+      <c r="E51" s="53" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F52" s="45" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="46" t="inlineStr">
+      <c r="F51" s="53" t="n"/>
+      <c r="G51" s="49" t="n"/>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="49" t="n"/>
+      <c r="J51" s="49" t="n"/>
+      <c r="K51" s="49" t="n"/>
+      <c r="L51" s="49" t="n"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="49" t="n"/>
+      <c r="B52" s="54" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="C53" s="46" t="inlineStr">
+      <c r="C52" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D53" s="46" t="n">
+      <c r="D52" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E53" s="46" t="inlineStr">
+      <c r="E52" s="54" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F53" s="46" t="inlineStr">
+      <c r="F52" s="54" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="B54" s="45" t="inlineStr">
+      <c r="G52" s="49" t="n"/>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="49" t="n"/>
+      <c r="J52" s="49" t="n"/>
+      <c r="K52" s="49" t="n"/>
+      <c r="L52" s="49" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="49" t="n"/>
+      <c r="B53" s="53" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="C54" s="45" t="inlineStr">
+      <c r="C53" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D54" s="45" t="n">
+      <c r="D53" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="45" t="inlineStr">
+      <c r="E53" s="53" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F54" s="45" t="inlineStr">
+      <c r="F53" s="53" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="B55" s="46" t="inlineStr">
+      <c r="G53" s="49" t="n"/>
+      <c r="H53" s="49" t="n"/>
+      <c r="I53" s="49" t="n"/>
+      <c r="J53" s="49" t="n"/>
+      <c r="K53" s="49" t="n"/>
+      <c r="L53" s="49" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="49" t="n"/>
+      <c r="B54" s="54" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="C55" s="46" t="inlineStr">
+      <c r="C54" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D55" s="46" t="n">
+      <c r="D54" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="46" t="inlineStr">
+      <c r="E54" s="54" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F55" s="46" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="B56" s="45" t="inlineStr">
+      <c r="F54" s="54" t="n"/>
+      <c r="G54" s="49" t="n"/>
+      <c r="H54" s="49" t="n"/>
+      <c r="I54" s="49" t="n"/>
+      <c r="J54" s="49" t="n"/>
+      <c r="K54" s="49" t="n"/>
+      <c r="L54" s="49" t="n"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="49" t="n"/>
+      <c r="B55" s="53" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="C56" s="45" t="inlineStr">
+      <c r="C55" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D56" s="45" t="n">
+      <c r="D55" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="45" t="inlineStr">
+      <c r="E55" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F56" s="45" t="inlineStr">
+      <c r="F55" s="53" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="B57" s="46" t="inlineStr">
+      <c r="G55" s="49" t="n"/>
+      <c r="H55" s="49" t="n"/>
+      <c r="I55" s="49" t="n"/>
+      <c r="J55" s="49" t="n"/>
+      <c r="K55" s="49" t="n"/>
+      <c r="L55" s="49" t="n"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="49" t="n"/>
+      <c r="B56" s="54" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="C57" s="46" t="inlineStr">
+      <c r="C56" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D57" s="46" t="n">
+      <c r="D56" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="46" t="inlineStr">
+      <c r="E56" s="54" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F57" s="46" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="B58" s="45" t="inlineStr">
+      <c r="F56" s="54" t="n"/>
+      <c r="G56" s="49" t="n"/>
+      <c r="H56" s="49" t="n"/>
+      <c r="I56" s="49" t="n"/>
+      <c r="J56" s="49" t="n"/>
+      <c r="K56" s="49" t="n"/>
+      <c r="L56" s="49" t="n"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="49" t="n"/>
+      <c r="B57" s="53" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="C58" s="45" t="inlineStr">
+      <c r="C57" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D58" s="45" t="n">
+      <c r="D57" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="45" t="inlineStr">
+      <c r="E57" s="53" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F58" s="45" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="B59" s="46" t="inlineStr">
+      <c r="F57" s="53" t="n"/>
+      <c r="G57" s="49" t="n"/>
+      <c r="H57" s="49" t="n"/>
+      <c r="I57" s="49" t="n"/>
+      <c r="J57" s="49" t="n"/>
+      <c r="K57" s="49" t="n"/>
+      <c r="L57" s="49" t="n"/>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="49" t="n"/>
+      <c r="B58" s="54" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="C59" s="46" t="inlineStr">
+      <c r="C58" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D59" s="46" t="n">
+      <c r="D58" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="46" t="inlineStr">
+      <c r="E58" s="54" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F59" s="46" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="45" t="inlineStr">
+      <c r="F58" s="54" t="n"/>
+      <c r="G58" s="49" t="n"/>
+      <c r="H58" s="49" t="n"/>
+      <c r="I58" s="49" t="n"/>
+      <c r="J58" s="49" t="n"/>
+      <c r="K58" s="49" t="n"/>
+      <c r="L58" s="49" t="n"/>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="49" t="n"/>
+      <c r="B59" s="53" t="inlineStr">
         <is>
           <t>B15</t>
         </is>
       </c>
-      <c r="C60" s="45" t="inlineStr">
+      <c r="C59" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D60" s="45" t="n">
+      <c r="D59" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="45" t="inlineStr">
+      <c r="E59" s="53" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F60" s="45" t="n"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="46" t="inlineStr">
+      <c r="F59" s="53" t="n"/>
+      <c r="G59" s="49" t="n"/>
+      <c r="H59" s="49" t="n"/>
+      <c r="I59" s="49" t="n"/>
+      <c r="J59" s="49" t="n"/>
+      <c r="K59" s="49" t="n"/>
+      <c r="L59" s="49" t="n"/>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="49" t="n"/>
+      <c r="B60" s="54" t="inlineStr">
         <is>
           <t>B16</t>
         </is>
       </c>
-      <c r="C61" s="46" t="inlineStr">
+      <c r="C60" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D61" s="46" t="n">
+      <c r="D60" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="E61" s="46" t="inlineStr">
+      <c r="E60" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F61" s="46" t="inlineStr">
+      <c r="F60" s="54" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="B62" s="45" t="inlineStr">
+      <c r="G60" s="49" t="n"/>
+      <c r="H60" s="49" t="n"/>
+      <c r="I60" s="49" t="n"/>
+      <c r="J60" s="49" t="n"/>
+      <c r="K60" s="49" t="n"/>
+      <c r="L60" s="49" t="n"/>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="49" t="n"/>
+      <c r="B61" s="53" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="C62" s="45" t="inlineStr">
+      <c r="C61" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D62" s="45" t="n">
+      <c r="D61" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="45" t="inlineStr">
+      <c r="E61" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F62" s="45" t="n"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="B63" s="46" t="inlineStr">
+      <c r="F61" s="53" t="n"/>
+      <c r="G61" s="49" t="n"/>
+      <c r="H61" s="49" t="n"/>
+      <c r="I61" s="49" t="n"/>
+      <c r="J61" s="49" t="n"/>
+      <c r="K61" s="49" t="n"/>
+      <c r="L61" s="49" t="n"/>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="49" t="n"/>
+      <c r="B62" s="54" t="inlineStr">
         <is>
           <t>B18</t>
         </is>
       </c>
-      <c r="C63" s="46" t="inlineStr">
+      <c r="C62" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D63" s="46" t="n">
+      <c r="D62" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="46" t="inlineStr">
+      <c r="E62" s="54" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F63" s="46" t="inlineStr">
+      <c r="F62" s="54" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="B64" s="45" t="inlineStr">
+      <c r="G62" s="49" t="n"/>
+      <c r="H62" s="49" t="n"/>
+      <c r="I62" s="49" t="n"/>
+      <c r="J62" s="49" t="n"/>
+      <c r="K62" s="49" t="n"/>
+      <c r="L62" s="49" t="n"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="49" t="n"/>
+      <c r="B63" s="53" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="C64" s="45" t="inlineStr">
+      <c r="C63" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D64" s="45" t="n">
+      <c r="D63" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="45" t="inlineStr">
+      <c r="E63" s="53" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F64" s="45" t="n"/>
+      <c r="F63" s="53" t="n"/>
+      <c r="G63" s="49" t="n"/>
+      <c r="H63" s="49" t="n"/>
+      <c r="I63" s="49" t="n"/>
+      <c r="J63" s="49" t="n"/>
+      <c r="K63" s="49" t="n"/>
+      <c r="L63" s="49" t="n"/>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="49" t="n"/>
+      <c r="B64" s="54" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C64" s="54" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D64" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="54" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F64" s="54" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G64" s="49" t="n"/>
+      <c r="H64" s="49" t="n"/>
+      <c r="I64" s="49" t="n"/>
+      <c r="J64" s="49" t="n"/>
+      <c r="K64" s="49" t="n"/>
+      <c r="L64" s="49" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="B65" s="46" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C65" s="46" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D65" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="46" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F65" s="46" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
+      <c r="A65" s="49" t="n"/>
+      <c r="B65" s="49" t="n"/>
+      <c r="C65" s="49" t="n"/>
+      <c r="D65" s="49" t="n"/>
+      <c r="E65" s="49" t="n"/>
+      <c r="F65" s="49" t="n"/>
+      <c r="G65" s="49" t="n"/>
+      <c r="H65" s="49" t="n"/>
+      <c r="I65" s="49" t="n"/>
+      <c r="J65" s="49" t="n"/>
+      <c r="K65" s="49" t="n"/>
+      <c r="L65" s="49" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
-      <c r="B66" s="46" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
-      <c r="E66" s="46" t="n"/>
-      <c r="F66" s="46" t="n"/>
+      <c r="A66" s="49" t="n"/>
+      <c r="B66" s="49" t="n"/>
+      <c r="C66" s="49" t="n"/>
+      <c r="D66" s="49" t="n"/>
+      <c r="E66" s="49" t="n"/>
+      <c r="F66" s="49" t="n"/>
+      <c r="G66" s="49" t="n"/>
+      <c r="H66" s="49" t="n"/>
+      <c r="I66" s="49" t="n"/>
+      <c r="J66" s="49" t="n"/>
+      <c r="K66" s="49" t="n"/>
+      <c r="L66" s="49" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
-      <c r="B67" s="46" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
-      <c r="E67" s="46" t="n"/>
-      <c r="F67" s="46" t="n"/>
+      <c r="A67" s="49" t="n"/>
+      <c r="B67" s="49" t="n"/>
+      <c r="C67" s="49" t="n"/>
+      <c r="D67" s="49" t="n"/>
+      <c r="E67" s="49" t="n"/>
+      <c r="F67" s="49" t="n"/>
+      <c r="G67" s="49" t="n"/>
+      <c r="H67" s="49" t="n"/>
+      <c r="I67" s="49" t="n"/>
+      <c r="J67" s="49" t="n"/>
+      <c r="K67" s="49" t="n"/>
+      <c r="L67" s="49" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10588,7 +11124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I26"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10602,943 +11138,1137 @@
     <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="49" t="n"/>
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="49" t="n"/>
+      <c r="E1" s="49" t="n"/>
+      <c r="F1" s="49" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="49" t="n"/>
+      <c r="I1" s="49" t="n"/>
+      <c r="J1" s="49" t="n"/>
+      <c r="K1" s="49" t="n"/>
+      <c r="L1" s="49" t="n"/>
+    </row>
     <row r="2">
-      <c r="B2" s="17" t="inlineStr">
+      <c r="A2" s="49" t="n"/>
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>P and DO Functions — Scan Log (Non-Hedge Inventory)</t>
         </is>
       </c>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="43" t="inlineStr">
+      <c r="A3" s="49" t="n"/>
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>Discourse-organization connectors and politeness scan across 60 abstracts. Hedge? = N for all. Not counted in Layer 1/2 totals.</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
+      <c r="I3" s="49" t="n"/>
+      <c r="J3" s="49" t="n"/>
+      <c r="K3" s="49" t="n"/>
+      <c r="L3" s="49" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="49" t="n"/>
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>Abstract ID</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D4" s="52" t="inlineStr">
         <is>
           <t>Phrase / Token</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E4" s="52" t="inlineStr">
         <is>
           <t>Context (short)</t>
         </is>
       </c>
-      <c r="F5" s="44" t="inlineStr">
+      <c r="F4" s="52" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="G5" s="44" t="inlineStr">
+      <c r="G4" s="52" t="inlineStr">
         <is>
           <t>Hedge?</t>
         </is>
       </c>
-      <c r="H5" s="44" t="inlineStr">
+      <c r="H4" s="52" t="inlineStr">
         <is>
           <t>Ambiguous</t>
         </is>
       </c>
-      <c r="I5" s="44" t="inlineStr">
+      <c r="I4" s="52" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="B6" s="45" t="inlineStr">
+      <c r="J4" s="49" t="n"/>
+      <c r="K4" s="49" t="n"/>
+      <c r="L4" s="49" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="49" t="n"/>
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Thus / Therefore</t>
         </is>
       </c>
-      <c r="E6" s="45" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>Thus, in the optimization process...; Therefore, further research will...</t>
         </is>
       </c>
-      <c r="F6" s="45" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G6" s="45" t="inlineStr">
+      <c r="G5" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H6" s="45" t="inlineStr">
+      <c r="H5" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I6" s="45" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>Move connectors (problem→method; limit→future work). Not epistemic hedges.</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="B7" s="46" t="inlineStr">
+      <c r="J5" s="49" t="n"/>
+      <c r="K5" s="49" t="n"/>
+      <c r="L5" s="49" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="49" t="n"/>
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D7" s="46" t="inlineStr">
+      <c r="D6" s="54" t="inlineStr">
         <is>
           <t>Hence / thus</t>
         </is>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E6" s="54" t="inlineStr">
         <is>
           <t>Hence, the biosynthesis is feasible; thus making a remarkable choice; thus demonstrating...</t>
         </is>
       </c>
-      <c r="F7" s="46" t="inlineStr">
+      <c r="F6" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G7" s="46" t="inlineStr">
+      <c r="G6" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H7" s="46" t="inlineStr">
+      <c r="H6" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I7" s="46" t="inlineStr">
+      <c r="I6" s="54" t="inlineStr">
         <is>
           <t>Claim-sequence connectors. Hedge if any is separate (may).</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="B8" s="45" t="inlineStr">
+      <c r="J6" s="49" t="n"/>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="49" t="n"/>
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>Thus</t>
         </is>
       </c>
-      <c r="E8" s="45" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>Thus, the researcher provided a policy proposal...</t>
         </is>
       </c>
-      <c r="F8" s="45" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G8" s="45" t="inlineStr">
+      <c r="G7" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H8" s="45" t="inlineStr">
+      <c r="H7" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I8" s="45" t="inlineStr">
+      <c r="I7" s="53" t="inlineStr">
         <is>
           <t>Results→recommendation connector.</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="B9" s="46" t="inlineStr">
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="49" t="n"/>
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D9" s="46" t="inlineStr">
+      <c r="D8" s="54" t="inlineStr">
         <is>
           <t>Hence</t>
         </is>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E8" s="54" t="inlineStr">
         <is>
           <t>Hence, this study aimed to investigate...</t>
         </is>
       </c>
-      <c r="F9" s="46" t="inlineStr">
+      <c r="F8" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G9" s="46" t="inlineStr">
+      <c r="G8" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H9" s="46" t="inlineStr">
+      <c r="H8" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I9" s="46" t="inlineStr">
+      <c r="I8" s="54" t="inlineStr">
         <is>
           <t>Background→aim connector.</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="49" t="n"/>
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>Hence</t>
         </is>
       </c>
-      <c r="E10" s="45" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>Hence, LAB have emerged as a focal point...</t>
         </is>
       </c>
-      <c r="F10" s="45" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G10" s="45" t="inlineStr">
+      <c r="G9" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H10" s="45" t="inlineStr">
+      <c r="H9" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I10" s="45" t="inlineStr">
+      <c r="I9" s="53" t="inlineStr">
         <is>
           <t>Problem→focus connector.</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="46" t="inlineStr">
+      <c r="J9" s="49" t="n"/>
+      <c r="K9" s="49" t="n"/>
+      <c r="L9" s="49" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="49" t="n"/>
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>B16</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D10" s="54" t="inlineStr">
         <is>
           <t>Thus / therefore</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E10" s="54" t="inlineStr">
         <is>
           <t>Thus, this study detected...; This study, therefore, underscores...</t>
         </is>
       </c>
-      <c r="F11" s="46" t="inlineStr">
+      <c r="F10" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G11" s="46" t="inlineStr">
+      <c r="G10" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H11" s="46" t="inlineStr">
+      <c r="H10" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I11" s="46" t="inlineStr">
+      <c r="I10" s="54" t="inlineStr">
         <is>
           <t>Rationale→aim / findings→implication connectors.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="B12" s="45" t="inlineStr">
+      <c r="J10" s="49" t="n"/>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="49" t="n"/>
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D12" s="45" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>Hence / Thus</t>
         </is>
       </c>
-      <c r="E12" s="45" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>Hence, sustainable planning should...; Thus, local government should...</t>
         </is>
       </c>
-      <c r="F12" s="45" t="inlineStr">
+      <c r="F11" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G12" s="45" t="inlineStr">
+      <c r="G11" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H12" s="45" t="inlineStr">
+      <c r="H11" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I12" s="45" t="inlineStr">
+      <c r="I11" s="53" t="inlineStr">
         <is>
           <t>Problem/findings→recommendation connectors.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="46" t="inlineStr">
+      <c r="J11" s="49" t="n"/>
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="49" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="49" t="n"/>
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C12" s="54" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D13" s="46" t="inlineStr">
+      <c r="D12" s="54" t="inlineStr">
         <is>
           <t>Therefore / Hence</t>
         </is>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E12" s="54" t="inlineStr">
         <is>
           <t>Therefore, this study aims...; Hence, the study aimed...</t>
         </is>
       </c>
-      <c r="F13" s="46" t="inlineStr">
+      <c r="F12" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G13" s="46" t="inlineStr">
+      <c r="G12" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H13" s="46" t="inlineStr">
+      <c r="H12" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I13" s="46" t="inlineStr">
+      <c r="I12" s="54" t="inlineStr">
         <is>
           <t>Background→aim connectors.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="B14" s="45" t="inlineStr">
+      <c r="J12" s="49" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="49" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="49" t="n"/>
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>VM7</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D14" s="45" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>Thus</t>
         </is>
       </c>
-      <c r="E14" s="45" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>Thus, no significant association could be established</t>
         </is>
       </c>
-      <c r="F14" s="45" t="inlineStr">
+      <c r="F13" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G14" s="45" t="inlineStr">
+      <c r="G13" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H14" s="45" t="inlineStr">
+      <c r="H13" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I14" s="45" t="inlineStr">
+      <c r="I13" s="53" t="inlineStr">
         <is>
           <t>Results→conclusion connector.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="B15" s="46" t="inlineStr">
+      <c r="J13" s="49" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="49" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>VM9</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D15" s="46" t="inlineStr">
+      <c r="D14" s="54" t="inlineStr">
         <is>
           <t>hence</t>
         </is>
       </c>
-      <c r="E15" s="46" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>hence, all individual shrimps counted as one sample</t>
         </is>
       </c>
-      <c r="F15" s="46" t="inlineStr">
+      <c r="F14" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G15" s="46" t="inlineStr">
+      <c r="G14" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H15" s="46" t="inlineStr">
+      <c r="H14" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I15" s="46" t="inlineStr">
+      <c r="I14" s="54" t="inlineStr">
         <is>
           <t>Methods sequencing only.</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="B16" s="45" t="inlineStr">
+      <c r="J14" s="49" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="49" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="49" t="n"/>
+      <c r="B15" s="53" t="inlineStr">
         <is>
           <t>VM12</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
+      <c r="C15" s="53" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D16" s="45" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>Hence</t>
         </is>
       </c>
-      <c r="E16" s="45" t="inlineStr">
+      <c r="E15" s="53" t="inlineStr">
         <is>
           <t>Hence, this study aimed to detect ASF virus...</t>
         </is>
       </c>
-      <c r="F16" s="45" t="inlineStr">
+      <c r="F15" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G16" s="45" t="inlineStr">
+      <c r="G15" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H16" s="45" t="inlineStr">
+      <c r="H15" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I16" s="45" t="inlineStr">
+      <c r="I15" s="53" t="inlineStr">
         <is>
           <t>Background→aim connector.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="B17" s="46" t="inlineStr">
+      <c r="J15" s="49" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="49" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="49" t="n"/>
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>Acs5</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C16" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D16" s="54" t="inlineStr">
         <is>
           <t>Therefore</t>
         </is>
       </c>
-      <c r="E17" s="46" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>Therefore, the... (yield inference connector)</t>
         </is>
       </c>
-      <c r="F17" s="46" t="inlineStr">
+      <c r="F16" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G17" s="46" t="inlineStr">
+      <c r="G16" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H17" s="46" t="inlineStr">
+      <c r="H16" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I17" s="46" t="inlineStr">
+      <c r="I16" s="54" t="inlineStr">
         <is>
           <t>Results→inference connector.</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="B18" s="45" t="inlineStr">
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="49" t="n"/>
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>Aas9</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D18" s="45" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>Therefore</t>
         </is>
       </c>
-      <c r="E18" s="45" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>Therefore, it is recommended for future researchers...</t>
         </is>
       </c>
-      <c r="F18" s="45" t="inlineStr">
+      <c r="F17" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G18" s="45" t="inlineStr">
+      <c r="G17" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H18" s="45" t="inlineStr">
+      <c r="H17" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I18" s="45" t="inlineStr">
+      <c r="I17" s="53" t="inlineStr">
         <is>
           <t>Results→recommendation connector.</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="B19" s="46" t="inlineStr">
+      <c r="J17" s="49" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="49" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="49" t="n"/>
+      <c r="B18" s="54" t="inlineStr">
         <is>
           <t>Acs3</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C18" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D19" s="46" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E19" s="46" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>In conclusion, the number of rooted...</t>
         </is>
       </c>
-      <c r="F19" s="46" t="inlineStr">
+      <c r="F18" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G19" s="46" t="inlineStr">
+      <c r="G18" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H19" s="46" t="inlineStr">
+      <c r="H18" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I19" s="46" t="inlineStr">
+      <c r="I18" s="54" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="B20" s="45" t="inlineStr">
+      <c r="J18" s="49" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="49" t="n"/>
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>Acs7</t>
         </is>
       </c>
-      <c r="C20" s="45" t="inlineStr">
+      <c r="C19" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D20" s="45" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E20" s="45" t="inlineStr">
+      <c r="E19" s="53" t="inlineStr">
         <is>
           <t>In conclusion, the use of rice hull...</t>
         </is>
       </c>
-      <c r="F20" s="45" t="inlineStr">
+      <c r="F19" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G20" s="45" t="inlineStr">
+      <c r="G19" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H20" s="45" t="inlineStr">
+      <c r="H19" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I20" s="45" t="inlineStr">
+      <c r="I19" s="53" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="B21" s="46" t="inlineStr">
+      <c r="J19" s="49" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="49" t="n"/>
+      <c r="B20" s="54" t="inlineStr">
         <is>
           <t>Acs10</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C20" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D21" s="46" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E21" s="46" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>In conclusion, T3:...</t>
         </is>
       </c>
-      <c r="F21" s="46" t="inlineStr">
+      <c r="F20" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G21" s="46" t="inlineStr">
+      <c r="G20" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H21" s="46" t="inlineStr">
+      <c r="H20" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I21" s="46" t="inlineStr">
+      <c r="I20" s="54" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="B22" s="45" t="inlineStr">
+      <c r="J20" s="49" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="49" t="n"/>
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>Aas3</t>
         </is>
       </c>
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D22" s="45" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E22" s="45" t="inlineStr">
+      <c r="E21" s="53" t="inlineStr">
         <is>
           <t>In conclusion, proved the treatment 1...</t>
         </is>
       </c>
-      <c r="F22" s="45" t="inlineStr">
+      <c r="F21" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G22" s="45" t="inlineStr">
+      <c r="G21" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H22" s="45" t="inlineStr">
+      <c r="H21" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I22" s="45" t="inlineStr">
+      <c r="I21" s="53" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="B23" s="46" t="inlineStr">
+      <c r="J21" s="49" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="49" t="n"/>
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Aas10</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C22" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D23" s="46" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E23" s="46" t="inlineStr">
+      <c r="E22" s="54" t="inlineStr">
         <is>
           <t>In conclusion, based on the results, it can be stated...</t>
         </is>
       </c>
-      <c r="F23" s="46" t="inlineStr">
+      <c r="F22" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G23" s="46" t="inlineStr">
+      <c r="G22" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H23" s="46" t="inlineStr">
+      <c r="H22" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I23" s="46" t="inlineStr">
+      <c r="I22" s="54" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="B24" s="47" t="inlineStr">
+      <c r="J22" s="49" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="49" t="n"/>
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>All disciplines</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D23" s="55" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
-      <c r="E24" s="47" t="inlineStr">
+      <c r="E23" s="55" t="inlineStr">
         <is>
           <t>No "as X suggested", "in our view", "please", "kindly", "with due respect", "one might argue"</t>
         </is>
       </c>
-      <c r="F24" s="47" t="inlineStr">
+      <c r="F23" s="55" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="G24" s="47" t="inlineStr">
+      <c r="G23" s="55" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H24" s="47" t="inlineStr">
+      <c r="H23" s="55" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I24" s="47" t="inlineStr">
+      <c r="I23" s="55" t="inlineStr">
         <is>
           <t>No politeness/deference devices in the 60 abstracts.</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="B25" s="47" t="inlineStr">
+      <c r="J23" s="49" t="n"/>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="49" t="n"/>
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>regarding / with regard to / overall / first-second</t>
         </is>
       </c>
-      <c r="E25" s="47" t="inlineStr">
+      <c r="E24" s="55" t="inlineStr">
         <is>
           <t>Common in VM KAP and ranking sentences</t>
         </is>
       </c>
-      <c r="F25" s="47" t="inlineStr">
+      <c r="F24" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="47" t="inlineStr">
+      <c r="G24" s="55" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H25" s="47" t="inlineStr">
+      <c r="H24" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I25" s="47" t="inlineStr">
+      <c r="I24" s="55" t="inlineStr">
         <is>
           <t>Topic prepositions and ordinal ranking of results are NOT discourse-organization function. Left untagged.</t>
         </is>
       </c>
+      <c r="J24" s="49" t="n"/>
+      <c r="K24" s="49" t="n"/>
+      <c r="L24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="49" t="n"/>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="55" t="inlineStr">
+        <is>
+          <t>should / recommended (FP-Rec)</t>
+        </is>
+      </c>
+      <c r="E25" s="55" t="inlineStr">
+        <is>
+          <t>See Rejected Candidates</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H25" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="55" t="inlineStr">
+        <is>
+          <t>Deontic prescriptions. Reject reason FP-Rec, not Layer 2 P or DO.</t>
+        </is>
+      </c>
+      <c r="J25" s="49" t="n"/>
+      <c r="K25" s="49" t="n"/>
+      <c r="L25" s="49" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="B26" s="47" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C26" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="47" t="inlineStr">
-        <is>
-          <t>should / recommended (FP-Rec)</t>
-        </is>
-      </c>
-      <c r="E26" s="47" t="inlineStr">
-        <is>
-          <t>See Rejected Candidates</t>
-        </is>
-      </c>
-      <c r="F26" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H26" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="47" t="inlineStr">
-        <is>
-          <t>Deontic prescriptions. Reject reason FP-Rec, not Layer 2 P or DO.</t>
-        </is>
-      </c>
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49" t="n"/>
+      <c r="K26" s="49" t="n"/>
+      <c r="L26" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="n"/>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="49" t="n"/>
+      <c r="K27" s="49" t="n"/>
+      <c r="L27" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="n"/>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="49" t="n"/>
+      <c r="K28" s="49" t="n"/>
+      <c r="L28" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="n"/>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="49" t="n"/>
+      <c r="K29" s="49" t="n"/>
+      <c r="L29" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="49" t="n"/>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="49" t="n"/>
+      <c r="K30" s="49" t="n"/>
+      <c r="L30" s="49" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -5442,216 +5442,216 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
+    <row r="65" ht="45" customHeight="1">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Hence, this study aimed to investigate the presence of potential mycobacterial infections in cultivated milkfish collected from fish-supplying areas of Pampanga.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>Lexical Hedges</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="I65" s="5" t="n">
         <v>256</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="21" t="inlineStr">
         <is>
           <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'presence of mycobacterial infections' asserts existence; 'potential mycobacterial infections' marks them as possible.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
+    <row r="66" ht="45" customHeight="1">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="22" t="inlineStr">
         <is>
           <t>Hence, lactic acid bacteria (LAB) have emerged as a focal point due to their potential quorum quenching (QQ) activities.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Lexical Hedges</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="20" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="I66" t="n">
+      <c r="I66" s="6" t="n">
         <v>149</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="23" t="inlineStr">
         <is>
           <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'their quorum quenching activities' asserts the activities exist.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
+    <row r="67" ht="45" customHeight="1">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>B16</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="18" t="inlineStr">
         <is>
           <t>The increasing popularity of SHC or “ukay-ukay” in the Philippines, coupled with potential public health concerns associated with transmitting pathogenic bacteria, emphasized this research’s need.</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Lexical Hedges</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="20" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" s="5" t="n">
         <v>223</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="21" t="inlineStr">
         <is>
           <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'public health concerns' asserted as fact vs possible. Same abstract also codes conclusion-position 'potential public health risks' as EC.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
+    <row r="68" ht="45" customHeight="1">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>VM9</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="22" t="inlineStr">
         <is>
           <t>Its persistence in marine environments, particularly in the form of microplastics, posed potential health risks to aquatic species and humans through seafood consumption.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Lexical Hedges</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="20" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="I68" s="6" t="n">
         <v>430</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="23" t="inlineStr">
         <is>
           <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'posed health risks' asserts risks as fact.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
+    <row r="69" ht="45" customHeight="1">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Aas5</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="18" t="inlineStr">
         <is>
           <t>Fortunately, insect farming can be seen as a potential solution for filling the protein gap for feed and food resources in a more sustainable manned compared to other animal protein sources.</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Lexical Hedges</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="20" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="I69" t="n">
+      <c r="I69" s="5" t="n">
         <v>316</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="21" t="inlineStr">
         <is>
           <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'a solution' is stronger endorsement than 'a potential solution'. Multi-hedge isolation: 'can' already coded EC in same sentence; 'potential' independently softens.</t>
         </is>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -271,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -371,6 +371,23 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3424,7 +3441,7 @@
     <row r="18" ht="45" customHeight="1">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -3433,16 +3450,16 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>The findings of this study showed and suggests that the extraction efficiency favors the highly polar solvents than the non-polar solvents in determining the antifungal potential of E. indica against Colletotrichum spp..</t>
+          <t>Hence, this study aimed to investigate the presence of potential mycobacterial infections in cultivated milkfish collected from fish-supplying areas of Pampanga.</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>suggests</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -3456,18 +3473,18 @@
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'showed and suggests that the extraction efficiency favors...'.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'presence of mycobacterial infections' asserts existence; 'potential mycobacterial infections' marks them as possible.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3476,21 +3493,21 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>The findings of this study attested that this specific type of grass could potentially be used as biofungicide agent.</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>could</t>
+          <t>Hence, lactic acid bacteria (LAB) have emerged as a focal point due to their potential quorum quenching (QQ) activities.</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>potential</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -3499,11 +3516,11 @@
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>242</v>
+        <v>149</v>
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'could potentially be used as biofungicide agent'.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'their quorum quenching activities' asserts the activities exist.</t>
         </is>
       </c>
     </row>
@@ -3519,21 +3536,21 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>The findings of this study attested that this specific type of grass could potentially be used as biofungicide agent.</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>potentially</t>
+          <t>The findings of this study showed and suggests that the extraction efficiency favors the highly polar solvents than the non-polar solvents in determining the antifungal potential of E. indica against Colletotrichum spp..</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>suggests</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Adverbial Hedges</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -3546,14 +3563,14 @@
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Adverbial hedge: 'potentially' qualifies the claim.</t>
+          <t>Lexical hedge: 'showed and suggests that the extraction efficiency favors...'.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3562,21 +3579,21 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>Methicillin-resistant Staphylococcus aureus (MRSA) is a common and potentially severe pathogen that has developed resistance to several types of antibiotics.</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>potentially</t>
+          <t>The findings of this study attested that this specific type of grass could potentially be used as biofungicide agent.</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>could</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Adverbial Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -3585,18 +3602,18 @@
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t>Adverbial hedge: 'potentially severe pathogen' qualifies the claim.</t>
+          <t>Modal hedge: 'could potentially be used as biofungicide agent'.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -3605,21 +3622,21 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Antibiotic susceptibility testing indicated the presence of both methicillin-sensitive S. aureus (MSSA) and methicillin-resistant S. aureus (MRSA) strains among the collected samples, highlighting the potential public health risks associated with the handling and purchasing of second-hand clothing.</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>potential</t>
+          <t>The findings of this study attested that this specific type of grass could potentially be used as biofungicide agent.</t>
+        </is>
+      </c>
+      <c r="F22" s="62" t="inlineStr">
+        <is>
+          <t>potentially</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Adverbial Hedges</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -3628,11 +3645,11 @@
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in implications): 'highlighting the potential public health risks' qualifies the claim.</t>
+          <t>Adverbial hedge: 'potentially' qualifies the claim.</t>
         </is>
       </c>
     </row>
@@ -3648,14 +3665,14 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>This study, therefore, underscores the need for proper precautions to mitigate the spread of potentially harmful bacteria, including MRSA, on second-hand clothing.</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) is a common and potentially severe pathogen that has developed resistance to several types of antibiotics.</t>
+        </is>
+      </c>
+      <c r="F23" s="62" t="inlineStr">
         <is>
           <t>potentially</t>
         </is>
@@ -3675,7 +3692,7 @@
       </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t>Adverbial hedge: 'potentially harmful bacteria' qualifies the claim.</t>
+          <t>Adverbial hedge: 'potentially severe pathogen' qualifies the claim.</t>
         </is>
       </c>
     </row>
@@ -3691,11 +3708,11 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>It highlights the importance of raising awareness among both vendors and consumers about the potential health risks associated with these garments.</t>
+          <t>The increasing popularity of SHC or “ukay-ukay” in the Philippines, coupled with potential public health concerns associated with transmitting pathogenic bacteria, emphasized this research’s need.</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -3718,14 +3735,14 @@
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in implications): 'the potential health risks associated with these garments' qualifies the claim.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'public health concerns' asserted as fact vs possible. Same abstract also codes conclusion-position 'potential public health risks' as EC.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3738,12 +3755,12 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>The TLC-MTT overlay assay showed that the extract exhibits antibacterial activity against S. aureus but was ineffective against E. coli, suggesting selective antibacterial potential.</t>
+          <t>Antibiotic susceptibility testing indicated the presence of both methicillin-sensitive S. aureus (MSSA) and methicillin-resistant S. aureus (MRSA) strains among the collected samples, highlighting the potential public health risks associated with the handling and purchasing of second-hand clothing.</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>suggesting</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3757,18 +3774,18 @@
         </is>
       </c>
       <c r="I25" s="5" t="n">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'suggesting selective antibacterial potential' = inferential conclusion.</t>
+          <t>Lexical hedge (claim in implications): 'highlighting the potential public health risks' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -3777,21 +3794,21 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>The TLC-MTT overlay assay showed that the extract exhibits antibacterial activity against S. aureus but was ineffective against E. coli, suggesting selective antibacterial potential.</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>potential</t>
+          <t>This study, therefore, underscores the need for proper precautions to mitigate the spread of potentially harmful bacteria, including MRSA, on second-hand clothing.</t>
+        </is>
+      </c>
+      <c r="F26" s="62" t="inlineStr">
+        <is>
+          <t>potentially</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Adverbial Hedges</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -3800,18 +3817,18 @@
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'selective antibacterial potential' qualifies the finding.</t>
+          <t>Adverbial hedge: 'potentially harmful bacteria' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3820,16 +3837,16 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>In the p-value in the analysis of economic impact is 0.064 and p-value of fishing practices is 0.069 are slightly above 0.05, the result suggests that there is no strong statistical evidence that heavy metal contamination alone is significantly affecting fishers’ income and practices.</t>
+          <t>It highlights the importance of raising awareness among both vendors and consumers about the potential health risks associated with these garments.</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>suggests</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3843,18 +3860,18 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'the result suggests that there is no strong statistical evidence...'.</t>
+          <t>Lexical hedge (claim in implications): 'the potential health risks associated with these garments' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -3863,16 +3880,16 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Thus, local government should address the possible negative impacts of tourism activities and manage the carrying capacity for sustainable tourism.</t>
+          <t>The TLC-MTT overlay assay showed that the extract exhibits antibacterial activity against S. aureus but was ineffective against E. coli, suggesting selective antibacterial potential.</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>suggesting</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -3886,18 +3903,18 @@
         </is>
       </c>
       <c r="I28" s="6" t="n">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'the possible negative impacts of tourism activities' qualifies the claim.</t>
+          <t>Lexical hedge: 'suggesting selective antibacterial potential' = inferential conclusion.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3906,16 +3923,16 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>However, there was no significant difference in the effect of Trichoderma harzianum among the test variables on any of the three days, suggesting that the fungus had a similar impact on the growth of all four test variables.</t>
+          <t>The TLC-MTT overlay assay showed that the extract exhibits antibacterial activity against S. aureus but was ineffective against E. coli, suggesting selective antibacterial potential.</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>suggesting</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3929,36 +3946,36 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'suggesting that the fungus had a similar impact on the growth of all four test variables' = inferential conclusion.</t>
+          <t>Lexical hedge (claim in conclusion): 'selective antibacterial potential' qualifies the finding.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>VM2</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Veterinary Medicine</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>In terms of attitude, 92% of the respondents showed good attitude, indicating a strong sense of empathy and concern for the welfare of stray animals on campus.</t>
+          <t>In the p-value in the analysis of economic impact is 0.064 and p-value of fishing practices is 0.069 are slightly above 0.05, the result suggests that there is no strong statistical evidence that heavy metal contamination alone is significantly affecting fishers’ income and practices.</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>indicating</t>
+          <t>suggests</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -3972,36 +3989,36 @@
         </is>
       </c>
       <c r="I30" s="6" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'indicating a strong sense of empathy and concern' = inferential conclusion.</t>
+          <t>Lexical hedge: 'the result suggests that there is no strong statistical evidence...'.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>VM2</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Veterinary Medicine</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>A strong relationship was found between sex and knowledge (p = 0.000), with female students more likely to have moderate to good knowledge.</t>
+          <t>Thus, local government should address the possible negative impacts of tourism activities and manage the carrying capacity for sustainable tourism.</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -4015,36 +4032,36 @@
         </is>
       </c>
       <c r="I31" s="5" t="n">
-        <v>358</v>
+        <v>290</v>
       </c>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'female students more likely to have moderate to good knowledge' qualifies the claim.</t>
+          <t>Lexical hedge: 'the possible negative impacts of tourism activities' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>VM2</t>
+          <t>B20</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Veterinary Medicine</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Female students, higher-year students, and those who owned pets were more likely to engage in responsible and humane behavior toward stray animals.</t>
+          <t>However, there was no significant difference in the effect of Trichoderma harzianum among the test variables on any of the three days, suggesting that the fungus had a similar impact on the growth of all four test variables.</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>likely</t>
+          <t>suggesting</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -4058,18 +4075,18 @@
         </is>
       </c>
       <c r="I32" s="6" t="n">
-        <v>358</v>
+        <v>223</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'those who owned pets were more likely to engage in responsible and humane behaviors' qualifies the claim.</t>
+          <t>Lexical hedge: 'suggesting that the fungus had a similar impact on the growth of all four test variables' = inferential conclusion.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>VM5</t>
+          <t>VM2</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4078,16 +4095,16 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>These findings highlight the potential of M. calabura L. as a source of antifungal agents, warranting further investigation into its therapeutic applications and formulation for dermatophytosis management.</t>
+          <t>In terms of attitude, 92% of the respondents showed good attitude, indicating a strong sense of empathy and concern for the welfare of stray animals on campus.</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>potential</t>
+          <t>indicating</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -4101,18 +4118,18 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>256</v>
+        <v>358</v>
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'the potential of M. calabura L. as a source of antifungal agents' qualifies the claim about implications.</t>
+          <t>Lexical hedge: 'indicating a strong sense of empathy and concern' = inferential conclusion.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>VM7</t>
+          <t>VM2</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -4121,21 +4138,21 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Thus, no significant association between clinical signs and heartworm infection could be established.</t>
-        </is>
-      </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>could</t>
+          <t>A strong relationship was found between sex and knowledge (p = 0.000), with female students more likely to have moderate to good knowledge.</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>likely</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -4144,18 +4161,18 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>Modal hedge: 'no significant association... could be established' possibility/negation.</t>
+          <t>Lexical hedge: 'female students more likely to have moderate to good knowledge' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>VM8</t>
+          <t>VM2</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -4164,16 +4181,16 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>These findings confirm the potential of both plant extracts as natural anthelmintics, with tamarind showing superior efficacy.</t>
+          <t>Female students, higher-year students, and those who owned pets were more likely to engage in responsible and humane behavior toward stray animals.</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>potential</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4187,18 +4204,18 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>253</v>
+        <v>358</v>
       </c>
       <c r="J35" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'the potential of both plant extracts as natural anthelmintics' qualifies the claim about implications.</t>
+          <t>Lexical hedge: 'those who owned pets were more likely to engage in responsible and humane behaviors' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>VM12</t>
+          <t>VM5</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -4207,21 +4224,21 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>The result of collective community and government efforts might be effective in preventing, controlling, and managing the spread of ASF, but it is not conclusive that ASF is not present in the municipality of Magalang.</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>might</t>
+          <t>These findings highlight the potential of M. calabura L. as a source of antifungal agents, warranting further investigation into its therapeutic applications and formulation for dermatophytosis management.</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>potential</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -4230,18 +4247,18 @@
         </is>
       </c>
       <c r="I36" s="6" t="n">
-        <v>182</v>
+        <v>256</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Modal hedge: 'collective community and government efforts might be effective in preventing...'.</t>
+          <t>Lexical hedge (claim in conclusion): 'the potential of M. calabura L. as a source of antifungal agents' qualifies the claim about implications.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>VM15</t>
+          <t>VM7</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -4250,21 +4267,21 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>Furthermore, the result of the study suggests that var.</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>suggests</t>
+          <t>Thus, no significant association between clinical signs and heartworm infection could be established.</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>could</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -4273,18 +4290,18 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="J37" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'the result of the study suggests that var. S54 presented the most potent anti-cancer and anti-angiogenic activity'.</t>
+          <t>Modal hedge: 'no significant association... could be established' possibility/negation.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>VM17</t>
+          <t>VM8</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -4293,11 +4310,11 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>The results demonstrated the potential of butterfly pea flower aqueous extract in improving the survival of zebrafish at its larval stage.</t>
+          <t>These findings confirm the potential of both plant extracts as natural anthelmintics, with tamarind showing superior efficacy.</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -4316,36 +4333,36 @@
         </is>
       </c>
       <c r="I38" s="6" t="n">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'the potential of butterfly pea flower aqueous extract in improving the survival of zebrafish' qualifies the claim.</t>
+          <t>Lexical hedge (claim in conclusion): 'the potential of both plant extracts as natural anthelmintics' qualifies the claim about implications.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Acs1</t>
+          <t>VM9</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Veterinary Medicine</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>These findings suggest that fermented banana peel, when applied at an optimal rate in combination with reduced synthetic fertilizer input, can significantly enhance the growth and yield performance of finger pepper, offering a sustainable alternative for crop production.</t>
+          <t>Its persistence in marine environments, particularly in the form of microplastics, posed potential health risks to aquatic species and humans through seafood consumption.</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -4359,41 +4376,41 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>203</v>
+        <v>430</v>
       </c>
       <c r="J39" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'These findings suggest that fermented banana peel... can significantly enhance the growth and yield performance'.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'posed health risks' asserts risks as fact.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Acs2</t>
+          <t>VM12</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Veterinary Medicine</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>suggests</t>
+          <t>The result of collective community and government efforts might be effective in preventing, controlling, and managing the spread of ASF, but it is not conclusive that ASF is not present in the municipality of Magalang.</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>might</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H40" s="20" t="inlineStr">
@@ -4402,41 +4419,41 @@
         </is>
       </c>
       <c r="I40" s="6" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits'.</t>
+          <t>Modal hedge: 'collective community and government efforts might be effective in preventing...'.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Acs2</t>
+          <t>VM15</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Veterinary Medicine</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>might</t>
+          <t>Furthermore, the result of the study suggests that var.</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>suggests</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H41" s="20" t="inlineStr">
@@ -4445,41 +4462,41 @@
         </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'statistical significance might not have been observed' possibility.</t>
+          <t>Lexical hedge: 'the result of the study suggests that var. S54 presented the most potent anti-cancer and anti-angiogenic activity'.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Acs2</t>
+          <t>VM17</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Veterinary Medicine</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>could</t>
+          <t>The results demonstrated the potential of butterfly pea flower aqueous extract in improving the survival of zebrafish at its larval stage.</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>potential</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H42" s="20" t="inlineStr">
@@ -4488,18 +4505,18 @@
         </is>
       </c>
       <c r="I42" s="6" t="n">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>Modal hedge: 'the mycorrhiza treatment could still offer potential benefits' possibility.</t>
+          <t>Lexical hedge (claim in conclusion): 'the potential of butterfly pea flower aqueous extract in improving the survival of zebrafish' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Acs2</t>
+          <t>Acs1</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4508,16 +4525,16 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
+          <t>These findings suggest that fermented banana peel, when applied at an optimal rate in combination with reduced synthetic fertilizer input, can significantly enhance the growth and yield performance of finger pepper, offering a sustainable alternative for crop production.</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>potential</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -4531,11 +4548,11 @@
         </is>
       </c>
       <c r="I43" s="5" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="J43" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'could still offer potential benefits to the plants' qualifies the claim.</t>
+          <t>Lexical hedge: 'These findings suggest that fermented banana peel... can significantly enhance the growth and yield performance'.</t>
         </is>
       </c>
     </row>
@@ -4551,11 +4568,11 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" s="22" t="inlineStr">
         <is>
-          <t>This suggests that while the differences might not have been significant in the study, the researchers believe that mycorrhiza could provide beneficial effects in practical agricultural contexts.</t>
+          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
@@ -4578,7 +4595,7 @@
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'This suggests that while the differences might not have been significant...'.</t>
+          <t>Lexical hedge: 'This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits'.</t>
         </is>
       </c>
     </row>
@@ -4594,11 +4611,11 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>This suggests that while the differences might not have been significant in the study, the researchers believe that mycorrhiza could provide beneficial effects in practical agricultural contexts.</t>
+          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
         </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
@@ -4621,7 +4638,7 @@
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'the differences might not have been significant in the study'.</t>
+          <t>Modal hedge: 'statistical significance might not have been observed' possibility.</t>
         </is>
       </c>
     </row>
@@ -4637,11 +4654,11 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E46" s="22" t="inlineStr">
         <is>
-          <t>This suggests that while the differences might not have been significant in the study, the researchers believe that mycorrhiza could provide beneficial effects in practical agricultural contexts.</t>
+          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
         </is>
       </c>
       <c r="F46" s="24" t="inlineStr">
@@ -4664,7 +4681,7 @@
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>Modal hedge: 'the researchers believe that mycorrhiza could provide beneficial effects'.</t>
+          <t>Modal hedge: 'the mycorrhiza treatment could still offer potential benefits' possibility.</t>
         </is>
       </c>
     </row>
@@ -4680,11 +4697,11 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>The study concluded that the application of mycorrhiza positive impact on mung beans during drought and root development highlights its potential benefits for plant growth.</t>
+          <t>This suggests that while statistical significance might not have been observed, the mycorrhiza treatment could still offer potential benefits to the plants.</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
@@ -4707,14 +4724,14 @@
       </c>
       <c r="J47" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'highlights its potential benefits for plant growth' qualifies the claim.</t>
+          <t>Lexical hedge (claim in conclusion): 'could still offer potential benefits to the plants' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Acs3</t>
+          <t>Acs2</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -4723,21 +4740,21 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>Most can survive the water treatment application but may not establish roots and die after several days.</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>may</t>
+          <t>This suggests that while the differences might not have been significant in the study, the researchers believe that mycorrhiza could provide beneficial effects in practical agricultural contexts.</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>suggests</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H48" s="20" t="inlineStr">
@@ -4746,18 +4763,18 @@
         </is>
       </c>
       <c r="I48" s="6" t="n">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>Modal hedge: 'may not establish roots and die after several days' possibility claim.</t>
+          <t>Lexical hedge: 'This suggests that while the differences might not have been significant...'.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Acs3</t>
+          <t>Acs2</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -4766,16 +4783,16 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>However, it can be derived that the application of different alternative rooting hormones has a comparable effect with synthetic rooting hormones based on the growth parameters.</t>
+          <t>This suggests that while the differences might not have been significant in the study, the researchers believe that mycorrhiza could provide beneficial effects in practical agricultural contexts.</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>can</t>
+          <t>might</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4789,18 +4806,18 @@
         </is>
       </c>
       <c r="I49" s="5" t="n">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="J49" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'it can be derived that the application of different alternative rooting hormones has a comparable effect'.</t>
+          <t>Modal hedge: 'the differences might not have been significant in the study'.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Acs5</t>
+          <t>Acs2</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -4813,17 +4830,17 @@
       </c>
       <c r="E50" s="22" t="inlineStr">
         <is>
-          <t>This suggests that Trichoderma and fermented azolla at proper application frequencies could be beneficial in enhancing cultivation, promoting both plant growth and economic returns.</t>
-        </is>
-      </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>suggests</t>
+          <t>This suggests that while the differences might not have been significant in the study, the researchers believe that mycorrhiza could provide beneficial effects in practical agricultural contexts.</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>could</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H50" s="20" t="inlineStr">
@@ -4832,18 +4849,18 @@
         </is>
       </c>
       <c r="I50" s="6" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'This suggests that Trichoderma and fermented azolla at proper application frequencies could be beneficial in enhancing cultivation'.</t>
+          <t>Modal hedge: 'the researchers believe that mycorrhiza could provide beneficial effects'.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Acs5</t>
+          <t>Acs2</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4852,21 +4869,21 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>This suggests that Trichoderma and fermented azolla at proper application frequencies could be beneficial in enhancing cultivation, promoting both plant growth and economic returns.</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>could</t>
+          <t>The study concluded that the application of mycorrhiza positive impact on mung beans during drought and root development highlights its potential benefits for plant growth.</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>potential</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H51" s="20" t="inlineStr">
@@ -4875,18 +4892,18 @@
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="J51" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'could be beneficial in enhancing cultivation, promoting both plant growth and economic returns'.</t>
+          <t>Lexical hedge (claim in conclusion): 'highlights its potential benefits for plant growth' qualifies the claim.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="45" customHeight="1">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Acs6</t>
+          <t>Acs3</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -4895,21 +4912,21 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>These findings highlight their potential as effective, low-cost, and sustainable soil amendments for ornamental and horticultural cultivation, offering practical options for growers seeking eco-friendly methods to improve plant performance.</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>potential</t>
+          <t>Most can survive the water treatment application but may not establish roots and die after several days.</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>may</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H52" s="20" t="inlineStr">
@@ -4918,18 +4935,18 @@
         </is>
       </c>
       <c r="I52" s="6" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'their potential as effective, low-cost, and sustainable soil amendments' qualifies the claim about implications.</t>
+          <t>Modal hedge: 'may not establish roots and die after several days' possibility claim.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Acs7</t>
+          <t>Acs3</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4938,11 +4955,11 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>This notable increase in plant height can be attributed to the nutrient-rich content of GB 1000+ FF, which enhances soil conditions and facilitates better nutrient availability.</t>
+          <t>However, it can be derived that the application of different alternative rooting hormones has a comparable effect with synthetic rooting hormones based on the growth parameters.</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
@@ -4961,18 +4978,18 @@
         </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="J53" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'can be attributed to the nutrient-rich content'.</t>
+          <t>Modal hedge: 'it can be derived that the application of different alternative rooting hormones has a comparable effect'.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Acs9</t>
+          <t>Acs5</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -4985,12 +5002,12 @@
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>These findings suggest that soaking sugarcane setts in Azospirillum spp. biofertilizer for 24 hours can effectively promote early growth by enhancing root development and biomass accumulation, thereby supporting improved propagation success.</t>
+          <t>This suggests that Trichoderma and fermented azolla at proper application frequencies could be beneficial in enhancing cultivation, promoting both plant growth and economic returns.</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>suggests</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -5004,18 +5021,18 @@
         </is>
       </c>
       <c r="I54" s="6" t="n">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'These findings suggest that soaking sugarcane setts in Azospirillum spp. biofertilizer for 24 hours can effectively promote early growth'.</t>
+          <t>Lexical hedge: 'This suggests that Trichoderma and fermented azolla at proper application frequencies could be beneficial in enhancing cultivation'.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="45" customHeight="1">
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Acs9</t>
+          <t>Acs5</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -5028,12 +5045,12 @@
       </c>
       <c r="E55" s="18" t="inlineStr">
         <is>
-          <t>These findings suggest that soaking sugarcane setts in Azospirillum spp. biofertilizer for 24 hours can effectively promote early growth by enhancing root development and biomass accumulation, thereby supporting improved propagation success.</t>
+          <t>This suggests that Trichoderma and fermented azolla at proper application frequencies could be beneficial in enhancing cultivation, promoting both plant growth and economic returns.</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>can</t>
+          <t>could</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5047,18 +5064,18 @@
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="J55" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'can effectively promote early growth' — tentative generalization from this study's findings, not an established property. Sits inside a 'suggest' clause softening an overgeneralization.</t>
+          <t>Modal hedge: 'could be beneficial in enhancing cultivation, promoting both plant growth and economic returns'.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="45" customHeight="1">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Aas3</t>
+          <t>Acs6</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -5067,16 +5084,16 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>The result of the study showed in the treatments that there were no significant differences observed in feed consumption, which implies that treatments were comparable on parameters.</t>
+          <t>These findings highlight their potential as effective, low-cost, and sustainable soil amendments for ornamental and horticultural cultivation, offering practical options for growers seeking eco-friendly methods to improve plant performance.</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
         <is>
-          <t>implies</t>
+          <t>potential</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -5090,18 +5107,18 @@
         </is>
       </c>
       <c r="I56" s="6" t="n">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="J56" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'which implies that treatments were comparable on parameters'.</t>
+          <t>Lexical hedge (claim in conclusion): 'their potential as effective, low-cost, and sustainable soil amendments' qualifies the claim about implications.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Aas3</t>
+          <t>Acs7</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5110,11 +5127,11 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>It can also be concluded that D1 rice bran mixed with water spinach and with golden apple snail used in the study can help minimize the cost of production, specifically the feed cost.</t>
+          <t>This notable increase in plant height can be attributed to the nutrient-rich content of GB 1000+ FF, which enhances soil conditions and facilitates better nutrient availability.</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
@@ -5133,18 +5150,18 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>296</v>
+        <v>207</v>
       </c>
       <c r="J57" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'It can also be concluded that D1 rice bran mixed with water spinach... can help minimize the cost of production'.</t>
+          <t>Modal hedge: 'can be attributed to the nutrient-rich content'.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Aas4</t>
+          <t>Acs9</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -5153,16 +5170,16 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E58" s="22" t="inlineStr">
         <is>
-          <t>The statistical analysis suggests that there is no significant difference among the treatments with regard to their initial weight, gain in weight, average daily gain, and feed conversion ratio of the experimental rabbits.</t>
+          <t>These findings suggest that soaking sugarcane setts in Azospirillum spp. biofertilizer for 24 hours can effectively promote early growth by enhancing root development and biomass accumulation, thereby supporting improved propagation success.</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>suggests</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -5176,18 +5193,18 @@
         </is>
       </c>
       <c r="I58" s="6" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'The statistical analysis suggests that there is no significant difference among the treatments' = introduces finding.</t>
+          <t>Lexical hedge: 'These findings suggest that soaking sugarcane setts in Azospirillum spp. biofertilizer for 24 hours can effectively promote early growth'.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="45" customHeight="1">
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Aas5</t>
+          <t>Acs9</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5196,11 +5213,11 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E59" s="18" t="inlineStr">
         <is>
-          <t>Fortunately, insect farming can be seen as a potential solution for filling the protein gap for feed and food resources in a more sustainable manned compared to other animal protein sources.</t>
+          <t>These findings suggest that soaking sugarcane setts in Azospirillum spp. biofertilizer for 24 hours can effectively promote early growth by enhancing root development and biomass accumulation, thereby supporting improved propagation success.</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
@@ -5219,18 +5236,18 @@
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>316</v>
+        <v>170</v>
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'insect farming can be seen as a potential solution'.</t>
+          <t>Modal hedge: 'can effectively promote early growth' — tentative generalization from this study's findings, not an established property. Sits inside a 'suggest' clause softening an overgeneralization.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="45" customHeight="1">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Aas7</t>
+          <t>Aas3</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -5239,16 +5256,16 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E60" s="22" t="inlineStr">
         <is>
-          <t>Statistical analysis showed that there was no significant difference but showed numerical trends among the treatments in relation to initial weight, final weight, gain in weight, average daily gain, dry matter intake, and feed conversion ratio of the experimental rabbits In conclusion, all treatments are comparable in terms of growth, implying that Fermented Madre de Agua is a viable feed component under these conditions.</t>
+          <t>The result of the study showed in the treatments that there were no significant differences observed in feed consumption, which implies that treatments were comparable on parameters.</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
-          <t>implying</t>
+          <t>implies</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -5262,18 +5279,18 @@
         </is>
       </c>
       <c r="I60" s="6" t="n">
-        <v>202</v>
+        <v>296</v>
       </c>
       <c r="J60" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'implying that Fermented Madre de Agua is a viable feed component' = inferential conclusion.</t>
+          <t>Lexical hedge: 'which implies that treatments were comparable on parameters'.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="45" customHeight="1">
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Aas7</t>
+          <t>Aas3</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -5282,16 +5299,16 @@
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E61" s="18" t="inlineStr">
         <is>
-          <t>Feeding 20% fermented Madre De Agua may improve final weight, while feeding 10% fermented Madre De Agua may reduce dry matter intake.</t>
+          <t>It can also be concluded that D1 rice bran mixed with water spinach and with golden apple snail used in the study can help minimize the cost of production, specifically the feed cost.</t>
         </is>
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>may</t>
+          <t>can</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -5305,18 +5322,18 @@
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>202</v>
+        <v>296</v>
       </c>
       <c r="J61" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'Feeding 20% fermented Madre De Agua may improve final weight' possibility claim.</t>
+          <t>Modal hedge: 'It can also be concluded that D1 rice bran mixed with water spinach... can help minimize the cost of production'.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="45" customHeight="1">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Aas7</t>
+          <t>Aas4</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -5325,21 +5342,21 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E62" s="22" t="inlineStr">
         <is>
-          <t>Feeding 20% fermented Madre De Agua may improve final weight, while feeding 10% fermented Madre De Agua may reduce dry matter intake.</t>
-        </is>
-      </c>
-      <c r="F62" s="24" t="inlineStr">
-        <is>
-          <t>may</t>
+          <t>The statistical analysis suggests that there is no significant difference among the treatments with regard to their initial weight, gain in weight, average daily gain, and feed conversion ratio of the experimental rabbits.</t>
+        </is>
+      </c>
+      <c r="F62" s="19" t="inlineStr">
+        <is>
+          <t>suggests</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Modal Verbs</t>
+          <t>Lexical Hedges</t>
         </is>
       </c>
       <c r="H62" s="20" t="inlineStr">
@@ -5348,18 +5365,18 @@
         </is>
       </c>
       <c r="I62" s="6" t="n">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="J62" s="23" t="inlineStr">
         <is>
-          <t>Modal hedge: 'feeding 10% fermented Madre De Agua may reduce dry matter intake' possibility claim.</t>
+          <t>Lexical hedge: 'The statistical analysis suggests that there is no significant difference among the treatments' = introduces finding.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="45" customHeight="1">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Aas10</t>
+          <t>Aas5</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5368,11 +5385,11 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>In conclusion, based on the results, it can be stated that the ratio of 70% guinea grass (GG) + 30% concentrate (C), the control group, had a significantly higher (P&lt;0.01) feed conversion ratio, while rabbits in treatment T3 (50% guinea grass, 20% azolla, and 30% concentrate) had a significantly higher (P&lt;0.01) dry matter intake.</t>
+          <t>Fortunately, insect farming can be seen as a potential solution for filling the protein gap for feed and food resources in a more sustainable manned compared to other animal protein sources.</t>
         </is>
       </c>
       <c r="F63" s="24" t="inlineStr">
@@ -5391,18 +5408,18 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="J63" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'it can be stated that the ratio of 70% guinea grass (GG) + 30% concentrate (C)... had a significantly higher feed conversion ratio'.</t>
+          <t>Modal hedge: 'insect farming can be seen as a potential solution'.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="45" customHeight="1">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Aas10</t>
+          <t>Aas5</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -5411,11 +5428,11 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
-          <t>The researchers also saw that the treatment of 50% Guinea grass + 20% Azolla + 30% concentrates has potential as an alternative feed ration for rabbits without adverse effects, and considering that azolla can help breeders to lessen the feed cost in production.</t>
+          <t>Fortunately, insect farming can be seen as a potential solution for filling the protein gap for feed and food resources in a more sustainable manned compared to other animal protein sources.</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
@@ -5434,36 +5451,36 @@
         </is>
       </c>
       <c r="I64" s="6" t="n">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="J64" s="23" t="inlineStr">
         <is>
-          <t>Lexical hedge (claim in conclusion): 'has potential as an alternative feed ration for rabbits' qualifies the claim about implications.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'a solution' is stronger endorsement than 'a potential solution'. Multi-hedge isolation: 'can' already coded EC in same sentence; 'potential' independently softens.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="45" customHeight="1">
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>Aas7</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>Hence, this study aimed to investigate the presence of potential mycobacterial infections in cultivated milkfish collected from fish-supplying areas of Pampanga.</t>
+          <t>Statistical analysis showed that there was no significant difference but showed numerical trends among the treatments in relation to initial weight, final weight, gain in weight, average daily gain, dry matter intake, and feed conversion ratio of the experimental rabbits In conclusion, all treatments are comparable in terms of growth, implying that Fermented Madre de Agua is a viable feed component under these conditions.</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
         <is>
-          <t>potential</t>
+          <t>implying</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -5477,41 +5494,41 @@
         </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'presence of mycobacterial infections' asserts existence; 'potential mycobacterial infections' marks them as possible.</t>
+          <t>Lexical hedge: 'implying that Fermented Madre de Agua is a viable feed component' = inferential conclusion.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="45" customHeight="1">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Aas7</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E66" s="22" t="inlineStr">
         <is>
-          <t>Hence, lactic acid bacteria (LAB) have emerged as a focal point due to their potential quorum quenching (QQ) activities.</t>
-        </is>
-      </c>
-      <c r="F66" s="19" t="inlineStr">
-        <is>
-          <t>potential</t>
+          <t>Feeding 20% fermented Madre De Agua may improve final weight, while feeding 10% fermented Madre De Agua may reduce dry matter intake.</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>may</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H66" s="20" t="inlineStr">
@@ -5520,41 +5537,41 @@
         </is>
       </c>
       <c r="I66" s="6" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="J66" s="23" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'their quorum quenching activities' asserts the activities exist.</t>
+          <t>Modal hedge: 'Feeding 20% fermented Madre De Agua may improve final weight' possibility claim.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="45" customHeight="1">
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>Aas7</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>The increasing popularity of SHC or “ukay-ukay” in the Philippines, coupled with potential public health concerns associated with transmitting pathogenic bacteria, emphasized this research’s need.</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr">
-        <is>
-          <t>potential</t>
+          <t>Feeding 20% fermented Madre De Agua may improve final weight, while feeding 10% fermented Madre De Agua may reduce dry matter intake.</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>may</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H67" s="20" t="inlineStr">
@@ -5563,41 +5580,41 @@
         </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'public health concerns' asserted as fact vs possible. Same abstract also codes conclusion-position 'potential public health risks' as EC.</t>
+          <t>Modal hedge: 'feeding 10% fermented Madre De Agua may reduce dry matter intake' possibility claim.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="45" customHeight="1">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>VM9</t>
+          <t>Aas10</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Veterinary Medicine</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E68" s="22" t="inlineStr">
         <is>
-          <t>Its persistence in marine environments, particularly in the form of microplastics, posed potential health risks to aquatic species and humans through seafood consumption.</t>
-        </is>
-      </c>
-      <c r="F68" s="19" t="inlineStr">
-        <is>
-          <t>potential</t>
+          <t>In conclusion, based on the results, it can be stated that the ratio of 70% guinea grass (GG) + 30% concentrate (C), the control group, had a significantly higher (P&lt;0.01) feed conversion ratio, while rabbits in treatment T3 (50% guinea grass, 20% azolla, and 30% concentrate) had a significantly higher (P&lt;0.01) dry matter intake.</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>can</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Lexical Hedges</t>
+          <t>Modal Verbs</t>
         </is>
       </c>
       <c r="H68" s="20" t="inlineStr">
@@ -5606,18 +5623,18 @@
         </is>
       </c>
       <c r="I68" s="6" t="n">
-        <v>430</v>
+        <v>283</v>
       </c>
       <c r="J68" s="23" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'posed health risks' asserts risks as fact.</t>
+          <t>Modal hedge: 'it can be stated that the ratio of 70% guinea grass (GG) + 30% concentrate (C)... had a significantly higher feed conversion ratio'.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="45" customHeight="1">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Aas5</t>
+          <t>Aas10</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5626,11 +5643,11 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E69" s="18" t="inlineStr">
         <is>
-          <t>Fortunately, insect farming can be seen as a potential solution for filling the protein gap for feed and food resources in a more sustainable manned compared to other animal protein sources.</t>
+          <t>The researchers also saw that the treatment of 50% Guinea grass + 20% Azolla + 30% concentrates has potential as an alternative feed ration for rabbits without adverse effects, and considering that azolla can help breeders to lessen the feed cost in production.</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
@@ -5649,11 +5666,11 @@
         </is>
       </c>
       <c r="I69" s="5" t="n">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="J69" s="21" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'a solution' is stronger endorsement than 'a potential solution'. Multi-hedge isolation: 'can' already coded EC in same sentence; 'potential' independently softens.</t>
+          <t>Lexical hedge (claim in conclusion): 'has potential as an alternative feed ration for rabbits' qualifies the claim about implications.</t>
         </is>
       </c>
     </row>
@@ -6293,35 +6310,35 @@
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>Overall, the combination of Ziehl-Neelsen staining, biochemical testing like the catalase test, and evaluating growth in the presence of the Salt Tolerance Test provides a comprehensive approach for diagnosing and studying mycobacteriosis in cultivated milkfish, offering insights that can guide effective management strategies to control the spread of this disease in aquaculture system.</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>can</t>
         </is>
       </c>
-      <c r="G21" s="32" t="inlineStr">
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>FP-Cap</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>Capability: 'insights that can guide effective management strategies' describes inherent ability.</t>
         </is>
@@ -6538,490 +6555,490 @@
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>This study aimed to assess the phytochemical composition, antioxidant potential, and antibacterial activity of P. propinquum fruit ethanolic extract using Thin Layer Chromatography (TLC)-based techniques.</t>
         </is>
       </c>
-      <c r="F28" s="29" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G28" s="30" t="inlineStr">
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>Topic-naming (aim): 'assess the phytochemical composition, antioxidant potential, and antibacterial activity of P. propinquum' names the research object.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>The TLC-DPPH assay demonstrated notable antioxidant activity, as indicated by the reduction of DPPH radicals.</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>indicated</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr">
+      <c r="G29" s="30" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Evidential pointer: 'notable antioxidant activity, as indicated by the reduction of DPPH radicals' — points to evidence for a claim already asserted, not uncertainty about the claim.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>Further studies should focus on the isolation and characterization of its active compounds, their mechanisms of action, and their potential pharmaceutical applications.</t>
         </is>
       </c>
-      <c r="F30" s="29" t="inlineStr">
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>should</t>
         </is>
       </c>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>Recommendation: 'Further studies should focus on the isolation and characterization' — deontic prescription, not hedge.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>Further studies should focus on the isolation and characterization of its active compounds, their mechanisms of action, and their potential pharmaceutical applications.</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr">
+      <c r="F31" s="29" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G31" s="32" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>Topic-naming (recommendation-embedded): 'their potential pharmaceutical applications' is the object of a future-research recommendation, not a hedged claim.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>Hence, sustainable planning and management approaches should be considered.</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>should</t>
         </is>
       </c>
-      <c r="G32" s="30" t="inlineStr">
+      <c r="G32" s="32" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>Recommendation: 'sustainable planning and management approaches should be considered' — deontic prescription, not hedge.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>Thus, local government should address the possible negative impacts of tourism activities and manage the carrying capacity for sustainable tourism.</t>
         </is>
       </c>
-      <c r="F33" s="31" t="inlineStr">
+      <c r="F33" s="29" t="inlineStr">
         <is>
           <t>should</t>
         </is>
       </c>
-      <c r="G33" s="32" t="inlineStr">
+      <c r="G33" s="30" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H33" s="23" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>Recommendation: 'local government should address the possible negative impacts of tourism activities' — deontic prescription, not hedge.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>Therefore, this study aims to examine the potential of Trichoderma harzianum, an endophytic fungus, as a biocontrol agent for Cercospora leaf spot-on eggplants in the Philippines.</t>
         </is>
       </c>
-      <c r="F34" s="29" t="inlineStr">
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G34" s="30" t="inlineStr">
+      <c r="G34" s="32" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>Topic-naming (aim): 'this study aims to examine the potential of Trichoderma harzianum' names the research object.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>Hence, the study aimed to investigate the antagonistic potential of Trichoderma harzianum among the four isolates.</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G35" s="32" t="inlineStr">
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>Topic-naming (aim): 'the study aimed to investigate the antagonistic potential of Trichoderma harzianum' names the research object.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>The results indicate that the mean effect of Trichoderma harzianum on the test variables varied across the three days of observation.</t>
         </is>
       </c>
-      <c r="F36" s="29" t="inlineStr">
+      <c r="F36" s="31" t="inlineStr">
         <is>
           <t>indicate</t>
         </is>
       </c>
-      <c r="G36" s="30" t="inlineStr">
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="23" t="inlineStr">
         <is>
           <t>[AMB] Factive reporting: 'The results indicate that the mean effect... varied' — factive reporting of a statistical outcome, synonym for 'showed'. Per Decision Rules: not a hedge when used as synonym for showed/demonstrated.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>VM3</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>The findings suggests the need for assessment of knowledge, attitudes and practices of retail egg vendors about food safety and regular antimicrobial resistance monitoring on retail eggs.</t>
         </is>
       </c>
-      <c r="F37" s="31" t="inlineStr">
+      <c r="F37" s="29" t="inlineStr">
         <is>
           <t>suggests</t>
         </is>
       </c>
-      <c r="G37" s="32" t="inlineStr">
+      <c r="G37" s="30" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Recommendation: 'The findings suggests the need for assessment of knowledge, attitudes and practices' prescribes action.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>VM4</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>These findings suggest the need to improve training, regulation of milk storage, and the enforcement of labeling and sanitation standards to improve public health safety in the milk supply chain.</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>suggest</t>
         </is>
       </c>
-      <c r="G38" s="30" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>Recommendation: 'These findings suggest the need to improve training, regulation of milk storage...' prescribes action.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>VM5</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>This study explores the potential antifungal properties of Muntingia calabura L. methanolic leaf extracts against Trichophyton mentagrophytes, a dermatophyte species.</t>
         </is>
       </c>
-      <c r="F39" s="31" t="inlineStr">
+      <c r="F39" s="29" t="inlineStr">
         <is>
           <t>potential</t>
         </is>
       </c>
-      <c r="G39" s="32" t="inlineStr">
+      <c r="G39" s="30" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>Topic-naming (aim): 'potential antifungal properties of Muntingia calabura L.' names the research object.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>VM7</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>These measures can collectively contribute to the effective management and prevention of heartworm disease in the local canine population.</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>can</t>
         </is>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H40" s="21" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>General (recommendation-embedded): 'These measures can collectively contribute to...' follows a list of recommendations.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>VM7</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>Further research with larger sample sizes and diverse populations is needed to validate these findings and enhance our understanding of heartworm infection in the study area.</t>
         </is>
       </c>
-      <c r="F41" s="31" t="inlineStr">
+      <c r="F41" s="29" t="inlineStr">
         <is>
           <t>needed</t>
         </is>
       </c>
-      <c r="G41" s="32" t="inlineStr">
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
+      <c r="H41" s="21" t="inlineStr">
         <is>
           <t>Recommendation: 'Further research... is needed to validate these findings' prescribes action.</t>
         </is>
@@ -7553,210 +7570,210 @@
       </c>
     </row>
     <row r="57" ht="45" customHeight="1">
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Aas8</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E57" s="18" t="inlineStr">
         <is>
           <t>However, T1 exhibited the lowest feed conversion ratio (FCR) and mortality rate, indicating superior feed efficiency and improved survivability to T2.</t>
         </is>
       </c>
-      <c r="F57" s="31" t="inlineStr">
+      <c r="F57" s="29" t="inlineStr">
         <is>
           <t>indicating</t>
         </is>
       </c>
-      <c r="G57" s="32" t="inlineStr">
+      <c r="G57" s="30" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H57" s="23" t="inlineStr">
+      <c r="H57" s="21" t="inlineStr">
         <is>
           <t>Operational restatement: 'lowest FCR... indicating superior feed efficiency' — lower feed conversion ratio is the definitional measure of superior feed efficiency in animal nutrition, not an inference.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Aas8</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n">
+      <c r="D58" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E58" s="22" t="inlineStr">
         <is>
           <t>Based on the results of the study, it is recommended to feed mallard ducks with 75% rice porridge and 25% fish entrails during brooding stage at day 1 to day 21 for enhancing weight gain and achieving higher final weights in mallard ducks.</t>
         </is>
       </c>
-      <c r="F58" s="29" t="inlineStr">
+      <c r="F58" s="31" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="G58" s="30" t="inlineStr">
+      <c r="G58" s="32" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H58" s="21" t="inlineStr">
+      <c r="H58" s="23" t="inlineStr">
         <is>
           <t>Recommendation: 'it is recommended to feed mallard ducks with 75% rice porridge and 25% fish entrails'.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="45" customHeight="1">
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Aas8</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E59" s="18" t="inlineStr">
         <is>
           <t>Further research can explore the long-term effects and cost-effectiveness of these treatments and their impact on meat quality and reproductive performance.</t>
         </is>
       </c>
-      <c r="F59" s="31" t="inlineStr">
+      <c r="F59" s="29" t="inlineStr">
         <is>
           <t>can</t>
         </is>
       </c>
-      <c r="G59" s="32" t="inlineStr">
+      <c r="G59" s="30" t="inlineStr">
         <is>
           <t>FP-Gen</t>
         </is>
       </c>
-      <c r="H59" s="23" t="inlineStr">
+      <c r="H59" s="21" t="inlineStr">
         <is>
           <t>General (future research statement): 'Further research can explore the long-term effects and cost-effectiveness' — future research framing, not hedge.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="45" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Aas9</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n">
+      <c r="D60" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E60" s="22" t="inlineStr">
         <is>
           <t>Therefore, it is recommended for future researchers to add Diatomaceous earth and neem tree extract and check the humidity.</t>
         </is>
       </c>
-      <c r="F60" s="29" t="inlineStr">
+      <c r="F60" s="31" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="G60" s="30" t="inlineStr">
+      <c r="G60" s="32" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H60" s="21" t="inlineStr">
+      <c r="H60" s="23" t="inlineStr">
         <is>
           <t>Recommendation: 'it is recommended for future researchers to add Diatomaceous earth and neem tree extract'.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="45" customHeight="1">
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Aas10</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E61" s="22" t="inlineStr">
+      <c r="E61" s="18" t="inlineStr">
         <is>
           <t>The researchers still recommended incorporating 50% Guinea grass + 20% Azolla + 30% concentrates for rabbit growth performance, considering the results show that this treatment performs well and doesn't differ from treatment 1, which is the farmer practice.</t>
         </is>
       </c>
-      <c r="F61" s="31" t="inlineStr">
+      <c r="F61" s="29" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="G61" s="32" t="inlineStr">
+      <c r="G61" s="30" t="inlineStr">
         <is>
           <t>FP-Rec</t>
         </is>
       </c>
-      <c r="H61" s="23" t="inlineStr">
+      <c r="H61" s="21" t="inlineStr">
         <is>
           <t>Recommendation: 'The researchers still recommended incorporating 50% Guinea grass + 20% Azolla + 30% concentrates for rabbit growth performance'.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="45" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Aas10</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n">
+      <c r="D62" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E62" s="18" t="inlineStr">
+      <c r="E62" s="22" t="inlineStr">
         <is>
           <t>The researchers also saw that the treatment of 50% Guinea grass + 20% Azolla + 30% concentrates has potential as an alternative feed ration for rabbits without adverse effects, and considering that azolla can help breeders to lessen the feed cost in production.</t>
         </is>
       </c>
-      <c r="F62" s="29" t="inlineStr">
+      <c r="F62" s="31" t="inlineStr">
         <is>
           <t>can</t>
         </is>
       </c>
-      <c r="G62" s="30" t="inlineStr">
+      <c r="G62" s="32" t="inlineStr">
         <is>
           <t>FP-Cap</t>
         </is>
       </c>
-      <c r="H62" s="21" t="inlineStr">
+      <c r="H62" s="23" t="inlineStr">
         <is>
           <t>Capability: 'azolla can help breeders to lessen the feed cost' describes inherent ability. Capability substitution test: 'is able to help' preserves meaning.</t>
         </is>
@@ -7861,7 +7878,7 @@
           <t>The result of antibacterial testing revealed that the Partial Fraction of Balitbitan (Cynometra ramiflora) did not possess the property to inhibit the growth of Staphylococcus aureus and Escherichia coli.</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7896,7 +7913,7 @@
           <t>There was no zone of inhibition when treated with the partial fraction of Balitbitan.</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7931,7 +7948,7 @@
           <t>A drop test was also performed, which revealed that the eco-bricks from all treatments were significantly damaged at the height of one meter, making them a weak, unsuitable material to use in building walkways.</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7966,7 +7983,7 @@
           <t>The research findings do not apply to buildings.</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="57" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8001,7 +8018,7 @@
           <t>All mice treated with pure leaf extract of Z. talanai, monosodium glutamate, distilled water and L-Taurine showed a significant effect (lesions / aberrations) to the cytoarchitecture of liver and kidney.</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8036,7 +8053,7 @@
           <t>Based on the results of this study, pure MSG and pure ethanolic leaf extract of Z. talanai caused the lesions / aberrations to the liver and kidney.</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="57" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -8071,7 +8088,7 @@
           <t>Using the Ziehl-Neelsen stain for acid-fast bacteria detection, along with biochemical testing methods such as the catalase test and assessing growth in the presence of the Salt Tolerance Test, revealed the presence of acid-fast bacteria in the tissues of infected milkfish, confirming the occurrence of mycobacteriosis infection.</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8106,7 +8123,7 @@
           <t>Overall, the combination of Ziehl-Neelsen staining, biochemical testing like the catalase test, and evaluating growth in the presence of the Salt Tolerance Test provides a comprehensive approach for diagnosing and studying mycobacteriosis in cultivated milkfish, offering insights that can guide effective management strategies to control the spread of this disease in aquaculture system.</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="57" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8141,7 +8158,7 @@
           <t>Nine out of ten isolates exhibit quorum quenching activities by inhibiting the swarming motility of Pseudomonas aeruginosa.</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8176,7 +8193,7 @@
           <t>The inhibition activity of LAB isolates against the quorum sensing-mediated swarming motility in P. aeruginosa was due to strong antibacterial activity.</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8211,7 +8228,7 @@
           <t>T1 revealed that Zoletil® alone is not enough to fully induce Stage 3 anesthesia in zebrafish.</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8246,7 +8263,7 @@
           <t>However, when sodium bicarbonate was added, Stage 3 was achieved, while using only a small amount of Zoletil®.</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="57" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -8281,7 +8298,7 @@
           <t>On the other hand, the evaluation of retail egg vendors showed a major issue of reusing the egg trays across vendors which has been strongly linked to bacterial growth on eggshells, yolks and albumen, with p-values of 0.030 and 0.014, respectively.</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="56" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -8316,7 +8333,7 @@
           <t>Results indicated that most vendors lacked formal training in milk-handling (100 %) did not use refrigeration, new bottles, or any preservation methods (100%).</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8351,7 +8368,7 @@
           <t>Mean values for PCV, RBC, HGB, MCH, MCHC, MCV, WBC, neutrophils, eosinophils, lymphocytes, monocytes, basophils, potassium, magnesium, and calcium were not significantly different while mean values for sodium between male and female NZW rabbits were found to be statistically different (p&lt;0.05).</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8386,7 +8403,7 @@
           <t>A total of 181 microplastics were detected across all samples, wherein the concentration of microplastics was higher in Treatment 1 (74.03%).</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8421,7 +8438,7 @@
           <t>In general, lung samples were sensitive to all antibiotics except amoxicillin-clavulanic acid.</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8456,7 +8473,7 @@
           <t>In contrast, the data showed that lung and chick samples exhibited marked resistance.</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8491,7 +8508,7 @@
           <t>One way ANOVA was used and the differences between the groups were statistically significant.</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8526,7 +8543,7 @@
           <t>Results revealed that Treatment 3, with 40% concentration of Noni had the highest zone of inhibition in vitro with comparable antibacterial activity as the positive control against S. aureus.</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8561,7 +8578,7 @@
           <t>With the in vitro and in vivo results, Noni fruit ethanolic extract with 40% concentration has antibacterial property.</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F25" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8596,7 +8613,7 @@
           <t>Participants exhibited an overall moderate level of awareness (mean=3.30) on canine zoonotic diseases.</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8631,7 +8648,7 @@
           <t>Using Pearson’s correlation, significant associations (p&lt;0.05) were found between awareness on zoonotic diseases and sociodemographic factors, such as educational attainment (p-value=0.000), monthly income (p-value=0.007), and years of dog ownership (p-value=0.001).</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F27" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8666,7 +8683,7 @@
           <t>The results indicated that most respondents demonstrated high knowledge about rabies (69.3%), particularly regarding transmission and prevention, However, misconceptions persisted, notably about rabies’ incurability (39.8%) and the role of neutering in disease control (50.3%).</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8701,7 +8718,7 @@
           <t>Multiple linear regression analysis confirmed interrelationships among KAP dimensions, revealing that higher knowledge scores significantly predicted better preventive behaviors (p &lt; 0.001).</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F29" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8736,7 +8753,7 @@
           <t>Based on the results, there was no significant difference among the different methods of kuhol amino acid app in terms of plant height, weight of marketable and weight of non-marketable fruit, number of marketable and non-marketable fruits, and computed yield.</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8771,7 +8788,7 @@
           <t>Different methods of kuhol amino acid application influenced the plant height, weight of fruits, number of marketable and non-marketable fruits, and computed yield.</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8806,7 +8823,7 @@
           <t>The results of the study revealed the following: a significant difference was observed in the number of productive tillers, actual yield per sample area, and computed yield per ton/ha.</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8841,7 +8858,7 @@
           <t>In conclusion, T3: NPK+14-14-14 was the most compelling treatment among all treatments in terms of producing the highest number of productive tillers and obtaining the heaviest yield per ton/ha.</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
+      <c r="F33" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8876,7 +8893,7 @@
           <t>The results of the study revealed the following: No significant differences were observed in terms of mean initial weight (kg), mean final weight (kg), mean gain in weight (kg), mean DM intake (kg), or feed conversion ratio.</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -8911,7 +8928,7 @@
           <t>The student researcher concluded that T2 (20% GA Leaves + 40% Paragrass + 40% Concentrate Feeds) was the most compelling treatment among all treatments for the rabbits in terms of outperforming the data numerically.</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F35" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -8946,7 +8963,7 @@
           <t>But when it came to mean ultimate weight in the treated birds, the fermented okara extract had the biggest impact, resulting in the heaviest weight.</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="57" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -8981,7 +8998,7 @@
           <t>Additionally, the total return result showed a promising future for fermented okara extract at a level of 60 ml (166.00 PHP).</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F37" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -9016,7 +9033,7 @@
           <t>It was found to have a significant effect on the growth and germination rate of pigeon pea in terms of days to germinate, plant height, a number of leaves, and length of leaves.</t>
         </is>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="F38" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -9051,7 +9068,7 @@
           <t>Sulfuric was second in terms of the scarification method effectiveness for pigeon pea, The study treatments overall proclaimed a not significant results based from the analyzed data from each treatments except from these group of data such as from the length of leaves from week 2 and week 3 and the length of roots that are all expressed a highly significant results at 1% level and also the plant height from week 3 that also expressed a significant result at 5% level.</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F39" s="56" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -9086,7 +9103,7 @@
           <t>The results disclosed that the percentage of mortality and moisture content were statistically significant at 1% (P&lt;0.01) and (P&lt;0.05) level with 48 hours after the post-treatment.</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -9121,7 +9138,7 @@
           <t>However, mortality rate and moisture content were not significant after 6 hours and 24 hours.</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F41" s="56" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -9245,27 +9262,31 @@
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="49" t="n"/>
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>Acs1</t>
-        </is>
-      </c>
-      <c r="C5" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D5" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="53" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="49" t="n"/>
-      <c r="H5" s="49" t="n"/>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G5" s="59" t="n"/>
+      <c r="H5" s="59" t="n"/>
       <c r="I5" s="49" t="n"/>
       <c r="J5" s="49" t="n"/>
       <c r="K5" s="49" t="n"/>
@@ -9273,31 +9294,31 @@
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="49" t="n"/>
-      <c r="B6" s="54" t="inlineStr">
-        <is>
-          <t>Acs10</t>
-        </is>
-      </c>
-      <c r="C6" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D6" s="54" t="n">
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="54" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F6" s="54" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G6" s="49" t="n"/>
-      <c r="H6" s="49" t="n"/>
+      <c r="E6" s="60" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>no zone of inhibition / did not possess</t>
+        </is>
+      </c>
+      <c r="G6" s="61" t="n"/>
+      <c r="H6" s="61" t="n"/>
       <c r="I6" s="49" t="n"/>
       <c r="J6" s="49" t="n"/>
       <c r="K6" s="49" t="n"/>
@@ -9305,31 +9326,27 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="49" t="n"/>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>Acs2</t>
-        </is>
-      </c>
-      <c r="C7" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D7" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="53" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F7" s="53" t="inlineStr">
-        <is>
-          <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
-        </is>
-      </c>
-      <c r="G7" s="49" t="n"/>
-      <c r="H7" s="49" t="n"/>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="n"/>
+      <c r="G7" s="59" t="n"/>
+      <c r="H7" s="59" t="n"/>
       <c r="I7" s="49" t="n"/>
       <c r="J7" s="49" t="n"/>
       <c r="K7" s="49" t="n"/>
@@ -9337,31 +9354,27 @@
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="49" t="n"/>
-      <c r="B8" s="54" t="inlineStr">
-        <is>
-          <t>Acs3</t>
-        </is>
-      </c>
-      <c r="C8" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D8" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="54" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F8" s="54" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G8" s="49" t="n"/>
-      <c r="H8" s="49" t="n"/>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="61" t="n"/>
+      <c r="H8" s="61" t="n"/>
       <c r="I8" s="49" t="n"/>
       <c r="J8" s="49" t="n"/>
       <c r="K8" s="49" t="n"/>
@@ -9369,31 +9382,31 @@
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="49" t="n"/>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>Acs4</t>
-        </is>
-      </c>
-      <c r="C9" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D9" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="53" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F9" s="53" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G9" s="49" t="n"/>
-      <c r="H9" s="49" t="n"/>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+      <c r="G9" s="59" t="n"/>
+      <c r="H9" s="59" t="n"/>
       <c r="I9" s="49" t="n"/>
       <c r="J9" s="49" t="n"/>
       <c r="K9" s="49" t="n"/>
@@ -9401,31 +9414,27 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="49" t="n"/>
-      <c r="B10" s="54" t="inlineStr">
-        <is>
-          <t>Acs5</t>
-        </is>
-      </c>
-      <c r="C10" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D10" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="54" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F10" s="54" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-      <c r="G10" s="49" t="n"/>
-      <c r="H10" s="49" t="n"/>
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="61" t="n"/>
+      <c r="H10" s="61" t="n"/>
       <c r="I10" s="49" t="n"/>
       <c r="J10" s="49" t="n"/>
       <c r="K10" s="49" t="n"/>
@@ -9433,27 +9442,27 @@
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="49" t="n"/>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>Acs6</t>
-        </is>
-      </c>
-      <c r="C11" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D11" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="53" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F11" s="53" t="n"/>
-      <c r="G11" s="49" t="n"/>
-      <c r="H11" s="49" t="n"/>
+      <c r="F11" s="58" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
       <c r="I11" s="49" t="n"/>
       <c r="J11" s="49" t="n"/>
       <c r="K11" s="49" t="n"/>
@@ -9461,31 +9470,31 @@
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="49" t="n"/>
-      <c r="B12" s="54" t="inlineStr">
-        <is>
-          <t>Acs7</t>
-        </is>
-      </c>
-      <c r="C12" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D12" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="54" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F12" s="54" t="inlineStr">
+      <c r="F12" s="60" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-      <c r="G12" s="49" t="n"/>
-      <c r="H12" s="49" t="n"/>
+      <c r="G12" s="61" t="n"/>
+      <c r="H12" s="61" t="n"/>
       <c r="I12" s="49" t="n"/>
       <c r="J12" s="49" t="n"/>
       <c r="K12" s="49" t="n"/>
@@ -9493,31 +9502,31 @@
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="49" t="n"/>
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t>Acs8</t>
-        </is>
-      </c>
-      <c r="C13" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D13" s="53" t="n">
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="58" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F13" s="53" t="inlineStr">
+      <c r="F13" s="58" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-      <c r="G13" s="49" t="n"/>
-      <c r="H13" s="49" t="n"/>
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="59" t="n"/>
       <c r="I13" s="49" t="n"/>
       <c r="J13" s="49" t="n"/>
       <c r="K13" s="49" t="n"/>
@@ -9525,31 +9534,27 @@
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="49" t="n"/>
-      <c r="B14" s="54" t="inlineStr">
-        <is>
-          <t>Acs9</t>
-        </is>
-      </c>
-      <c r="C14" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D14" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="54" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F14" s="54" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G14" s="49" t="n"/>
-      <c r="H14" s="49" t="n"/>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="61" t="n"/>
+      <c r="H14" s="61" t="n"/>
       <c r="I14" s="49" t="n"/>
       <c r="J14" s="49" t="n"/>
       <c r="K14" s="49" t="n"/>
@@ -9557,31 +9562,31 @@
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="49" t="n"/>
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t>Aas1</t>
-        </is>
-      </c>
-      <c r="C15" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D15" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="53" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F15" s="53" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G15" s="49" t="n"/>
-      <c r="H15" s="49" t="n"/>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="C15" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D15" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="58" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F15" s="58" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+      <c r="G15" s="59" t="n"/>
+      <c r="H15" s="59" t="n"/>
       <c r="I15" s="49" t="n"/>
       <c r="J15" s="49" t="n"/>
       <c r="K15" s="49" t="n"/>
@@ -9589,31 +9594,27 @@
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="49" t="n"/>
-      <c r="B16" s="54" t="inlineStr">
-        <is>
-          <t>Aas10</t>
-        </is>
-      </c>
-      <c r="C16" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D16" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="54" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F16" s="54" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-      <c r="G16" s="49" t="n"/>
-      <c r="H16" s="49" t="n"/>
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="n"/>
+      <c r="G16" s="61" t="n"/>
+      <c r="H16" s="61" t="n"/>
       <c r="I16" s="49" t="n"/>
       <c r="J16" s="49" t="n"/>
       <c r="K16" s="49" t="n"/>
@@ -9621,27 +9622,27 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="49" t="n"/>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>Aas2</t>
-        </is>
-      </c>
-      <c r="C17" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D17" s="53" t="n">
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D17" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="53" t="inlineStr">
+      <c r="E17" s="58" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F17" s="53" t="n"/>
-      <c r="G17" s="49" t="n"/>
-      <c r="H17" s="49" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="59" t="n"/>
+      <c r="H17" s="59" t="n"/>
       <c r="I17" s="49" t="n"/>
       <c r="J17" s="49" t="n"/>
       <c r="K17" s="49" t="n"/>
@@ -9649,31 +9650,27 @@
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="49" t="n"/>
-      <c r="B18" s="54" t="inlineStr">
-        <is>
-          <t>Aas3</t>
-        </is>
-      </c>
-      <c r="C18" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D18" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="54" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F18" s="54" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-      <c r="G18" s="49" t="n"/>
-      <c r="H18" s="49" t="n"/>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="60" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="n"/>
+      <c r="G18" s="61" t="n"/>
+      <c r="H18" s="61" t="n"/>
       <c r="I18" s="49" t="n"/>
       <c r="J18" s="49" t="n"/>
       <c r="K18" s="49" t="n"/>
@@ -9681,31 +9678,27 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="49" t="n"/>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>Aas4</t>
-        </is>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D19" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="53" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F19" s="53" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G19" s="49" t="n"/>
-      <c r="H19" s="49" t="n"/>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D19" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="58" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="59" t="n"/>
+      <c r="H19" s="59" t="n"/>
       <c r="I19" s="49" t="n"/>
       <c r="J19" s="49" t="n"/>
       <c r="K19" s="49" t="n"/>
@@ -9713,31 +9706,31 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="49" t="n"/>
-      <c r="B20" s="54" t="inlineStr">
-        <is>
-          <t>Aas5</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F20" s="54" t="inlineStr">
-        <is>
-          <t>sig language</t>
-        </is>
-      </c>
-      <c r="G20" s="49" t="n"/>
-      <c r="H20" s="49" t="n"/>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="60" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="n"/>
+      <c r="H20" s="61" t="n"/>
       <c r="I20" s="49" t="n"/>
       <c r="J20" s="49" t="n"/>
       <c r="K20" s="49" t="n"/>
@@ -9745,31 +9738,27 @@
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="49" t="n"/>
-      <c r="B21" s="53" t="inlineStr">
-        <is>
-          <t>Aas6</t>
-        </is>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="53" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F21" s="53" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G21" s="49" t="n"/>
-      <c r="H21" s="49" t="n"/>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D21" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="58" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="59" t="n"/>
+      <c r="H21" s="59" t="n"/>
       <c r="I21" s="49" t="n"/>
       <c r="J21" s="49" t="n"/>
       <c r="K21" s="49" t="n"/>
@@ -9777,31 +9766,31 @@
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="49" t="n"/>
-      <c r="B22" s="54" t="inlineStr">
-        <is>
-          <t>Aas7</t>
-        </is>
-      </c>
-      <c r="C22" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="54" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F22" s="54" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G22" s="49" t="n"/>
-      <c r="H22" s="49" t="n"/>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="60" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>diagnostic</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="n"/>
+      <c r="H22" s="61" t="n"/>
       <c r="I22" s="49" t="n"/>
       <c r="J22" s="49" t="n"/>
       <c r="K22" s="49" t="n"/>
@@ -9809,27 +9798,27 @@
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="49" t="n"/>
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="C23" s="53" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D23" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="53" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F23" s="53" t="n"/>
-      <c r="G23" s="49" t="n"/>
-      <c r="H23" s="49" t="n"/>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C23" s="58" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D23" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="58" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="F23" s="58" t="n"/>
+      <c r="G23" s="59" t="n"/>
+      <c r="H23" s="59" t="n"/>
       <c r="I23" s="49" t="n"/>
       <c r="J23" s="49" t="n"/>
       <c r="K23" s="49" t="n"/>
@@ -9837,31 +9826,31 @@
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="49" t="n"/>
-      <c r="B24" s="54" t="inlineStr">
-        <is>
-          <t>Aas9</t>
-        </is>
-      </c>
-      <c r="C24" s="54" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="54" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C24" s="60" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D24" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F24" s="54" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-      <c r="G24" s="49" t="n"/>
-      <c r="H24" s="49" t="n"/>
+      <c r="F24" s="60" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G24" s="61" t="n"/>
+      <c r="H24" s="61" t="n"/>
       <c r="I24" s="49" t="n"/>
       <c r="J24" s="49" t="n"/>
       <c r="K24" s="49" t="n"/>
@@ -9869,27 +9858,27 @@
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="49" t="n"/>
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="58" t="inlineStr">
         <is>
           <t>VM1</t>
         </is>
       </c>
-      <c r="C25" s="53" t="inlineStr">
+      <c r="C25" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D25" s="53" t="n">
+      <c r="D25" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="53" t="inlineStr">
+      <c r="E25" s="58" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F25" s="53" t="n"/>
-      <c r="G25" s="49" t="n"/>
-      <c r="H25" s="49" t="n"/>
+      <c r="F25" s="58" t="n"/>
+      <c r="G25" s="59" t="n"/>
+      <c r="H25" s="59" t="n"/>
       <c r="I25" s="49" t="n"/>
       <c r="J25" s="49" t="n"/>
       <c r="K25" s="49" t="n"/>
@@ -9897,27 +9886,27 @@
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="49" t="n"/>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>VM2</t>
         </is>
       </c>
-      <c r="C26" s="54" t="inlineStr">
+      <c r="C26" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D26" s="54" t="n">
+      <c r="D26" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="54" t="inlineStr">
+      <c r="E26" s="60" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="49" t="n"/>
-      <c r="H26" s="49" t="n"/>
+      <c r="F26" s="60" t="n"/>
+      <c r="G26" s="61" t="n"/>
+      <c r="H26" s="61" t="n"/>
       <c r="I26" s="49" t="n"/>
       <c r="J26" s="49" t="n"/>
       <c r="K26" s="49" t="n"/>
@@ -9925,31 +9914,31 @@
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="49" t="n"/>
-      <c r="B27" s="53" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>VM3</t>
         </is>
       </c>
-      <c r="C27" s="53" t="inlineStr">
+      <c r="C27" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D27" s="53" t="n">
+      <c r="D27" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="53" t="inlineStr">
+      <c r="E27" s="58" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F27" s="53" t="inlineStr">
+      <c r="F27" s="58" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-      <c r="G27" s="49" t="n"/>
-      <c r="H27" s="49" t="n"/>
+      <c r="G27" s="59" t="n"/>
+      <c r="H27" s="59" t="n"/>
       <c r="I27" s="49" t="n"/>
       <c r="J27" s="49" t="n"/>
       <c r="K27" s="49" t="n"/>
@@ -9957,31 +9946,31 @@
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="49" t="n"/>
-      <c r="B28" s="54" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>VM4</t>
         </is>
       </c>
-      <c r="C28" s="54" t="inlineStr">
+      <c r="C28" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D28" s="54" t="n">
+      <c r="D28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="54" t="inlineStr">
+      <c r="E28" s="60" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F28" s="54" t="inlineStr">
+      <c r="F28" s="60" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-      <c r="G28" s="49" t="n"/>
-      <c r="H28" s="49" t="n"/>
+      <c r="G28" s="61" t="n"/>
+      <c r="H28" s="61" t="n"/>
       <c r="I28" s="49" t="n"/>
       <c r="J28" s="49" t="n"/>
       <c r="K28" s="49" t="n"/>
@@ -9989,27 +9978,27 @@
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="49" t="n"/>
-      <c r="B29" s="53" t="inlineStr">
+      <c r="B29" s="58" t="inlineStr">
         <is>
           <t>VM5</t>
         </is>
       </c>
-      <c r="C29" s="53" t="inlineStr">
+      <c r="C29" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D29" s="53" t="n">
+      <c r="D29" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="53" t="inlineStr">
+      <c r="E29" s="58" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F29" s="53" t="n"/>
-      <c r="G29" s="49" t="n"/>
-      <c r="H29" s="49" t="n"/>
+      <c r="F29" s="58" t="n"/>
+      <c r="G29" s="59" t="n"/>
+      <c r="H29" s="59" t="n"/>
       <c r="I29" s="49" t="n"/>
       <c r="J29" s="49" t="n"/>
       <c r="K29" s="49" t="n"/>
@@ -10017,31 +10006,31 @@
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="49" t="n"/>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>VM6</t>
         </is>
       </c>
-      <c r="C30" s="54" t="inlineStr">
+      <c r="C30" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D30" s="54" t="n">
+      <c r="D30" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="54" t="inlineStr">
+      <c r="E30" s="60" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F30" s="54" t="inlineStr">
+      <c r="F30" s="60" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-      <c r="G30" s="49" t="n"/>
-      <c r="H30" s="49" t="n"/>
+      <c r="G30" s="61" t="n"/>
+      <c r="H30" s="61" t="n"/>
       <c r="I30" s="49" t="n"/>
       <c r="J30" s="49" t="n"/>
       <c r="K30" s="49" t="n"/>
@@ -10049,31 +10038,31 @@
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="49" t="n"/>
-      <c r="B31" s="53" t="inlineStr">
+      <c r="B31" s="58" t="inlineStr">
         <is>
           <t>VM7</t>
         </is>
       </c>
-      <c r="C31" s="53" t="inlineStr">
+      <c r="C31" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D31" s="53" t="n">
+      <c r="D31" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="53" t="inlineStr">
+      <c r="E31" s="58" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F31" s="53" t="inlineStr">
+      <c r="F31" s="58" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-      <c r="G31" s="49" t="n"/>
-      <c r="H31" s="49" t="n"/>
+      <c r="G31" s="59" t="n"/>
+      <c r="H31" s="59" t="n"/>
       <c r="I31" s="49" t="n"/>
       <c r="J31" s="49" t="n"/>
       <c r="K31" s="49" t="n"/>
@@ -10081,27 +10070,27 @@
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="49" t="n"/>
-      <c r="B32" s="54" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>VM8</t>
         </is>
       </c>
-      <c r="C32" s="54" t="inlineStr">
+      <c r="C32" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D32" s="54" t="n">
+      <c r="D32" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="54" t="inlineStr">
+      <c r="E32" s="60" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F32" s="54" t="n"/>
-      <c r="G32" s="49" t="n"/>
-      <c r="H32" s="49" t="n"/>
+      <c r="F32" s="60" t="n"/>
+      <c r="G32" s="61" t="n"/>
+      <c r="H32" s="61" t="n"/>
       <c r="I32" s="49" t="n"/>
       <c r="J32" s="49" t="n"/>
       <c r="K32" s="49" t="n"/>
@@ -10109,31 +10098,31 @@
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="49" t="n"/>
-      <c r="B33" s="53" t="inlineStr">
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t>VM9</t>
         </is>
       </c>
-      <c r="C33" s="53" t="inlineStr">
+      <c r="C33" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D33" s="53" t="n">
+      <c r="D33" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="53" t="inlineStr">
+      <c r="E33" s="58" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F33" s="53" t="inlineStr">
+      <c r="F33" s="58" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-      <c r="G33" s="49" t="n"/>
-      <c r="H33" s="49" t="n"/>
+      <c r="G33" s="59" t="n"/>
+      <c r="H33" s="59" t="n"/>
       <c r="I33" s="49" t="n"/>
       <c r="J33" s="49" t="n"/>
       <c r="K33" s="49" t="n"/>
@@ -10141,31 +10130,31 @@
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="49" t="n"/>
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>VM10</t>
         </is>
       </c>
-      <c r="C34" s="54" t="inlineStr">
+      <c r="C34" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D34" s="54" t="n">
+      <c r="D34" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="54" t="inlineStr">
+      <c r="E34" s="60" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F34" s="54" t="inlineStr">
+      <c r="F34" s="60" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-      <c r="G34" s="49" t="n"/>
-      <c r="H34" s="49" t="n"/>
+      <c r="G34" s="61" t="n"/>
+      <c r="H34" s="61" t="n"/>
       <c r="I34" s="49" t="n"/>
       <c r="J34" s="49" t="n"/>
       <c r="K34" s="49" t="n"/>
@@ -10173,27 +10162,27 @@
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="49" t="n"/>
-      <c r="B35" s="53" t="inlineStr">
+      <c r="B35" s="58" t="inlineStr">
         <is>
           <t>VM11</t>
         </is>
       </c>
-      <c r="C35" s="53" t="inlineStr">
+      <c r="C35" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D35" s="53" t="n">
+      <c r="D35" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="53" t="inlineStr">
+      <c r="E35" s="58" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F35" s="53" t="n"/>
-      <c r="G35" s="49" t="n"/>
-      <c r="H35" s="49" t="n"/>
+      <c r="F35" s="58" t="n"/>
+      <c r="G35" s="59" t="n"/>
+      <c r="H35" s="59" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="49" t="n"/>
       <c r="K35" s="49" t="n"/>
@@ -10201,31 +10190,31 @@
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="49" t="n"/>
-      <c r="B36" s="54" t="inlineStr">
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>VM12</t>
         </is>
       </c>
-      <c r="C36" s="54" t="inlineStr">
+      <c r="C36" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D36" s="54" t="n">
+      <c r="D36" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="54" t="inlineStr">
+      <c r="E36" s="60" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F36" s="54" t="inlineStr">
+      <c r="F36" s="60" t="inlineStr">
         <is>
           <t>diagnostic</t>
         </is>
       </c>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
+      <c r="G36" s="61" t="n"/>
+      <c r="H36" s="61" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="49" t="n"/>
       <c r="K36" s="49" t="n"/>
@@ -10233,31 +10222,31 @@
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="49" t="n"/>
-      <c r="B37" s="53" t="inlineStr">
+      <c r="B37" s="58" t="inlineStr">
         <is>
           <t>VM13</t>
         </is>
       </c>
-      <c r="C37" s="53" t="inlineStr">
+      <c r="C37" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D37" s="53" t="n">
+      <c r="D37" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="53" t="inlineStr">
+      <c r="E37" s="58" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F37" s="53" t="inlineStr">
+      <c r="F37" s="58" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
+      <c r="G37" s="59" t="n"/>
+      <c r="H37" s="59" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="49" t="n"/>
       <c r="K37" s="49" t="n"/>
@@ -10265,27 +10254,27 @@
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="49" t="n"/>
-      <c r="B38" s="54" t="inlineStr">
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>VM14</t>
         </is>
       </c>
-      <c r="C38" s="54" t="inlineStr">
+      <c r="C38" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D38" s="54" t="n">
+      <c r="D38" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="54" t="inlineStr">
+      <c r="E38" s="60" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F38" s="54" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
+      <c r="F38" s="60" t="n"/>
+      <c r="G38" s="61" t="n"/>
+      <c r="H38" s="61" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="49" t="n"/>
       <c r="K38" s="49" t="n"/>
@@ -10293,27 +10282,27 @@
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="49" t="n"/>
-      <c r="B39" s="53" t="inlineStr">
+      <c r="B39" s="58" t="inlineStr">
         <is>
           <t>VM15</t>
         </is>
       </c>
-      <c r="C39" s="53" t="inlineStr">
+      <c r="C39" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D39" s="53" t="n">
+      <c r="D39" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="53" t="inlineStr">
+      <c r="E39" s="58" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F39" s="53" t="n"/>
-      <c r="G39" s="49" t="n"/>
-      <c r="H39" s="49" t="n"/>
+      <c r="F39" s="58" t="n"/>
+      <c r="G39" s="59" t="n"/>
+      <c r="H39" s="59" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="49" t="n"/>
       <c r="K39" s="49" t="n"/>
@@ -10321,31 +10310,31 @@
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="49" t="n"/>
-      <c r="B40" s="54" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>VM16</t>
         </is>
       </c>
-      <c r="C40" s="54" t="inlineStr">
+      <c r="C40" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D40" s="54" t="n">
+      <c r="D40" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="54" t="inlineStr">
+      <c r="E40" s="60" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F40" s="54" t="inlineStr">
+      <c r="F40" s="60" t="inlineStr">
         <is>
           <t>NS language; sig language</t>
         </is>
       </c>
-      <c r="G40" s="49" t="n"/>
-      <c r="H40" s="49" t="n"/>
+      <c r="G40" s="61" t="n"/>
+      <c r="H40" s="61" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="49" t="n"/>
       <c r="K40" s="49" t="n"/>
@@ -10353,31 +10342,31 @@
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="49" t="n"/>
-      <c r="B41" s="53" t="inlineStr">
+      <c r="B41" s="58" t="inlineStr">
         <is>
           <t>VM17</t>
         </is>
       </c>
-      <c r="C41" s="53" t="inlineStr">
+      <c r="C41" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D41" s="53" t="n">
+      <c r="D41" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="53" t="inlineStr">
+      <c r="E41" s="58" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F41" s="53" t="inlineStr">
+      <c r="F41" s="58" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-      <c r="G41" s="49" t="n"/>
-      <c r="H41" s="49" t="n"/>
+      <c r="G41" s="59" t="n"/>
+      <c r="H41" s="59" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="49" t="n"/>
       <c r="K41" s="49" t="n"/>
@@ -10385,31 +10374,31 @@
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="49" t="n"/>
-      <c r="B42" s="54" t="inlineStr">
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>VM18</t>
         </is>
       </c>
-      <c r="C42" s="54" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D42" s="54" t="n">
+      <c r="D42" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="54" t="inlineStr">
+      <c r="E42" s="60" t="inlineStr">
         <is>
           <t>Continuous</t>
         </is>
       </c>
-      <c r="F42" s="54" t="inlineStr">
+      <c r="F42" s="60" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-      <c r="G42" s="49" t="n"/>
-      <c r="H42" s="49" t="n"/>
+      <c r="G42" s="61" t="n"/>
+      <c r="H42" s="61" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="49" t="n"/>
       <c r="K42" s="49" t="n"/>
@@ -10417,27 +10406,27 @@
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="49" t="n"/>
-      <c r="B43" s="53" t="inlineStr">
+      <c r="B43" s="58" t="inlineStr">
         <is>
           <t>VM19</t>
         </is>
       </c>
-      <c r="C43" s="53" t="inlineStr">
+      <c r="C43" s="58" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D43" s="53" t="n">
+      <c r="D43" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="53" t="inlineStr">
+      <c r="E43" s="58" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F43" s="53" t="n"/>
-      <c r="G43" s="49" t="n"/>
-      <c r="H43" s="49" t="n"/>
+      <c r="F43" s="58" t="n"/>
+      <c r="G43" s="59" t="n"/>
+      <c r="H43" s="59" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="49" t="n"/>
       <c r="K43" s="49" t="n"/>
@@ -10445,31 +10434,31 @@
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="49" t="n"/>
-      <c r="B44" s="54" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>VM20</t>
         </is>
       </c>
-      <c r="C44" s="54" t="inlineStr">
+      <c r="C44" s="60" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="D44" s="54" t="n">
+      <c r="D44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="54" t="inlineStr">
+      <c r="E44" s="60" t="inlineStr">
         <is>
           <t>Binary</t>
         </is>
       </c>
-      <c r="F44" s="54" t="inlineStr">
+      <c r="F44" s="60" t="inlineStr">
         <is>
           <t>sig language</t>
         </is>
       </c>
-      <c r="G44" s="49" t="n"/>
-      <c r="H44" s="49" t="n"/>
+      <c r="G44" s="61" t="n"/>
+      <c r="H44" s="61" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="49" t="n"/>
       <c r="K44" s="49" t="n"/>
@@ -10477,31 +10466,27 @@
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="49" t="n"/>
-      <c r="B45" s="53" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C45" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D45" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="53" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F45" s="53" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G45" s="49" t="n"/>
-      <c r="H45" s="49" t="n"/>
+      <c r="B45" s="58" t="inlineStr">
+        <is>
+          <t>Acs1</t>
+        </is>
+      </c>
+      <c r="C45" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D45" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="58" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F45" s="58" t="n"/>
+      <c r="G45" s="59" t="n"/>
+      <c r="H45" s="59" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="49" t="n"/>
       <c r="K45" s="49" t="n"/>
@@ -10509,31 +10494,31 @@
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="49" t="n"/>
-      <c r="B46" s="54" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C46" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D46" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="54" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F46" s="54" t="inlineStr">
-        <is>
-          <t>no zone of inhibition / did not possess</t>
-        </is>
-      </c>
-      <c r="G46" s="49" t="n"/>
-      <c r="H46" s="49" t="n"/>
+      <c r="B46" s="60" t="inlineStr">
+        <is>
+          <t>Acs2</t>
+        </is>
+      </c>
+      <c r="C46" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D46" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="60" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F46" s="60" t="inlineStr">
+        <is>
+          <t>NS language; rescue-hedging pattern (sig not observed but potential benefits)</t>
+        </is>
+      </c>
+      <c r="G46" s="61" t="n"/>
+      <c r="H46" s="61" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="49" t="n"/>
       <c r="K46" s="49" t="n"/>
@@ -10541,27 +10526,31 @@
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="49" t="n"/>
-      <c r="B47" s="53" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="C47" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D47" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="53" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F47" s="53" t="n"/>
-      <c r="G47" s="49" t="n"/>
-      <c r="H47" s="49" t="n"/>
+      <c r="B47" s="58" t="inlineStr">
+        <is>
+          <t>Acs3</t>
+        </is>
+      </c>
+      <c r="C47" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D47" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F47" s="58" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G47" s="59" t="n"/>
+      <c r="H47" s="59" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="49" t="n"/>
       <c r="K47" s="49" t="n"/>
@@ -10569,27 +10558,31 @@
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="49" t="n"/>
-      <c r="B48" s="54" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C48" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D48" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="54" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F48" s="54" t="n"/>
-      <c r="G48" s="49" t="n"/>
-      <c r="H48" s="49" t="n"/>
+      <c r="B48" s="60" t="inlineStr">
+        <is>
+          <t>Acs4</t>
+        </is>
+      </c>
+      <c r="C48" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D48" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="60" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F48" s="60" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G48" s="61" t="n"/>
+      <c r="H48" s="61" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="49" t="n"/>
       <c r="K48" s="49" t="n"/>
@@ -10597,31 +10590,31 @@
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="49" t="n"/>
-      <c r="B49" s="53" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="C49" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D49" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="53" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="F49" s="53" t="inlineStr">
-        <is>
-          <t>NS language; sig language</t>
-        </is>
-      </c>
-      <c r="G49" s="49" t="n"/>
-      <c r="H49" s="49" t="n"/>
+      <c r="B49" s="58" t="inlineStr">
+        <is>
+          <t>Acs5</t>
+        </is>
+      </c>
+      <c r="C49" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D49" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="58" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F49" s="58" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+      <c r="G49" s="59" t="n"/>
+      <c r="H49" s="59" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="49" t="n"/>
       <c r="K49" s="49" t="n"/>
@@ -10629,27 +10622,27 @@
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="49" t="n"/>
-      <c r="B50" s="54" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C50" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D50" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="54" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F50" s="54" t="n"/>
-      <c r="G50" s="49" t="n"/>
-      <c r="H50" s="49" t="n"/>
+      <c r="B50" s="60" t="inlineStr">
+        <is>
+          <t>Acs6</t>
+        </is>
+      </c>
+      <c r="C50" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D50" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F50" s="60" t="n"/>
+      <c r="G50" s="61" t="n"/>
+      <c r="H50" s="61" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="49" t="n"/>
       <c r="K50" s="49" t="n"/>
@@ -10657,27 +10650,31 @@
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="49" t="n"/>
-      <c r="B51" s="53" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="C51" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D51" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="53" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F51" s="53" t="n"/>
-      <c r="G51" s="49" t="n"/>
-      <c r="H51" s="49" t="n"/>
+      <c r="B51" s="58" t="inlineStr">
+        <is>
+          <t>Acs7</t>
+        </is>
+      </c>
+      <c r="C51" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D51" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F51" s="58" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G51" s="59" t="n"/>
+      <c r="H51" s="59" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="49" t="n"/>
       <c r="K51" s="49" t="n"/>
@@ -10685,31 +10682,31 @@
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="49" t="n"/>
-      <c r="B52" s="54" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="C52" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D52" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="54" t="inlineStr">
+      <c r="B52" s="60" t="inlineStr">
+        <is>
+          <t>Acs8</t>
+        </is>
+      </c>
+      <c r="C52" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D52" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="60" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F52" s="54" t="inlineStr">
+      <c r="F52" s="60" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-      <c r="G52" s="49" t="n"/>
-      <c r="H52" s="49" t="n"/>
+      <c r="G52" s="61" t="n"/>
+      <c r="H52" s="61" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="49" t="n"/>
       <c r="K52" s="49" t="n"/>
@@ -10717,31 +10714,31 @@
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="49" t="n"/>
-      <c r="B53" s="53" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="C53" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D53" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="53" t="inlineStr">
+      <c r="B53" s="58" t="inlineStr">
+        <is>
+          <t>Acs9</t>
+        </is>
+      </c>
+      <c r="C53" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D53" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="58" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F53" s="53" t="inlineStr">
+      <c r="F53" s="58" t="inlineStr">
         <is>
           <t>NS language</t>
         </is>
       </c>
-      <c r="G53" s="49" t="n"/>
-      <c r="H53" s="49" t="n"/>
+      <c r="G53" s="59" t="n"/>
+      <c r="H53" s="59" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="49" t="n"/>
       <c r="K53" s="49" t="n"/>
@@ -10749,27 +10746,31 @@
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="49" t="n"/>
-      <c r="B54" s="54" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C54" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D54" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="54" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F54" s="54" t="n"/>
-      <c r="G54" s="49" t="n"/>
-      <c r="H54" s="49" t="n"/>
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t>Acs10</t>
+        </is>
+      </c>
+      <c r="C54" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D54" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="60" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F54" s="60" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G54" s="61" t="n"/>
+      <c r="H54" s="61" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="49" t="n"/>
       <c r="K54" s="49" t="n"/>
@@ -10777,31 +10778,31 @@
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="49" t="n"/>
-      <c r="B55" s="53" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="C55" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D55" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="53" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F55" s="53" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-      <c r="G55" s="49" t="n"/>
-      <c r="H55" s="49" t="n"/>
+      <c r="B55" s="58" t="inlineStr">
+        <is>
+          <t>Aas1</t>
+        </is>
+      </c>
+      <c r="C55" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D55" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F55" s="58" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G55" s="59" t="n"/>
+      <c r="H55" s="59" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="49" t="n"/>
       <c r="K55" s="49" t="n"/>
@@ -10809,27 +10810,27 @@
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="49" t="n"/>
-      <c r="B56" s="54" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
-      </c>
-      <c r="C56" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D56" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="54" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F56" s="54" t="n"/>
-      <c r="G56" s="49" t="n"/>
-      <c r="H56" s="49" t="n"/>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>Aas2</t>
+        </is>
+      </c>
+      <c r="C56" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D56" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="60" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F56" s="60" t="n"/>
+      <c r="G56" s="61" t="n"/>
+      <c r="H56" s="61" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="49" t="n"/>
       <c r="K56" s="49" t="n"/>
@@ -10837,27 +10838,31 @@
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="49" t="n"/>
-      <c r="B57" s="53" t="inlineStr">
-        <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="C57" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D57" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="53" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="F57" s="53" t="n"/>
-      <c r="G57" s="49" t="n"/>
-      <c r="H57" s="49" t="n"/>
+      <c r="B57" s="58" t="inlineStr">
+        <is>
+          <t>Aas3</t>
+        </is>
+      </c>
+      <c r="C57" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D57" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F57" s="58" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+      <c r="G57" s="59" t="n"/>
+      <c r="H57" s="59" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="49" t="n"/>
       <c r="K57" s="49" t="n"/>
@@ -10865,27 +10870,31 @@
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="49" t="n"/>
-      <c r="B58" s="54" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="C58" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D58" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" s="54" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="F58" s="54" t="n"/>
-      <c r="G58" s="49" t="n"/>
-      <c r="H58" s="49" t="n"/>
+      <c r="B58" s="60" t="inlineStr">
+        <is>
+          <t>Aas4</t>
+        </is>
+      </c>
+      <c r="C58" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D58" s="60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="60" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F58" s="60" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G58" s="61" t="n"/>
+      <c r="H58" s="61" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="49" t="n"/>
       <c r="K58" s="49" t="n"/>
@@ -10893,27 +10902,31 @@
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="49" t="n"/>
-      <c r="B59" s="53" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
-      </c>
-      <c r="C59" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D59" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F59" s="53" t="n"/>
-      <c r="G59" s="49" t="n"/>
-      <c r="H59" s="49" t="n"/>
+      <c r="B59" s="58" t="inlineStr">
+        <is>
+          <t>Aas5</t>
+        </is>
+      </c>
+      <c r="C59" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D59" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="58" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="F59" s="58" t="inlineStr">
+        <is>
+          <t>sig language</t>
+        </is>
+      </c>
+      <c r="G59" s="59" t="n"/>
+      <c r="H59" s="59" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="49" t="n"/>
       <c r="K59" s="49" t="n"/>
@@ -10921,31 +10934,31 @@
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="49" t="n"/>
-      <c r="B60" s="54" t="inlineStr">
-        <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="C60" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D60" s="54" t="n">
-        <v>5</v>
-      </c>
-      <c r="E60" s="54" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F60" s="54" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-      <c r="G60" s="49" t="n"/>
-      <c r="H60" s="49" t="n"/>
+      <c r="B60" s="60" t="inlineStr">
+        <is>
+          <t>Aas6</t>
+        </is>
+      </c>
+      <c r="C60" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D60" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="60" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F60" s="60" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G60" s="61" t="n"/>
+      <c r="H60" s="61" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="49" t="n"/>
       <c r="K60" s="49" t="n"/>
@@ -10953,27 +10966,31 @@
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="49" t="n"/>
-      <c r="B61" s="53" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C61" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D61" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="53" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F61" s="53" t="n"/>
-      <c r="G61" s="49" t="n"/>
-      <c r="H61" s="49" t="n"/>
+      <c r="B61" s="58" t="inlineStr">
+        <is>
+          <t>Aas7</t>
+        </is>
+      </c>
+      <c r="C61" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D61" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F61" s="58" t="inlineStr">
+        <is>
+          <t>NS language</t>
+        </is>
+      </c>
+      <c r="G61" s="59" t="n"/>
+      <c r="H61" s="59" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="49" t="n"/>
       <c r="K61" s="49" t="n"/>
@@ -10981,31 +10998,27 @@
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="49" t="n"/>
-      <c r="B62" s="54" t="inlineStr">
-        <is>
-          <t>B18</t>
-        </is>
-      </c>
-      <c r="C62" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D62" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="54" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F62" s="54" t="inlineStr">
-        <is>
-          <t>diagnostic</t>
-        </is>
-      </c>
-      <c r="G62" s="49" t="n"/>
-      <c r="H62" s="49" t="n"/>
+      <c r="B62" s="60" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C62" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D62" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="60" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F62" s="60" t="n"/>
+      <c r="G62" s="61" t="n"/>
+      <c r="H62" s="61" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="49" t="n"/>
       <c r="K62" s="49" t="n"/>
@@ -11013,27 +11026,31 @@
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="49" t="n"/>
-      <c r="B63" s="53" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="C63" s="53" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D63" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="53" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="F63" s="53" t="n"/>
-      <c r="G63" s="49" t="n"/>
-      <c r="H63" s="49" t="n"/>
+      <c r="B63" s="58" t="inlineStr">
+        <is>
+          <t>Aas9</t>
+        </is>
+      </c>
+      <c r="C63" s="58" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D63" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="58" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="F63" s="58" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+      <c r="G63" s="59" t="n"/>
+      <c r="H63" s="59" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="49" t="n"/>
       <c r="K63" s="49" t="n"/>
@@ -11041,37 +11058,37 @@
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="49" t="n"/>
-      <c r="B64" s="54" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C64" s="54" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D64" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="54" t="inlineStr">
+      <c r="B64" s="60" t="inlineStr">
+        <is>
+          <t>Aas10</t>
+        </is>
+      </c>
+      <c r="C64" s="60" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D64" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="60" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="F64" s="54" t="inlineStr">
-        <is>
-          <t>NS language</t>
-        </is>
-      </c>
-      <c r="G64" s="49" t="n"/>
-      <c r="H64" s="49" t="n"/>
+      <c r="F64" s="60" t="inlineStr">
+        <is>
+          <t>NS language; sig language</t>
+        </is>
+      </c>
+      <c r="G64" s="61" t="n"/>
+      <c r="H64" s="61" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="49" t="n"/>
       <c r="K64" s="49" t="n"/>
       <c r="L64" s="49" t="n"/>
     </row>
-    <row r="65" ht="22" customHeight="1">
+    <row r="65">
       <c r="A65" s="49" t="n"/>
       <c r="B65" s="49" t="n"/>
       <c r="C65" s="49" t="n"/>
@@ -11085,7 +11102,7 @@
       <c r="K65" s="49" t="n"/>
       <c r="L65" s="49" t="n"/>
     </row>
-    <row r="66" ht="32" customHeight="1">
+    <row r="66">
       <c r="A66" s="49" t="n"/>
       <c r="B66" s="49" t="n"/>
       <c r="C66" s="49" t="n"/>
@@ -11099,7 +11116,7 @@
       <c r="K66" s="49" t="n"/>
       <c r="L66" s="49" t="n"/>
     </row>
-    <row r="67" ht="32" customHeight="1">
+    <row r="67">
       <c r="A67" s="49" t="n"/>
       <c r="B67" s="49" t="n"/>
       <c r="C67" s="49" t="n"/>
@@ -11744,7 +11761,7 @@
       <c r="A16" s="49" t="n"/>
       <c r="B16" s="54" t="inlineStr">
         <is>
-          <t>Acs5</t>
+          <t>Acs3</t>
         </is>
       </c>
       <c r="C16" s="54" t="inlineStr">
@@ -11754,12 +11771,12 @@
       </c>
       <c r="D16" s="54" t="inlineStr">
         <is>
-          <t>Therefore</t>
+          <t>In conclusion</t>
         </is>
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Therefore, the... (yield inference connector)</t>
+          <t>In conclusion, the number of rooted...</t>
         </is>
       </c>
       <c r="F16" s="54" t="inlineStr">
@@ -11779,7 +11796,7 @@
       </c>
       <c r="I16" s="54" t="inlineStr">
         <is>
-          <t>Results→inference connector.</t>
+          <t>Meta-textual framing of conclusion move.</t>
         </is>
       </c>
       <c r="J16" s="49" t="n"/>
@@ -11788,44 +11805,44 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="49" t="n"/>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>Aas9</t>
-        </is>
-      </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>Acs5</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>Therefore</t>
         </is>
       </c>
-      <c r="E17" s="53" t="inlineStr">
-        <is>
-          <t>Therefore, it is recommended for future researchers...</t>
-        </is>
-      </c>
-      <c r="F17" s="53" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
+        <is>
+          <t>Therefore, the... (yield inference connector)</t>
+        </is>
+      </c>
+      <c r="F17" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G17" s="53" t="inlineStr">
+      <c r="G17" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H17" s="53" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I17" s="53" t="inlineStr">
-        <is>
-          <t>Results→recommendation connector.</t>
+      <c r="I17" s="54" t="inlineStr">
+        <is>
+          <t>Results→inference connector.</t>
         </is>
       </c>
       <c r="J17" s="49" t="n"/>
@@ -11834,42 +11851,42 @@
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="49" t="n"/>
-      <c r="B18" s="54" t="inlineStr">
-        <is>
-          <t>Acs3</t>
-        </is>
-      </c>
-      <c r="C18" s="54" t="inlineStr">
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>Acs7</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D18" s="54" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E18" s="54" t="inlineStr">
-        <is>
-          <t>In conclusion, the number of rooted...</t>
-        </is>
-      </c>
-      <c r="F18" s="54" t="inlineStr">
+      <c r="E18" s="53" t="inlineStr">
+        <is>
+          <t>In conclusion, the use of rice hull...</t>
+        </is>
+      </c>
+      <c r="F18" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G18" s="54" t="inlineStr">
+      <c r="G18" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H18" s="54" t="inlineStr">
+      <c r="H18" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I18" s="54" t="inlineStr">
+      <c r="I18" s="53" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
@@ -11880,42 +11897,42 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="49" t="n"/>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>Acs7</t>
-        </is>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
+      <c r="B19" s="54" t="inlineStr">
+        <is>
+          <t>Acs10</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D19" s="53" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E19" s="53" t="inlineStr">
-        <is>
-          <t>In conclusion, the use of rice hull...</t>
-        </is>
-      </c>
-      <c r="F19" s="53" t="inlineStr">
+      <c r="E19" s="54" t="inlineStr">
+        <is>
+          <t>In conclusion, T3:...</t>
+        </is>
+      </c>
+      <c r="F19" s="54" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G19" s="53" t="inlineStr">
+      <c r="G19" s="54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H19" s="53" t="inlineStr">
+      <c r="H19" s="54" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I19" s="53" t="inlineStr">
+      <c r="I19" s="54" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
@@ -11926,42 +11943,42 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="49" t="n"/>
-      <c r="B20" s="54" t="inlineStr">
-        <is>
-          <t>Acs10</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="inlineStr">
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>Aas3</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="D20" s="54" t="inlineStr">
+      <c r="D20" s="53" t="inlineStr">
         <is>
           <t>In conclusion</t>
         </is>
       </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>In conclusion, T3:...</t>
-        </is>
-      </c>
-      <c r="F20" s="54" t="inlineStr">
+      <c r="E20" s="53" t="inlineStr">
+        <is>
+          <t>In conclusion, proved the treatment 1...</t>
+        </is>
+      </c>
+      <c r="F20" s="53" t="inlineStr">
         <is>
           <t>DO</t>
         </is>
       </c>
-      <c r="G20" s="54" t="inlineStr">
+      <c r="G20" s="53" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H20" s="54" t="inlineStr">
+      <c r="H20" s="53" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I20" s="54" t="inlineStr">
+      <c r="I20" s="53" t="inlineStr">
         <is>
           <t>Meta-textual framing of conclusion move.</t>
         </is>
@@ -11974,7 +11991,7 @@
       <c r="A21" s="49" t="n"/>
       <c r="B21" s="53" t="inlineStr">
         <is>
-          <t>Aas3</t>
+          <t>Aas9</t>
         </is>
       </c>
       <c r="C21" s="53" t="inlineStr">
@@ -11984,12 +12001,12 @@
       </c>
       <c r="D21" s="53" t="inlineStr">
         <is>
-          <t>In conclusion</t>
+          <t>Therefore</t>
         </is>
       </c>
       <c r="E21" s="53" t="inlineStr">
         <is>
-          <t>In conclusion, proved the treatment 1...</t>
+          <t>Therefore, it is recommended for future researchers...</t>
         </is>
       </c>
       <c r="F21" s="53" t="inlineStr">
@@ -12009,7 +12026,7 @@
       </c>
       <c r="I21" s="53" t="inlineStr">
         <is>
-          <t>Meta-textual framing of conclusion move.</t>
+          <t>Results→recommendation connector.</t>
         </is>
       </c>
       <c r="J21" s="49" t="n"/>
@@ -12066,27 +12083,27 @@
       <c r="A23" s="49" t="n"/>
       <c r="B23" s="55" t="inlineStr">
         <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C23" s="55" t="inlineStr">
-        <is>
-          <t>All disciplines</t>
-        </is>
-      </c>
       <c r="D23" s="55" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>regarding / with regard to / overall / first-second</t>
         </is>
       </c>
       <c r="E23" s="55" t="inlineStr">
         <is>
-          <t>No "as X suggested", "in our view", "please", "kindly", "with due respect", "one might argue"</t>
+          <t>Common in VM KAP and ranking sentences</t>
         </is>
       </c>
       <c r="F23" s="55" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="55" t="inlineStr">
@@ -12096,12 +12113,12 @@
       </c>
       <c r="H23" s="55" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="55" t="inlineStr">
         <is>
-          <t>No politeness/deference devices in the 60 abstracts.</t>
+          <t>Topic prepositions and ordinal ranking of results are NOT discourse-organization function. Left untagged.</t>
         </is>
       </c>
       <c r="J23" s="49" t="n"/>
@@ -12122,12 +12139,12 @@
       </c>
       <c r="D24" s="55" t="inlineStr">
         <is>
-          <t>regarding / with regard to / overall / first-second</t>
+          <t>should / recommended (FP-Rec)</t>
         </is>
       </c>
       <c r="E24" s="55" t="inlineStr">
         <is>
-          <t>Common in VM KAP and ranking sentences</t>
+          <t>See Rejected Candidates</t>
         </is>
       </c>
       <c r="F24" s="55" t="inlineStr">
@@ -12147,7 +12164,7 @@
       </c>
       <c r="I24" s="55" t="inlineStr">
         <is>
-          <t>Topic prepositions and ordinal ranking of results are NOT discourse-organization function. Left untagged.</t>
+          <t>Deontic prescriptions. Reject reason FP-Rec, not Layer 2 P or DO.</t>
         </is>
       </c>
       <c r="J24" s="49" t="n"/>
@@ -12158,27 +12175,27 @@
       <c r="A25" s="49" t="n"/>
       <c r="B25" s="55" t="inlineStr">
         <is>
-          <t>NOTE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C25" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>All disciplines</t>
         </is>
       </c>
       <c r="D25" s="55" t="inlineStr">
         <is>
-          <t>should / recommended (FP-Rec)</t>
+          <t>(none)</t>
         </is>
       </c>
       <c r="E25" s="55" t="inlineStr">
         <is>
-          <t>See Rejected Candidates</t>
+          <t>No "as X suggested", "in our view", "please", "kindly", "with due respect", "one might argue"</t>
         </is>
       </c>
       <c r="F25" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G25" s="55" t="inlineStr">
@@ -12188,19 +12205,19 @@
       </c>
       <c r="H25" s="55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I25" s="55" t="inlineStr">
         <is>
-          <t>Deontic prescriptions. Reject reason FP-Rec, not Layer 2 P or DO.</t>
+          <t>No politeness/deference devices in the 60 abstracts.</t>
         </is>
       </c>
       <c r="J25" s="49" t="n"/>
       <c r="K25" s="49" t="n"/>
       <c r="L25" s="49" t="n"/>
     </row>
-    <row r="26" ht="40" customHeight="1">
+    <row r="26">
       <c r="A26" s="49" t="n"/>
       <c r="B26" s="49" t="n"/>
       <c r="C26" s="49" t="n"/>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,8 +137,27 @@
       <color rgb="008C8A84"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -213,8 +232,13 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -267,11 +291,19 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -388,6 +420,27 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,19 +807,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H101"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -781,6 +835,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -925,6 +980,8 @@
         <v>0.47</v>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1018,6 +1075,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1117,6 +1176,8 @@
         <v>33</v>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -1186,6 +1247,8 @@
         <v>4</v>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="16" t="inlineStr">
         <is>
@@ -1193,6 +1256,8 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -2789,6 +2854,267 @@
       <c r="G101" s="5" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="63" t="inlineStr">
+        <is>
+          <t>Outcome Type by Discipline (Table 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="64" t="inlineStr">
+        <is>
+          <t>Counts are abstracts (one outcome type per abstract). Matches thesis Table 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C107" s="65" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D107" s="65" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="E107" s="65" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="F107" s="65" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C108" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F108" s="67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C109" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" s="69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C110" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" s="67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C111" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D111" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="69" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C112" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="70" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C113" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D113" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E113" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="F113" s="71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="63" t="inlineStr">
+        <is>
+          <t>Outcome Type Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="64" t="inlineStr">
+        <is>
+          <t>Same definitions used in thesis Part IV. Not hedge types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C119" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D119" s="65" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="45" customHeight="1">
+      <c r="B120" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C120" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="D120" s="66" t="inlineStr">
+        <is>
+          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="45" customHeight="1">
+      <c r="B121" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C121" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D121" s="68" t="inlineStr">
+        <is>
+          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="45" customHeight="1">
+      <c r="B122" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C122" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D122" s="66" t="inlineStr">
+        <is>
+          <t>Abstract combines more than one outcome style (e.g., binary plus continuous, or continuous plus a null test).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="45" customHeight="1">
+      <c r="B123" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C123" s="69" t="n">
+        <v>21</v>
+      </c>
+      <c r="D123" s="68" t="inlineStr">
+        <is>
+          <t>Abstract explicitly reports non-significance, no significant difference, or a null statistical result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="45" customHeight="1">
+      <c r="B124" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C124" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" s="66" t="inlineStr">
+        <is>
+          <t>Results language does not fit the four boxes cleanly (e.g., descriptive profiles, rankings, or designs that are not clearly binary, continuous, mixed, or null).</t>
         </is>
       </c>
     </row>
@@ -9165,15 +9491,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11129,6 +11455,267 @@
       <c r="J67" s="49" t="n"/>
       <c r="K67" s="49" t="n"/>
       <c r="L67" s="49" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>Outcome Type by Discipline (Table 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="64" t="inlineStr">
+        <is>
+          <t>Counts are abstracts. One outcome type per abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C73" s="65" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D73" s="65" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="E73" s="65" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="F73" s="65" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C74" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E74" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C75" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C76" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C77" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D77" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="69" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C78" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="70" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C79" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D79" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="F79" s="71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="63" t="inlineStr">
+        <is>
+          <t>Outcome Type Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="64" t="inlineStr">
+        <is>
+          <t>Same definitions used in thesis Part IV. These are not hedge types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C85" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D85" s="65" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="B86" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C86" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="D86" s="66" t="inlineStr">
+        <is>
+          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="B87" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C87" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" s="68" t="inlineStr">
+        <is>
+          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="45" customHeight="1">
+      <c r="B88" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C88" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D88" s="66" t="inlineStr">
+        <is>
+          <t>Abstract combines more than one outcome style (e.g., binary plus continuous, or continuous plus a null test).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="45" customHeight="1">
+      <c r="B89" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C89" s="69" t="n">
+        <v>21</v>
+      </c>
+      <c r="D89" s="68" t="inlineStr">
+        <is>
+          <t>Abstract explicitly reports non-significance, no significant difference, or a null statistical result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="B90" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C90" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="66" t="inlineStr">
+        <is>
+          <t>Results language does not fit the four boxes cleanly (e.g., descriptive profiles, rankings, or designs that are not clearly binary, continuous, mixed, or null).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="B2:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,6 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -835,7 +834,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -980,8 +978,6 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1075,8 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1176,8 +1170,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -1247,8 +1239,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="B37" s="16" t="inlineStr">
         <is>
@@ -1256,8 +1246,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -9491,7 +9479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -11456,267 +11444,13 @@
       <c r="K67" s="49" t="n"/>
       <c r="L67" s="49" t="n"/>
     </row>
-    <row r="70">
-      <c r="B70" s="63" t="inlineStr">
-        <is>
-          <t>Outcome Type by Discipline (Table 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="64" t="inlineStr">
-        <is>
-          <t>Counts are abstracts. One outcome type per abstract.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="65" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="C73" s="65" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D73" s="65" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="E73" s="65" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="F73" s="65" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="66" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C74" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="E74" s="67" t="n">
-        <v>7</v>
-      </c>
-      <c r="F74" s="67" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="68" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="C75" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="D75" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="E75" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="F75" s="69" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="66" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="C76" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E76" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="F76" s="67" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="68" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="C77" s="69" t="n">
-        <v>14</v>
-      </c>
-      <c r="D77" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" s="69" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="66" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C78" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E78" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="70" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C79" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="D79" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="E79" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="F79" s="71" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="63" t="inlineStr">
-        <is>
-          <t>Outcome Type Definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="64" t="inlineStr">
-        <is>
-          <t>Same definitions used in thesis Part IV. These are not hedge types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="65" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="C85" s="65" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="D85" s="65" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="45" customHeight="1">
-      <c r="B86" s="66" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C86" s="67" t="n">
-        <v>15</v>
-      </c>
-      <c r="D86" s="66" t="inlineStr">
-        <is>
-          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="45" customHeight="1">
-      <c r="B87" s="68" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="C87" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="D87" s="68" t="inlineStr">
-        <is>
-          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="45" customHeight="1">
-      <c r="B88" s="66" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="C88" s="67" t="n">
-        <v>9</v>
-      </c>
-      <c r="D88" s="66" t="inlineStr">
-        <is>
-          <t>Abstract combines more than one outcome style (e.g., binary plus continuous, or continuous plus a null test).</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="45" customHeight="1">
-      <c r="B89" s="68" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="C89" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="D89" s="68" t="inlineStr">
-        <is>
-          <t>Abstract explicitly reports non-significance, no significant difference, or a null statistical result.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="45" customHeight="1">
-      <c r="B90" s="66" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C90" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="D90" s="66" t="inlineStr">
-        <is>
-          <t>Results language does not fit the four boxes cleanly (e.g., descriptive profiles, rankings, or designs that are not clearly binary, continuous, mixed, or null).</t>
-        </is>
-      </c>
-    </row>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="86" ht="45" customHeight="1"/>
+    <row r="87" ht="45" customHeight="1"/>
+    <row r="88" ht="45" customHeight="1"/>
+    <row r="89" ht="45" customHeight="1"/>
+    <row r="90" ht="45" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -807,19 +807,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H124"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -834,6 +835,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -978,6 +980,8 @@
         <v>0.47</v>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1071,6 +1075,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1170,6 +1176,8 @@
         <v>33</v>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -1239,6 +1247,8 @@
         <v>4</v>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="16" t="inlineStr">
         <is>
@@ -1246,6 +1256,8 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -2845,262 +2857,621 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="B104" s="63" t="inlineStr">
         <is>
-          <t>Outcome Type by Discipline (Table 7)</t>
+          <t>Hedge Token Inventory by Form (Table 3)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="64" t="inlineStr">
         <is>
-          <t>Counts are abstracts (one outcome type per abstract). Matches thesis Table 7.</t>
+          <t>Every retained surface form with Layer 1 type and count. Sums to 65. Matches thesis Table 3.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="65" t="inlineStr">
         <is>
-          <t>Outcome Type</t>
+          <t>Hedge form</t>
         </is>
       </c>
       <c r="C107" s="65" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Layer 1 type</t>
         </is>
       </c>
       <c r="D107" s="65" t="inlineStr">
         <is>
-          <t>Veterinary Medicine</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E107" s="65" t="inlineStr">
         <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="F107" s="65" t="inlineStr">
-        <is>
-          <t>Total</t>
+          <t>% of total hedges</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="66" t="inlineStr">
         <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C108" s="67" t="n">
-        <v>0</v>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="C108" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
       </c>
       <c r="D108" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="E108" s="67" t="n">
-        <v>7</v>
-      </c>
-      <c r="F108" s="67" t="n">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="E108" s="67" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="68" t="inlineStr">
         <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="C109" s="69" t="n">
-        <v>4</v>
+          <t>suggests</t>
+        </is>
+      </c>
+      <c r="C109" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
       </c>
       <c r="D109" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="E109" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="F109" s="69" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="E109" s="69" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="66" t="inlineStr">
         <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="C110" s="67" t="n">
-        <v>2</v>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="C110" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
       </c>
       <c r="D110" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="E110" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="F110" s="67" t="n">
-        <v>9</v>
+      <c r="E110" s="67" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="68" t="inlineStr">
         <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="C111" s="69" t="n">
-        <v>14</v>
+          <t>suggesting</t>
+        </is>
+      </c>
+      <c r="C111" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
       </c>
       <c r="D111" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="F111" s="69" t="n">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="E111" s="69" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="66" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C112" s="67" t="n">
-        <v>0</v>
+          <t>implies</t>
+        </is>
+      </c>
+      <c r="C112" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
       </c>
       <c r="D112" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E112" s="67" t="n">
         <v>2</v>
       </c>
-      <c r="F112" s="67" t="n">
-        <v>5</v>
+      <c r="E112" s="67" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="70" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C113" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="D113" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="E113" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="F113" s="71" t="n">
-        <v>60</v>
+      <c r="B113" s="68" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="C113" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D113" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" s="69" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="66" t="inlineStr">
+        <is>
+          <t>likely</t>
+        </is>
+      </c>
+      <c r="C114" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D114" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" s="67" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="68" t="inlineStr">
+        <is>
+          <t>implying</t>
+        </is>
+      </c>
+      <c r="C115" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D115" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="69" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="63" t="inlineStr">
-        <is>
-          <t>Outcome Type Definitions</t>
+      <c r="B116" s="66" t="inlineStr">
+        <is>
+          <t>inferring</t>
+        </is>
+      </c>
+      <c r="C116" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D116" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="67" t="inlineStr">
+        <is>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="64" t="inlineStr">
-        <is>
-          <t>Same definitions used in thesis Part IV. Not hedge types.</t>
+      <c r="B117" s="68" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="C117" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D117" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="69" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="66" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="C118" s="66" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D118" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" s="67" t="inlineStr">
+        <is>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="65" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="C119" s="65" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="D119" s="65" t="inlineStr">
-        <is>
-          <t>Meaning</t>
+      <c r="B119" s="68" t="inlineStr">
+        <is>
+          <t>could</t>
+        </is>
+      </c>
+      <c r="C119" s="68" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D119" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="E119" s="69" t="inlineStr">
+        <is>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="45" customHeight="1">
       <c r="B120" s="66" t="inlineStr">
         <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C120" s="67" t="n">
-        <v>15</v>
-      </c>
-      <c r="D120" s="66" t="inlineStr">
-        <is>
-          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="C120" s="66" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D120" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E120" s="67" t="inlineStr">
+        <is>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="45" customHeight="1">
       <c r="B121" s="68" t="inlineStr">
         <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="C121" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="D121" s="68" t="inlineStr">
-        <is>
-          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
+          <t>might</t>
+        </is>
+      </c>
+      <c r="C121" s="68" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D121" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" s="69" t="inlineStr">
+        <is>
+          <t>4.6%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="45" customHeight="1">
       <c r="B122" s="66" t="inlineStr">
         <is>
+          <t>potentially</t>
+        </is>
+      </c>
+      <c r="C122" s="66" t="inlineStr">
+        <is>
+          <t>Adverbial Hedges</t>
+        </is>
+      </c>
+      <c r="D122" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="67" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="45" customHeight="1">
+      <c r="B123" s="70" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C123" s="70" t="inlineStr"/>
+      <c r="D123" s="71" t="n">
+        <v>65</v>
+      </c>
+      <c r="E123" s="71" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="45" customHeight="1"/>
+    <row r="126">
+      <c r="B126" s="63" t="inlineStr">
+        <is>
+          <t>Outcome Type by Discipline (Table 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="64" t="inlineStr">
+        <is>
+          <t>Counts are abstracts (one outcome type per abstract). Matches thesis Table 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128"/>
+    <row r="129">
+      <c r="B129" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C129" s="65" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D129" s="65" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="E129" s="65" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="F129" s="65" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C130" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E130" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" s="67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C131" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E131" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="66" t="inlineStr">
+        <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="C122" s="67" t="n">
+      <c r="C132" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="D122" s="66" t="inlineStr">
+    </row>
+    <row r="133">
+      <c r="B133" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C133" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D133" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" s="69" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C134" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F134" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="70" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C135" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D135" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E135" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="F135" s="71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138">
+      <c r="B138" s="63" t="inlineStr">
+        <is>
+          <t>Outcome Type Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="64" t="inlineStr">
+        <is>
+          <t>Same definitions used in thesis Part IV. Not hedge types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140"/>
+    <row r="141">
+      <c r="B141" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C141" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D141" s="65" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C142" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="D142" s="66" t="inlineStr">
+        <is>
+          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C143" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D143" s="68" t="inlineStr">
+        <is>
+          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C144" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D144" s="66" t="inlineStr">
         <is>
           <t>Abstract combines more than one outcome style (e.g., binary plus continuous, or continuous plus a null test).</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="45" customHeight="1">
-      <c r="B123" s="68" t="inlineStr">
+    <row r="145">
+      <c r="B145" s="68" t="inlineStr">
         <is>
           <t>Null/NS</t>
         </is>
       </c>
-      <c r="C123" s="69" t="n">
+      <c r="C145" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="D123" s="68" t="inlineStr">
+      <c r="D145" s="68" t="inlineStr">
         <is>
           <t>Abstract explicitly reports non-significance, no significant difference, or a null statistical result.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="45" customHeight="1">
-      <c r="B124" s="66" t="inlineStr">
+    <row r="146">
+      <c r="B146" s="66" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C124" s="67" t="n">
+      <c r="C146" s="67" t="n">
         <v>5</v>
       </c>
-      <c r="D124" s="66" t="inlineStr">
+      <c r="D146" s="66" t="inlineStr">
         <is>
           <t>Results language does not fit the four boxes cleanly (e.g., descriptive profiles, rankings, or designs that are not clearly binary, continuous, mixed, or null).</t>
         </is>
@@ -9479,7 +9850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -11444,8 +11815,6 @@
       <c r="K67" s="49" t="n"/>
       <c r="L67" s="49" t="n"/>
     </row>
-    <row r="68"/>
-    <row r="69"/>
     <row r="86" ht="45" customHeight="1"/>
     <row r="87" ht="45" customHeight="1"/>
     <row r="88" ht="45" customHeight="1"/>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -155,6 +155,11 @@
     <font>
       <name val="Georgia"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="15">
@@ -303,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -441,6 +446,10 @@
     <xf numFmtId="0" fontId="24" fillId="14" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -807,29 +816,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="88" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Compiled Hedging Codings — PSAU Corpus</t>
+      <c r="B2" s="72" t="inlineStr">
+        <is>
+          <t>Compiled Hedging Codings - PSAU Corpus</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>60 abstracts across Agriculture, Veterinary Medicine, and Biology</t>
         </is>
@@ -837,2643 +846,2632 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Discipline Summary</t>
+      <c r="B5" s="63" t="inlineStr">
+        <is>
+          <t>1. Discipline Summary</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>Abstracts</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="65" t="inlineStr">
         <is>
           <t>Total Words</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="65" t="inlineStr">
         <is>
           <t>Hedges</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="65" t="inlineStr">
         <is>
           <t>False Positives</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="65" t="inlineStr">
         <is>
           <t>Unhedged Sites</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="65" t="inlineStr">
         <is>
           <t>Hedge Density (per 100 words)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="67" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="67" t="n">
         <v>4300</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="67" t="n">
         <v>27</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="67" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="67" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="67" t="n">
         <v>0.63</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="69" t="n">
         <v>4509</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="69" t="n">
         <v>28</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="69" t="n">
         <v>32</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="69" t="n">
         <v>0.62</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>Veterinary Medicine</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="67" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="67" t="n">
         <v>5060</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="67" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="67" t="n">
         <v>12</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="67" t="n">
         <v>15</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="67" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="71" t="n">
         <v>60</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="71" t="n">
         <v>13869</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="71" t="n">
         <v>65</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="71" t="n">
         <v>58</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="71" t="n">
         <v>37</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="71" t="n">
         <v>0.47</v>
       </c>
     </row>
     <row r="11"/>
-    <row r="12"/>
+    <row r="12">
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>2. Hedge Type Breakdown (Layer 1) - Table 2</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Hedge Type Breakdown (Layer 1)</t>
+      <c r="B13" s="65" t="inlineStr">
+        <is>
+          <t>Layer 1 Type</t>
+        </is>
+      </c>
+      <c r="C13" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>% of Hedges</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Layer 1 Type</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Fill Color</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="C14" s="67" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" s="67" t="inlineStr">
+        <is>
+          <t>32.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="C15" s="69" t="n">
+        <v>41</v>
+      </c>
+      <c r="D15" s="69" t="inlineStr">
+        <is>
+          <t>63.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="66" t="inlineStr">
+        <is>
+          <t>Adverbial Hedges</t>
+        </is>
+      </c>
+      <c r="C16" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="67" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>Clause-Level Hedges</t>
+        </is>
+      </c>
+      <c r="C17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="69" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="63" t="inlineStr">
+        <is>
+          <t>3. Hedge Token Inventory by Form - Table 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>Every retained surface form. Counts sum to 65.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>Hedge form</t>
+        </is>
+      </c>
+      <c r="C21" s="65" t="inlineStr">
+        <is>
+          <t>Layer 1 type</t>
+        </is>
+      </c>
+      <c r="D21" s="65" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>% of Hedges</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="E21" s="65" t="inlineStr">
+        <is>
+          <t>% of total hedges</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="66" t="inlineStr">
+        <is>
+          <t>potential</t>
+        </is>
+      </c>
+      <c r="C22" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="68" t="inlineStr">
+        <is>
+          <t>suggests</t>
+        </is>
+      </c>
+      <c r="C23" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D23" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="69" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="66" t="inlineStr">
+        <is>
+          <t>suggest</t>
+        </is>
+      </c>
+      <c r="C24" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="68" t="inlineStr">
+        <is>
+          <t>suggesting</t>
+        </is>
+      </c>
+      <c r="C25" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="66" t="inlineStr">
+        <is>
+          <t>implies</t>
+        </is>
+      </c>
+      <c r="C26" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="68" t="inlineStr">
+        <is>
+          <t>indicating</t>
+        </is>
+      </c>
+      <c r="C27" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D27" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="66" t="inlineStr">
+        <is>
+          <t>likely</t>
+        </is>
+      </c>
+      <c r="C28" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D28" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="68" t="inlineStr">
+        <is>
+          <t>implying</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D29" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="69" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="66" t="inlineStr">
+        <is>
+          <t>inferring</t>
+        </is>
+      </c>
+      <c r="C30" s="66" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D30" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="68" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="C31" s="68" t="inlineStr">
+        <is>
+          <t>Lexical Hedges</t>
+        </is>
+      </c>
+      <c r="D31" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="69" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="66" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>Modal Verbs</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="9" t="n">
+      <c r="D32" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="68" t="inlineStr">
+        <is>
+          <t>could</t>
+        </is>
+      </c>
+      <c r="C33" s="68" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D33" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="69" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="66" t="inlineStr">
+        <is>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="C34" s="66" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D34" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="68" t="inlineStr">
+        <is>
+          <t>might</t>
+        </is>
+      </c>
+      <c r="C35" s="68" t="inlineStr">
+        <is>
+          <t>Modal Verbs</t>
+        </is>
+      </c>
+      <c r="D35" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="66" t="inlineStr">
+        <is>
+          <t>potentially</t>
+        </is>
+      </c>
+      <c r="C36" s="66" t="inlineStr">
+        <is>
+          <t>Adverbial Hedges</t>
+        </is>
+      </c>
+      <c r="D36" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="67" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="73" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C37" s="73" t="inlineStr"/>
+      <c r="D37" s="71" t="n">
+        <v>65</v>
+      </c>
+      <c r="E37" s="71" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="B39" s="63" t="inlineStr">
+        <is>
+          <t>4. False Positive Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="65" t="inlineStr">
+        <is>
+          <t>FP Code</t>
+        </is>
+      </c>
+      <c r="C40" s="65" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="D40" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="66" t="inlineStr">
+        <is>
+          <t>FP-Cap</t>
+        </is>
+      </c>
+      <c r="C41" s="66" t="inlineStr">
+        <is>
+          <t>Capability: describes what something is able to do, not uncertainty</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="68" t="inlineStr">
+        <is>
+          <t>FP-Rec</t>
+        </is>
+      </c>
+      <c r="C42" s="68" t="inlineStr">
+        <is>
+          <t>Recommendation: prescribes what should be done, not uncertainty about a claim</t>
+        </is>
+      </c>
+      <c r="D42" s="69" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="66" t="inlineStr">
+        <is>
+          <t>FP-Proc</t>
+        </is>
+      </c>
+      <c r="C43" s="66" t="inlineStr">
+        <is>
+          <t>Procedural norm: describes routine/standard procedure, not uncertainty</t>
+        </is>
+      </c>
+      <c r="D43" s="67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="68" t="inlineStr">
+        <is>
+          <t>FP-Loc</t>
+        </is>
+      </c>
+      <c r="C44" s="68" t="inlineStr">
+        <is>
+          <t>Location: 'appears in Table/Figure...'</t>
+        </is>
+      </c>
+      <c r="D44" s="69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="66" t="inlineStr">
+        <is>
+          <t>FP-Gen</t>
+        </is>
+      </c>
+      <c r="C45" s="66" t="inlineStr">
+        <is>
+          <t>General exclusion: topic-naming, evidential pointer, etc.</t>
+        </is>
+      </c>
+      <c r="D45" s="67" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>5. Layer 3 - Unhedged Assertion Site Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="65" t="inlineStr">
+        <is>
+          <t>Subtype</t>
+        </is>
+      </c>
+      <c r="C48" s="65" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D48" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="66" t="inlineStr">
+        <is>
+          <t>[R]</t>
+        </is>
+      </c>
+      <c r="C49" s="66" t="inlineStr">
+        <is>
+          <t>Result Claim: finding stated as settled fact</t>
+        </is>
+      </c>
+      <c r="D49" s="67" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="68" t="inlineStr">
+        <is>
+          <t>[G]</t>
+        </is>
+      </c>
+      <c r="C50" s="68" t="inlineStr">
+        <is>
+          <t>Generalization: broader inference beyond the data</t>
+        </is>
+      </c>
+      <c r="D50" s="69" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="66" t="inlineStr">
+        <is>
+          <t>[C]</t>
+        </is>
+      </c>
+      <c r="C51" s="66" t="inlineStr">
+        <is>
+          <t>Causal Claim: cause-and-effect link stated as established</t>
+        </is>
+      </c>
+      <c r="D51" s="67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>6. Outcome Type by Discipline - Table 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>Counts are abstracts (one outcome type per abstract).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C55" s="65" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D55" s="65" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="E55" s="65" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="F55" s="65" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C56" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" s="67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C57" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C58" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" s="67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C59" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D59" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>32.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>63.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Adverbial Hedges</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="9" t="n">
+    </row>
+    <row r="60">
+      <c r="B60" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C60" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Clause-Level Hedges</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr"/>
-      <c r="D18" s="9" t="n">
+      <c r="E60" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="73" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C61" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D61" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E61" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" s="71" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>7. Outcome Type Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>Same definitions used in thesis Part IV. These are not hedge types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="65" t="inlineStr">
+        <is>
+          <t>Outcome Type</t>
+        </is>
+      </c>
+      <c r="C65" s="65" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D65" s="65" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="B66" s="66" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="C66" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" s="66" t="inlineStr">
+        <is>
+          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="B67" s="68" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="C67" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" s="68" t="inlineStr">
+        <is>
+          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="B68" s="66" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C68" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" s="66" t="inlineStr">
+        <is>
+          <t>Abstract combines more than one outcome style (e.g., binary plus continuous, or continuous plus a null test).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="B69" s="68" t="inlineStr">
+        <is>
+          <t>Null/NS</t>
+        </is>
+      </c>
+      <c r="C69" s="69" t="n">
+        <v>21</v>
+      </c>
+      <c r="D69" s="68" t="inlineStr">
+        <is>
+          <t>Abstract explicitly reports non-significance, no significant difference, or a null statistical result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="B70" s="66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C70" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" s="66" t="inlineStr">
+        <is>
+          <t>Results language does not fit the four boxes cleanly (e.g., descriptive profiles, rankings, or designs that are not clearly binary, continuous, mixed, or null).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="B72" s="64" t="inlineStr">
+        <is>
+          <t>Source: corpus of 60 abstracts. Coded per Hedging Codebook. Detail rows are in the Hedges, Unhedged Sites, Rejected Candidates, and Outcome Type sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74">
+      <c r="B74" s="63" t="inlineStr">
+        <is>
+          <t>8. Per-Abstract Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="64" t="inlineStr">
+        <is>
+          <t>Ordered Biology → Veterinary Medicine → Agriculture (Acs then Aas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="65" t="inlineStr">
+        <is>
+          <t>Abstract ID</t>
+        </is>
+      </c>
+      <c r="C76" s="65" t="inlineStr">
+        <is>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="D76" s="65" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+      <c r="E76" s="65" t="inlineStr">
+        <is>
+          <t>Hedge Count</t>
+        </is>
+      </c>
+      <c r="F76" s="65" t="inlineStr">
+        <is>
+          <t>Hedges per 100 Words</t>
+        </is>
+      </c>
+      <c r="G76" s="65" t="inlineStr">
+        <is>
+          <t>Zero-Hedge?</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="66" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C77" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D77" s="67" t="n">
+        <v>258</v>
+      </c>
+      <c r="E77" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="67" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G77" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="68" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C78" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D78" s="69" t="n">
+        <v>189</v>
+      </c>
+      <c r="E78" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>False Positive Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>FP Code</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>FP-Cap</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Capability: describes what something is able to do, not uncertainty</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n">
+      <c r="F78" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="66" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C79" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D79" s="67" t="n">
+        <v>142</v>
+      </c>
+      <c r="E79" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G79" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="68" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C80" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D80" s="69" t="n">
+        <v>231</v>
+      </c>
+      <c r="E80" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" s="69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G80" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="66" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C81" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D81" s="67" t="n">
+        <v>245</v>
+      </c>
+      <c r="E81" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="67" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G81" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="68" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C82" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D82" s="69" t="n">
+        <v>232</v>
+      </c>
+      <c r="E82" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="66" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C83" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D83" s="67" t="n">
+        <v>266</v>
+      </c>
+      <c r="E83" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" s="67" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G83" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="68" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C84" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D84" s="69" t="n">
+        <v>241</v>
+      </c>
+      <c r="E84" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="69" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G84" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="66" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C85" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D85" s="67" t="n">
+        <v>212</v>
+      </c>
+      <c r="E85" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="68" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C86" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D86" s="69" t="n">
+        <v>302</v>
+      </c>
+      <c r="E86" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="69" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G86" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="66" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="C87" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D87" s="67" t="n">
+        <v>256</v>
+      </c>
+      <c r="E87" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="67" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G87" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="68" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="C88" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D88" s="69" t="n">
+        <v>149</v>
+      </c>
+      <c r="E88" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="69" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G88" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="66" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="C89" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D89" s="67" t="n">
+        <v>148</v>
+      </c>
+      <c r="E89" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="68" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="C90" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D90" s="69" t="n">
+        <v>242</v>
+      </c>
+      <c r="E90" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" s="69" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G90" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="66" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="C91" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D91" s="67" t="n">
+        <v>131</v>
+      </c>
+      <c r="E91" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="68" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="C92" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D92" s="69" t="n">
+        <v>223</v>
+      </c>
+      <c r="E92" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" s="69" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G92" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="66" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="C93" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D93" s="67" t="n">
+        <v>243</v>
+      </c>
+      <c r="E93" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="67" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G93" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="68" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="C94" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D94" s="69" t="n">
+        <v>286</v>
+      </c>
+      <c r="E94" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="69" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G94" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="66" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="C95" s="67" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D95" s="67" t="n">
+        <v>290</v>
+      </c>
+      <c r="E95" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="67" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G95" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="68" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="C96" s="69" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="D96" s="69" t="n">
+        <v>223</v>
+      </c>
+      <c r="E96" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="69" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G96" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="66" t="inlineStr">
+        <is>
+          <t>VM1</t>
+        </is>
+      </c>
+      <c r="C97" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D97" s="67" t="n">
+        <v>211</v>
+      </c>
+      <c r="E97" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="68" t="inlineStr">
+        <is>
+          <t>VM2</t>
+        </is>
+      </c>
+      <c r="C98" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D98" s="69" t="n">
+        <v>358</v>
+      </c>
+      <c r="E98" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" s="69" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G98" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="66" t="inlineStr">
+        <is>
+          <t>VM3</t>
+        </is>
+      </c>
+      <c r="C99" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D99" s="67" t="n">
+        <v>296</v>
+      </c>
+      <c r="E99" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="68" t="inlineStr">
+        <is>
+          <t>VM4</t>
+        </is>
+      </c>
+      <c r="C100" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D100" s="69" t="n">
+        <v>250</v>
+      </c>
+      <c r="E100" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="66" t="inlineStr">
+        <is>
+          <t>VM5</t>
+        </is>
+      </c>
+      <c r="C101" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D101" s="67" t="n">
+        <v>256</v>
+      </c>
+      <c r="E101" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="67" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G101" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="68" t="inlineStr">
+        <is>
+          <t>VM6</t>
+        </is>
+      </c>
+      <c r="C102" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D102" s="69" t="n">
+        <v>278</v>
+      </c>
+      <c r="E102" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="66" t="inlineStr">
+        <is>
+          <t>VM7</t>
+        </is>
+      </c>
+      <c r="C103" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D103" s="67" t="n">
+        <v>174</v>
+      </c>
+      <c r="E103" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="67" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G103" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="68" t="inlineStr">
+        <is>
+          <t>VM8</t>
+        </is>
+      </c>
+      <c r="C104" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D104" s="69" t="n">
+        <v>253</v>
+      </c>
+      <c r="E104" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="69" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G104" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="66" t="inlineStr">
+        <is>
+          <t>VM9</t>
+        </is>
+      </c>
+      <c r="C105" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D105" s="67" t="n">
+        <v>430</v>
+      </c>
+      <c r="E105" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="67" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G105" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="68" t="inlineStr">
+        <is>
+          <t>VM10</t>
+        </is>
+      </c>
+      <c r="C106" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D106" s="69" t="n">
+        <v>277</v>
+      </c>
+      <c r="E106" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="66" t="inlineStr">
+        <is>
+          <t>VM11</t>
+        </is>
+      </c>
+      <c r="C107" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D107" s="67" t="n">
+        <v>236</v>
+      </c>
+      <c r="E107" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="68" t="inlineStr">
+        <is>
+          <t>VM12</t>
+        </is>
+      </c>
+      <c r="C108" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D108" s="69" t="n">
+        <v>182</v>
+      </c>
+      <c r="E108" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="69" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G108" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="66" t="inlineStr">
+        <is>
+          <t>VM13</t>
+        </is>
+      </c>
+      <c r="C109" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D109" s="67" t="n">
+        <v>215</v>
+      </c>
+      <c r="E109" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="68" t="inlineStr">
+        <is>
+          <t>VM14</t>
+        </is>
+      </c>
+      <c r="C110" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D110" s="69" t="n">
+        <v>183</v>
+      </c>
+      <c r="E110" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="66" t="inlineStr">
+        <is>
+          <t>VM15</t>
+        </is>
+      </c>
+      <c r="C111" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D111" s="67" t="n">
+        <v>258</v>
+      </c>
+      <c r="E111" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="67" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G111" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="68" t="inlineStr">
+        <is>
+          <t>VM16</t>
+        </is>
+      </c>
+      <c r="C112" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D112" s="69" t="n">
+        <v>261</v>
+      </c>
+      <c r="E112" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="66" t="inlineStr">
+        <is>
+          <t>VM17</t>
+        </is>
+      </c>
+      <c r="C113" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D113" s="67" t="n">
+        <v>232</v>
+      </c>
+      <c r="E113" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="67" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G113" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="68" t="inlineStr">
+        <is>
+          <t>VM18</t>
+        </is>
+      </c>
+      <c r="C114" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D114" s="69" t="n">
+        <v>267</v>
+      </c>
+      <c r="E114" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="66" t="inlineStr">
+        <is>
+          <t>VM19</t>
+        </is>
+      </c>
+      <c r="C115" s="67" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D115" s="67" t="n">
+        <v>172</v>
+      </c>
+      <c r="E115" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="68" t="inlineStr">
+        <is>
+          <t>VM20</t>
+        </is>
+      </c>
+      <c r="C116" s="69" t="inlineStr">
+        <is>
+          <t>Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D116" s="69" t="n">
+        <v>271</v>
+      </c>
+      <c r="E116" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="66" t="inlineStr">
+        <is>
+          <t>Acs1</t>
+        </is>
+      </c>
+      <c r="C117" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D117" s="67" t="n">
+        <v>203</v>
+      </c>
+      <c r="E117" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="67" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G117" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="68" t="inlineStr">
+        <is>
+          <t>Acs2</t>
+        </is>
+      </c>
+      <c r="C118" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D118" s="69" t="n">
+        <v>184</v>
+      </c>
+      <c r="E118" s="69" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>FP-Rec</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Recommendation: prescribes what should be done, not uncertainty about a claim</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>FP-Proc</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Procedural norm: describes routine/standard procedure, not uncertainty</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
+      <c r="F118" s="69" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G118" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="66" t="inlineStr">
+        <is>
+          <t>Acs3</t>
+        </is>
+      </c>
+      <c r="C119" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D119" s="67" t="n">
+        <v>235</v>
+      </c>
+      <c r="E119" s="67" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>FP-Loc</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Location: 'appears in Table/Figure...'</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n">
+      <c r="F119" s="67" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G119" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="68" t="inlineStr">
+        <is>
+          <t>Acs4</t>
+        </is>
+      </c>
+      <c r="C120" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D120" s="69" t="n">
+        <v>221</v>
+      </c>
+      <c r="E120" s="69" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>FP-Gen</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>General exclusion: topic-naming, evidential pointer, etc.</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Layer 3 — Unhedged Assertion Site Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Subtype</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>[R]</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Result Claim: finding stated as settled fact</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>[G]</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Generalization: broader inference beyond the data</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>[C]</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Causal Claim: cause-and-effect link stated as established</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37">
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>Source: 005_CorpusCoverted.docx (60 abstracts). Coded per Hedging Codebook. All decisions in 'Hedges', 'Unhedged Sites', and 'Rejected Candidates' sheets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Per-Abstract Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Abstract ID</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Discipline</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Word Count</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Hedge Count</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Hedges per 100 Words</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Zero-Hedge?</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>258</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="F120" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="66" t="inlineStr">
+        <is>
+          <t>Acs5</t>
+        </is>
+      </c>
+      <c r="C121" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D121" s="67" t="n">
+        <v>199</v>
+      </c>
+      <c r="E121" s="67" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="F121" s="67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G121" s="67" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>189</v>
-      </c>
-      <c r="E43" s="5" t="n">
+    <row r="122">
+      <c r="B122" s="68" t="inlineStr">
+        <is>
+          <t>Acs6</t>
+        </is>
+      </c>
+      <c r="C122" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D122" s="69" t="n">
+        <v>245</v>
+      </c>
+      <c r="E122" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="69" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G122" s="69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="66" t="inlineStr">
+        <is>
+          <t>Acs7</t>
+        </is>
+      </c>
+      <c r="C123" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D123" s="67" t="n">
+        <v>207</v>
+      </c>
+      <c r="E123" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="67" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G123" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="68" t="inlineStr">
+        <is>
+          <t>Acs8</t>
+        </is>
+      </c>
+      <c r="C124" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D124" s="69" t="n">
+        <v>164</v>
+      </c>
+      <c r="E124" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F124" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G124" s="69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="E44" s="6" t="n">
+    <row r="125">
+      <c r="B125" s="66" t="inlineStr">
+        <is>
+          <t>Acs9</t>
+        </is>
+      </c>
+      <c r="C125" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D125" s="67" t="n">
+        <v>170</v>
+      </c>
+      <c r="E125" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" s="67" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G125" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="68" t="inlineStr">
+        <is>
+          <t>Acs10</t>
+        </is>
+      </c>
+      <c r="C126" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D126" s="69" t="n">
+        <v>246</v>
+      </c>
+      <c r="E126" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="66" t="inlineStr">
+        <is>
+          <t>Aas1</t>
+        </is>
+      </c>
+      <c r="C127" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D127" s="67" t="n">
+        <v>203</v>
+      </c>
+      <c r="E127" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="68" t="inlineStr">
+        <is>
+          <t>Aas2</t>
+        </is>
+      </c>
+      <c r="C128" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D128" s="69" t="n">
+        <v>182</v>
+      </c>
+      <c r="E128" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="66" t="inlineStr">
+        <is>
+          <t>Aas3</t>
+        </is>
+      </c>
+      <c r="C129" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D129" s="67" t="n">
+        <v>296</v>
+      </c>
+      <c r="E129" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="67" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G129" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="68" t="inlineStr">
+        <is>
+          <t>Aas4</t>
+        </is>
+      </c>
+      <c r="C130" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D130" s="69" t="n">
+        <v>161</v>
+      </c>
+      <c r="E130" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="F130" s="69" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G130" s="69" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>231</v>
-      </c>
-      <c r="E45" s="5" t="n">
+    <row r="131">
+      <c r="B131" s="66" t="inlineStr">
+        <is>
+          <t>Aas5</t>
+        </is>
+      </c>
+      <c r="C131" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D131" s="67" t="n">
+        <v>316</v>
+      </c>
+      <c r="E131" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" s="67" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G131" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="68" t="inlineStr">
+        <is>
+          <t>Aas6</t>
+        </is>
+      </c>
+      <c r="C132" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D132" s="69" t="n">
+        <v>209</v>
+      </c>
+      <c r="E132" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="66" t="inlineStr">
+        <is>
+          <t>Aas7</t>
+        </is>
+      </c>
+      <c r="C133" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D133" s="67" t="n">
+        <v>202</v>
+      </c>
+      <c r="E133" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="F133" s="67" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G133" s="67" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>245</v>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
+    <row r="134">
+      <c r="B134" s="68" t="inlineStr">
+        <is>
+          <t>Aas8</t>
+        </is>
+      </c>
+      <c r="C134" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D134" s="69" t="n">
+        <v>186</v>
+      </c>
+      <c r="E134" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="66" t="inlineStr">
+        <is>
+          <t>Aas9</t>
+        </is>
+      </c>
+      <c r="C135" s="67" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D135" s="67" t="n">
+        <v>188</v>
+      </c>
+      <c r="E135" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="68" t="inlineStr">
+        <is>
+          <t>Aas10</t>
+        </is>
+      </c>
+      <c r="C136" s="69" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="D136" s="69" t="n">
+        <v>283</v>
+      </c>
+      <c r="E136" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" s="69" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G136" s="69" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>232</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>266</v>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>241</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>212</v>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>302</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>256</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>148</v>
-      </c>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="n">
-        <v>131</v>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>243</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>B18</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="n">
-        <v>290</v>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>223</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>VM1</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>211</v>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>VM2</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>358</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>VM3</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="n">
-        <v>296</v>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>VM4</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>VM5</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>256</v>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>VM6</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>278</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>VM7</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="n">
-        <v>174</v>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>VM8</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>253</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>VM9</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="n">
-        <v>430</v>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>VM10</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>277</v>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>VM11</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>236</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>VM12</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="n">
-        <v>182</v>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>VM13</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="n">
-        <v>215</v>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>VM14</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>VM15</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>258</v>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>VM16</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>VM17</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="n">
-        <v>232</v>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>VM18</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>VM19</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="n">
-        <v>172</v>
-      </c>
-      <c r="E80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>VM20</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>271</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Acs1</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="n">
-        <v>203</v>
-      </c>
-      <c r="E82" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Acs2</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>Acs3</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="n">
-        <v>235</v>
-      </c>
-      <c r="E84" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>Acs4</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>Acs5</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="n">
-        <v>199</v>
-      </c>
-      <c r="E86" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F86" s="6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>Acs6</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="n">
-        <v>245</v>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Acs7</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="n">
-        <v>207</v>
-      </c>
-      <c r="E88" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>Acs8</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Acs9</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="n">
-        <v>170</v>
-      </c>
-      <c r="E90" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>Acs10</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="n">
-        <v>246</v>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Aas1</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="n">
-        <v>203</v>
-      </c>
-      <c r="E92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Aas2</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>182</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Aas3</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="n">
-        <v>296</v>
-      </c>
-      <c r="E94" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" s="6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Aas4</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>161</v>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>Aas5</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>316</v>
-      </c>
-      <c r="E96" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Aas6</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>209</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Aas7</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>202</v>
-      </c>
-      <c r="E98" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>Aas8</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="n">
-        <v>186</v>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Aas9</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="n">
-        <v>188</v>
-      </c>
-      <c r="E100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>Aas10</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="n">
-        <v>283</v>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104">
-      <c r="B104" s="63" t="inlineStr">
-        <is>
-          <t>Hedge Token Inventory by Form (Table 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="64" t="inlineStr">
-        <is>
-          <t>Every retained surface form with Layer 1 type and count. Sums to 65. Matches thesis Table 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="65" t="inlineStr">
-        <is>
-          <t>Hedge form</t>
-        </is>
-      </c>
-      <c r="C107" s="65" t="inlineStr">
-        <is>
-          <t>Layer 1 type</t>
-        </is>
-      </c>
-      <c r="D107" s="65" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="E107" s="65" t="inlineStr">
-        <is>
-          <t>% of total hedges</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="66" t="inlineStr">
-        <is>
-          <t>potential</t>
-        </is>
-      </c>
-      <c r="C108" s="66" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D108" s="67" t="n">
-        <v>19</v>
-      </c>
-      <c r="E108" s="67" t="inlineStr">
-        <is>
-          <t>29.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="68" t="inlineStr">
-        <is>
-          <t>suggests</t>
-        </is>
-      </c>
-      <c r="C109" s="68" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D109" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="E109" s="69" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="66" t="inlineStr">
-        <is>
-          <t>suggest</t>
-        </is>
-      </c>
-      <c r="C110" s="66" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D110" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E110" s="67" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="68" t="inlineStr">
-        <is>
-          <t>suggesting</t>
-        </is>
-      </c>
-      <c r="C111" s="68" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D111" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" s="69" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="66" t="inlineStr">
-        <is>
-          <t>implies</t>
-        </is>
-      </c>
-      <c r="C112" s="66" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D112" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="E112" s="67" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="68" t="inlineStr">
-        <is>
-          <t>indicating</t>
-        </is>
-      </c>
-      <c r="C113" s="68" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D113" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" s="69" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="66" t="inlineStr">
-        <is>
-          <t>likely</t>
-        </is>
-      </c>
-      <c r="C114" s="66" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D114" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="E114" s="67" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="68" t="inlineStr">
-        <is>
-          <t>implying</t>
-        </is>
-      </c>
-      <c r="C115" s="68" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D115" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="69" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="66" t="inlineStr">
-        <is>
-          <t>inferring</t>
-        </is>
-      </c>
-      <c r="C116" s="66" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D116" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="67" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="68" t="inlineStr">
-        <is>
-          <t>possible</t>
-        </is>
-      </c>
-      <c r="C117" s="68" t="inlineStr">
-        <is>
-          <t>Lexical Hedges</t>
-        </is>
-      </c>
-      <c r="D117" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="69" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="66" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="C118" s="66" t="inlineStr">
-        <is>
-          <t>Modal Verbs</t>
-        </is>
-      </c>
-      <c r="D118" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E118" s="67" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="68" t="inlineStr">
-        <is>
-          <t>could</t>
-        </is>
-      </c>
-      <c r="C119" s="68" t="inlineStr">
-        <is>
-          <t>Modal Verbs</t>
-        </is>
-      </c>
-      <c r="D119" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="E119" s="69" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="45" customHeight="1">
-      <c r="B120" s="66" t="inlineStr">
-        <is>
-          <t>may</t>
-        </is>
-      </c>
-      <c r="C120" s="66" t="inlineStr">
-        <is>
-          <t>Modal Verbs</t>
-        </is>
-      </c>
-      <c r="D120" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E120" s="67" t="inlineStr">
-        <is>
-          <t>9.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="45" customHeight="1">
-      <c r="B121" s="68" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="C121" s="68" t="inlineStr">
-        <is>
-          <t>Modal Verbs</t>
-        </is>
-      </c>
-      <c r="D121" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="E121" s="69" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="45" customHeight="1">
-      <c r="B122" s="66" t="inlineStr">
-        <is>
-          <t>potentially</t>
-        </is>
-      </c>
-      <c r="C122" s="66" t="inlineStr">
-        <is>
-          <t>Adverbial Hedges</t>
-        </is>
-      </c>
-      <c r="D122" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" s="67" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="45" customHeight="1">
-      <c r="B123" s="70" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C123" s="70" t="inlineStr"/>
-      <c r="D123" s="71" t="n">
-        <v>65</v>
-      </c>
-      <c r="E123" s="71" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="45" customHeight="1"/>
-    <row r="126">
-      <c r="B126" s="63" t="inlineStr">
-        <is>
-          <t>Outcome Type by Discipline (Table 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="64" t="inlineStr">
-        <is>
-          <t>Counts are abstracts (one outcome type per abstract). Matches thesis Table 7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128"/>
-    <row r="129">
-      <c r="B129" s="65" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="C129" s="65" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="D129" s="65" t="inlineStr">
-        <is>
-          <t>Veterinary Medicine</t>
-        </is>
-      </c>
-      <c r="E129" s="65" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="F129" s="65" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="66" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C130" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="E130" s="67" t="n">
-        <v>7</v>
-      </c>
-      <c r="F130" s="67" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="68" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="C131" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="D131" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="E131" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="F131" s="69" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="66" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="C132" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D132" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="F132" s="67" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="68" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="C133" s="69" t="n">
-        <v>14</v>
-      </c>
-      <c r="D133" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E133" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="F133" s="69" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="66" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C134" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E134" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="F134" s="67" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="70" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C135" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="D135" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="E135" s="71" t="n">
-        <v>20</v>
-      </c>
-      <c r="F135" s="71" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138">
-      <c r="B138" s="63" t="inlineStr">
-        <is>
-          <t>Outcome Type Definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="64" t="inlineStr">
-        <is>
-          <t>Same definitions used in thesis Part IV. Not hedge types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140"/>
-    <row r="141">
-      <c r="B141" s="65" t="inlineStr">
-        <is>
-          <t>Outcome Type</t>
-        </is>
-      </c>
-      <c r="C141" s="65" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="D141" s="65" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="66" t="inlineStr">
-        <is>
-          <t>Binary</t>
-        </is>
-      </c>
-      <c r="C142" s="67" t="n">
-        <v>15</v>
-      </c>
-      <c r="D142" s="66" t="inlineStr">
-        <is>
-          <t>Presence or absence findings or clear yes/no outcomes (e.g., zone of inhibition vs none, pathogen detected vs not, positive vs negative diagnostic result).</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="68" t="inlineStr">
-        <is>
-          <t>Continuous</t>
-        </is>
-      </c>
-      <c r="C143" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="D143" s="68" t="inlineStr">
-        <is>
-          <t>Graded quantities such as means, yields, rates, concentrations, or growth measures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="66" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="C144" s="67" t="n">
-        <v>9</v>
-      </c>
-      <c r="D144" s="66" t="inlineStr">
-        <is>
-          <t>Abstract combines more than one outcome style (e.g., binary plus continuous, or continuous plus a null test).</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="68" t="inlineStr">
-        <is>
-          <t>Null/NS</t>
-        </is>
-      </c>
-      <c r="C145" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="D145" s="68" t="inlineStr">
-        <is>
-          <t>Abstract explicitly reports non-significance, no significant difference, or a null statistical result.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="66" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C146" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="D146" s="66" t="inlineStr">
-        <is>
-          <t>Results language does not fit the four boxes cleanly (e.g., descriptive profiles, rankings, or designs that are not clearly binary, continuous, mixed, or null).</t>
         </is>
       </c>
     </row>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="B2:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -829,7 +829,6 @@
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="72" t="inlineStr">
         <is>
@@ -844,7 +843,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="63" t="inlineStr">
         <is>
@@ -989,7 +987,6 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="63" t="inlineStr">
         <is>
@@ -1074,7 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="63" t="inlineStr">
         <is>
@@ -1427,7 +1423,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="B39" s="63" t="inlineStr">
         <is>
@@ -1527,7 +1522,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="B47" s="63" t="inlineStr">
         <is>
@@ -1597,7 +1591,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="B53" s="63" t="inlineStr">
         <is>
@@ -1753,7 +1746,6 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="B63" s="63" t="inlineStr">
         <is>
@@ -1860,7 +1852,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="B72" s="64" t="inlineStr">
         <is>
@@ -1868,7 +1859,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="B74" s="63" t="inlineStr">
         <is>
@@ -3687,7 +3677,7 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>Lexical hedge: 'indicating unsafe conditions' — inference from coliform presence to a safety judgment, not a restatement of operational meaning. Per indicating rule: inference beyond the data = hedge.</t>
+          <t>Lexical hedge: 'indicating unsafe conditions'  -  inference from coliform presence to a safety judgment, not a restatement of operational meaning. Per indicating rule: inference beyond the data = hedge.</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4150,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'presence of mycobacterial infections' asserts existence; 'potential mycobacterial infections' marks them as possible.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment  -  'presence of mycobacterial infections' asserts existence; 'potential mycobacterial infections' marks them as possible.</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4193,7 @@
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'their quorum quenching activities' asserts the activities exist.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment  -  'their quorum quenching activities' asserts the activities exist.</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4408,7 @@
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'public health concerns' asserted as fact vs possible. Same abstract also codes conclusion-position 'potential public health risks' as EC.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment  -  'public health concerns' asserted as fact vs possible. Same abstract also codes conclusion-position 'potential public health risks' as EC.</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5053,7 @@
       </c>
       <c r="J39" s="21" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'posed health risks' asserts risks as fact.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment  -  'posed health risks' asserts risks as fact.</t>
         </is>
       </c>
     </row>
@@ -5923,7 +5913,7 @@
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
-          <t>Modal hedge: 'can effectively promote early growth' — tentative generalization from this study's findings, not an established property. Sits inside a 'suggest' clause softening an overgeneralization.</t>
+          <t>Modal hedge: 'can effectively promote early growth'  -  tentative generalization from this study's findings, not an established property. Sits inside a 'suggest' clause softening an overgeneralization.</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6128,7 @@
       </c>
       <c r="J64" s="23" t="inlineStr">
         <is>
-          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment — 'a solution' is stronger endorsement than 'a potential solution'. Multi-hedge isolation: 'can' already coded EC in same sentence; 'potential' independently softens.</t>
+          <t>[AMB] Lexical hedge (Working Test): removing 'potential' changes commitment  -  'a solution' is stronger endorsement than 'a potential solution'. Multi-hedge isolation: 'can' already coded EC in same sentence; 'potential' independently softens.</t>
         </is>
       </c>
     </row>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -3501,7 +3501,7 @@
     <row r="3">
       <c r="B3" s="48" t="inlineStr">
         <is>
-          <t>Confirmed Layer 1 type + Layer 2 function codes for all retained hedges (n=65 tokens).</t>
+          <t>Confirmed Layer 1 type + Layer 2 function for retained hedges (n=65). Stage 1 retention; Stage 2 function (all EC in this sample).</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
     <row r="3">
       <c r="B3" s="48" t="inlineStr">
         <is>
-          <t>False-positive hedge candidates rejected under the Working Test, with reason codes.</t>
+          <t>False-positive candidates rejected under Stage 1 exclusions and decision rules (FP-Gen, FP-Rec, FP-Proc, FP-Cap). Full Stage 1 pass: no promotions into retained set.</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
       <c r="A3" s="49" t="n"/>
       <c r="B3" s="51" t="inlineStr">
         <is>
-          <t>Discourse-organization connectors and politeness scan across 60 abstracts. Hedge? = N for all. Not counted in Layer 1/2 totals.</t>
+          <t>DO connectors and P scan across 60 abstracts. Sequence-only DO and absent P: not retained at Stage 1. Not counted in Layer 1/2 totals.</t>
         </is>
       </c>
       <c r="C3" s="49" t="n"/>
@@ -12976,7 +12976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H44"/>
+  <dimension ref="B1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -12989,6 +12989,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="17" t="inlineStr">
         <is>
@@ -12999,7 +13000,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Final coded output for the 60-abstract PSAU corpus, coded per the Hedging Codebook.</t>
+          <t>Final coded output for the 60-abstract PSAU corpus. Stage 1 full pass completed: n=65 retained, all EC at Stage 2; no P forms in corpus; sequence-only DO and FP codes unchanged.</t>
         </is>
       </c>
     </row>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H136"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -829,6 +829,7 @@
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="72" t="inlineStr">
         <is>
@@ -843,6 +844,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="63" t="inlineStr">
         <is>
@@ -987,17 +989,18 @@
         <v>0.47</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="63" t="inlineStr">
         <is>
-          <t>2. Hedge Type Breakdown (Layer 1) - Table 2</t>
+          <t>2. Hedge Type Breakdown (Type) - Table 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="65" t="inlineStr">
         <is>
-          <t>Layer 1 Type</t>
+          <t>Grammatical type</t>
         </is>
       </c>
       <c r="C13" s="65" t="inlineStr">
@@ -1071,6 +1074,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="63" t="inlineStr">
         <is>
@@ -1093,7 +1097,7 @@
       </c>
       <c r="C21" s="65" t="inlineStr">
         <is>
-          <t>Layer 1 type</t>
+          <t>Grammatical type</t>
         </is>
       </c>
       <c r="D21" s="65" t="inlineStr">
@@ -1423,6 +1427,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="B39" s="63" t="inlineStr">
         <is>
@@ -1522,10 +1527,11 @@
         <v>33</v>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" s="63" t="inlineStr">
         <is>
-          <t>5. Layer 3 - Unhedged Assertion Site Breakdown</t>
+          <t>5. Unhedged Assertion Site Breakdown</t>
         </is>
       </c>
     </row>
@@ -1591,6 +1597,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="B53" s="63" t="inlineStr">
         <is>
@@ -1746,6 +1753,7 @@
         <v>60</v>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="B63" s="63" t="inlineStr">
         <is>
@@ -1852,6 +1860,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="B72" s="64" t="inlineStr">
         <is>
@@ -1859,6 +1868,7 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="B74" s="63" t="inlineStr">
         <is>
@@ -12976,7 +12986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H44"/>
+  <dimension ref="B2:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -12989,7 +12999,6 @@
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="17" t="inlineStr">
         <is>

--- a/thesis/007_CompiledResult_Draft_005.xlsx
+++ b/thesis/007_CompiledResult_Draft_005.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -160,6 +160,20 @@
       <name val="Georgia"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="15">
@@ -308,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -450,6 +464,11 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -816,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="B2:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -829,7 +848,6 @@
     <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="72" t="inlineStr">
         <is>
@@ -844,7 +862,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="63" t="inlineStr">
         <is>
@@ -989,7 +1006,6 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="63" t="inlineStr">
         <is>
@@ -1074,7 +1090,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="63" t="inlineStr">
         <is>
@@ -1427,7 +1442,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="B39" s="63" t="inlineStr">
         <is>
@@ -1527,7 +1541,6 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="B47" s="63" t="inlineStr">
         <is>
@@ -1597,7 +1610,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="B53" s="63" t="inlineStr">
         <is>
@@ -1753,7 +1765,6 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="B63" s="63" t="inlineStr">
         <is>
@@ -1860,7 +1871,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="B72" s="64" t="inlineStr">
         <is>
@@ -1868,7 +1878,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="B74" s="63" t="inlineStr">
         <is>
@@ -8478,7 +8487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H41"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8489,6 +8498,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -8504,6 +8514,11 @@
           <t>Layer 3 optional unhedged assertion sites [R]/[G]/[C] (corpus-wide).</t>
         </is>
       </c>
+      <c r="I3" s="74" t="inlineStr">
+        <is>
+          <t>Illustrative only; reverse-test examples, not observed corpus hedges.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
@@ -8541,6 +8556,11 @@
           <t>Coder Notes</t>
         </is>
       </c>
+      <c r="I4" s="75" t="inlineStr">
+        <is>
+          <t>Example hedge (illustrative)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="B5" s="5" t="inlineStr">
@@ -8576,6 +8596,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I5" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="B6" s="6" t="inlineStr">
@@ -8611,6 +8636,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I6" s="76" t="inlineStr">
+        <is>
+          <t>there appeared to be no zone of inhibition</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="B7" s="5" t="inlineStr">
@@ -8646,6 +8676,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I7" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
@@ -8681,6 +8716,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I8" s="76" t="inlineStr">
+        <is>
+          <t>may not apply / do not necessarily apply</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
@@ -8716,6 +8756,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I9" s="76" t="inlineStr">
+        <is>
+          <t>appeared to show / suggested</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="B10" s="6" t="inlineStr">
@@ -8751,6 +8796,11 @@
           <t>Unhedged clause [C] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I10" s="76" t="inlineStr">
+        <is>
+          <t>may have caused / appeared to cause</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
@@ -8786,6 +8836,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I11" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="B12" s="6" t="inlineStr">
@@ -8821,6 +8876,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I12" s="76" t="inlineStr">
+        <is>
+          <t>may provide / appears to provide</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
@@ -8856,6 +8916,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I13" s="76" t="inlineStr">
+        <is>
+          <t>appear to exhibit / may exhibit</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
@@ -8891,6 +8956,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I14" s="76" t="inlineStr">
+        <is>
+          <t>appeared to be / may have been</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
@@ -8926,6 +8996,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I15" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="B16" s="6" t="inlineStr">
@@ -8961,6 +9036,11 @@
           <t>Unhedged clause [C] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I16" s="76" t="inlineStr">
+        <is>
+          <t>appeared to achieve / may have achieved</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
@@ -8996,6 +9076,11 @@
           <t>Unhedged clause [C] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I17" s="76" t="inlineStr">
+        <is>
+          <t>appeared to show / suggested</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="B18" s="6" t="inlineStr">
@@ -9031,6 +9116,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I18" s="76" t="inlineStr">
+        <is>
+          <t>appeared to indicate / may indicate</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="B19" s="5" t="inlineStr">
@@ -9066,6 +9156,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I19" s="76" t="inlineStr">
+        <is>
+          <t>appeared to find / may suggest</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="B20" s="6" t="inlineStr">
@@ -9101,6 +9196,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I20" s="76" t="inlineStr">
+        <is>
+          <t>appeared to be / may have been</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="B21" s="5" t="inlineStr">
@@ -9136,6 +9236,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I21" s="76" t="inlineStr">
+        <is>
+          <t>appeared to be / may have been</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
@@ -9171,6 +9276,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I22" s="76" t="inlineStr">
+        <is>
+          <t>appeared to show / suggested</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="B23" s="5" t="inlineStr">
@@ -9206,6 +9316,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I23" s="76" t="inlineStr">
+        <is>
+          <t>appeared to be / may have been</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
@@ -9241,6 +9356,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I24" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
@@ -9276,6 +9396,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I25" s="76" t="inlineStr">
+        <is>
+          <t>may have / appears to have</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="B26" s="6" t="inlineStr">
@@ -9311,6 +9436,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I26" s="76" t="inlineStr">
+        <is>
+          <t>appeared to exhibit / may have exhibited</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="B27" s="5" t="inlineStr">
@@ -9346,6 +9476,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I27" s="76" t="inlineStr">
+        <is>
+          <t>appeared to find / may suggest</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="B28" s="6" t="inlineStr">
@@ -9381,6 +9516,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I28" s="76" t="inlineStr">
+        <is>
+          <t>appeared to indicate / may indicate</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="B29" s="5" t="inlineStr">
@@ -9416,6 +9556,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I29" s="76" t="inlineStr">
+        <is>
+          <t>appeared to confirm / may confirm</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="B30" s="6" t="inlineStr">
@@ -9451,6 +9596,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I30" s="76" t="inlineStr">
+        <is>
+          <t>there appeared to be no significant difference</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="B31" s="5" t="inlineStr">
@@ -9486,6 +9636,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I31" s="76" t="inlineStr">
+        <is>
+          <t>may have influenced / appeared to influence</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
@@ -9521,6 +9676,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I32" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
@@ -9556,6 +9716,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I33" s="76" t="inlineStr">
+        <is>
+          <t>appeared to be / may have been</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="B34" s="6" t="inlineStr">
@@ -9591,6 +9756,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I34" s="76" t="inlineStr">
+        <is>
+          <t>appeared to reveal / may reveal</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="B35" s="5" t="inlineStr">
@@ -9626,6 +9796,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I35" s="76" t="inlineStr">
+        <is>
+          <t>appeared to be / may have been</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
@@ -9661,6 +9836,11 @@
           <t>Unhedged clause [C] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I36" s="76" t="inlineStr">
+        <is>
+          <t>appeared to have / may have had</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="B37" s="5" t="inlineStr">
@@ -9696,6 +9876,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I37" s="76" t="inlineStr">
+        <is>
+          <t>appeared to show / suggested</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="B38" s="6" t="inlineStr">
@@ -9731,6 +9916,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I38" s="76" t="inlineStr">
+        <is>
+          <t>appeared to find / may suggest</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="B39" s="5" t="inlineStr">
@@ -9766,6 +9956,11 @@
           <t>Unhedged clause [G] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I39" s="76" t="inlineStr">
+        <is>
+          <t>suggested / appeared to show</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="B40" s="6" t="inlineStr">
@@ -9801,6 +9996,11 @@
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
         </is>
       </c>
+      <c r="I40" s="76" t="inlineStr">
+        <is>
+          <t>appeared to disclose / suggested</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
@@ -9834,6 +10034,11 @@
       <c r="H41" s="21" t="inlineStr">
         <is>
           <t>Unhedged clause [R] (sentence-level mark, curated). Reverse test: a hedge could be inserted without changing the facts.</t>
+        </is>
+      </c>
+      <c r="I41" s="76" t="inlineStr">
+        <is>
+          <t>appeared not to be significant</t>
         </is>
       </c>
     </row>
